--- a/Results/Hydrogen/hydrogen particulate matter results.xlsx
+++ b/Results/Hydrogen/hydrogen particulate matter results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.366392414758873e-07</v>
+        <v>4.366392414758979e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.936670559190915e-07</v>
+        <v>3.936670559190912e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>8.051541435880208e-06</v>
+        <v>8.051541435880191e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>3.936670559190915e-07</v>
+        <v>3.936670559190912e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>3.936670559190915e-07</v>
+        <v>3.936670559190912e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>4.036299184806355e-06</v>
+        <v>4.036299184806348e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>1.455499789368538e-06</v>
+        <v>1.455499789368524e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>3.936670559190915e-07</v>
+        <v>3.936670559190912e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>7.900681948354738e-07</v>
+        <v>7.900681948354687e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>6.980655527460504e-07</v>
+        <v>6.980655527460446e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.349530518736891e-06</v>
+        <v>1.178281530338768e-06</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.025740673436631e-08</v>
+        <v>6.025740673436641e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.301730932589344e-08</v>
+        <v>5.30173093258935e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>6.025740673436631e-08</v>
+        <v>6.025740673436641e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.423340778795503e-08</v>
+        <v>5.423340778795521e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.423340778795501e-08</v>
+        <v>5.423340778795514e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.981712675539076e-08</v>
+        <v>5.981712675539083e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>6.025740673436631e-08</v>
+        <v>6.025740673436641e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.732999974403948e-08</v>
+        <v>5.732999974403968e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>6.025740673436631e-08</v>
+        <v>6.025740673436641e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>6.025740673436631e-08</v>
+        <v>6.025740673436641e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>6.025740673436631e-08</v>
+        <v>6.025740673436641e-08</v>
       </c>
     </row>
     <row r="4">
@@ -595,34 +595,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.179599036339622e-07</v>
+        <v>5.705250091532254e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.850617043672371e-08</v>
+        <v>4.850617043672366e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.813238218081983e-08</v>
+        <v>6.813218453849867e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>4.786910075493023e-08</v>
+        <v>4.786910075493031e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.361911658513966e-08</v>
+        <v>5.361911658513975e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.175196236549866e-07</v>
+        <v>1.175196236549868e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.236006816988419e-07</v>
+        <v>1.236006816988417e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.150324966436354e-07</v>
+        <v>5.412509392499581e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.867853001226618e-08</v>
+        <v>5.867853001226714e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.336612535878894e-08</v>
+        <v>5.336612535878896e-08</v>
       </c>
       <c r="L4" t="n">
         <v>5.736812362766006e-08</v>
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.078869942230717e-07</v>
+        <v>1.078869942230716e-07</v>
       </c>
       <c r="C5" t="n">
         <v>1.049595872327451e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>1.078787258132965e-07</v>
+        <v>1.078787258132966e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.048637168607971e-07</v>
+        <v>1.048637168607972e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.048637168607971e-07</v>
+        <v>1.048637168607972e-07</v>
       </c>
       <c r="G5" t="n">
         <v>1.074467142440962e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.078869942230717e-07</v>
+        <v>1.078869942230716e-07</v>
       </c>
       <c r="I5" t="n">
         <v>1.049595872327451e-07</v>
       </c>
       <c r="J5" t="n">
-        <v>1.078869942230717e-07</v>
+        <v>1.078869942230716e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.078869942230717e-07</v>
+        <v>1.078869942230716e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.078869942230717e-07</v>
+        <v>1.078869942230716e-07</v>
       </c>
     </row>
     <row r="6">
@@ -675,28 +675,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.756872942155772e-07</v>
+        <v>1.756872942155771e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.665242177410398e-07</v>
+        <v>2.6652421774104e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.889697352551196e-07</v>
+        <v>2.8896973525512e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.40867553836747e-07</v>
+        <v>2.408675538367471e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.756817942100691e-07</v>
+        <v>1.756817942100692e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.690738497145977e-07</v>
+        <v>2.690738497145979e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.695141296935625e-07</v>
+        <v>2.69514129693563e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.665867227032468e-07</v>
+        <v>2.665867227032467e-07</v>
       </c>
       <c r="J6" t="n">
         <v>2.695325693471075e-07</v>
@@ -705,7 +705,7 @@
         <v>1.739444125735331e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.675241050203671e-07</v>
+        <v>3.675241050203674e-07</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.957102060853319e-07</v>
+        <v>2.957102060853321e-07</v>
       </c>
       <c r="C7" t="n">
         <v>3.668140388495851e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>3.697416155964931e-07</v>
+        <v>3.69741615596493e-07</v>
       </c>
       <c r="E7" t="n">
         <v>4.522446861720689e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>3.668140491737316e-07</v>
+        <v>3.668140491737306e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>3.693011658609364e-07</v>
+        <v>3.693011658609367e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>3.697414458399113e-07</v>
+        <v>3.697414458399119e-07</v>
       </c>
       <c r="I7" t="n">
         <v>3.668140388495851e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>3.697414458399113e-07</v>
+        <v>3.697414458399119e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.765228564620837e-07</v>
+        <v>3.268475261819505e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>3.697414458399113e-07</v>
+        <v>3.697414458399119e-07</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.175206072869641e-08</v>
+        <v>6.175206072869816e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.465298833201373e-08</v>
+        <v>4.46529883320137e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.014685898710428e-07</v>
+        <v>-1.014685898710429e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>4.465298833201373e-08</v>
+        <v>4.46529883320137e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>4.465298833201373e-08</v>
+        <v>4.46529883320137e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.411858998049866e-08</v>
+        <v>-1.411858998049847e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.348035064442418e-08</v>
+        <v>4.348035064442417e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.465298833201373e-08</v>
+        <v>4.46529883320137e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.510831403015925e-08</v>
+        <v>5.51083140301593e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.626853763347747e-08</v>
+        <v>5.626853763347752e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.839385479320798e-08</v>
+        <v>4.839385479320794e-08</v>
       </c>
     </row>
     <row r="9">
@@ -795,13 +795,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.547041665342224e-08</v>
+        <v>6.547041665342214e-08</v>
       </c>
       <c r="C9" t="n">
         <v>4.823331797743095e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.00377202623524e-09</v>
+        <v>-1.003772026235194e-09</v>
       </c>
       <c r="E9" t="n">
         <v>4.823331797743095e-08</v>
@@ -810,22 +810,22 @@
         <v>4.823331797743095e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.414392736774892e-08</v>
+        <v>3.414392736774902e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.805297594335389e-08</v>
+        <v>5.805297594335385e-08</v>
       </c>
       <c r="I9" t="n">
         <v>4.823331797743095e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>6.277006888440389e-08</v>
+        <v>6.277006888440386e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.323772897618402e-08</v>
+        <v>6.323772897618405e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.004568779204595e-08</v>
+        <v>6.004568779204599e-08</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.690265430143056e-07</v>
+        <v>1.690265430143051e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>4.270441188257602e-07</v>
+        <v>4.270441188257594e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>4.189471375831555e-07</v>
+        <v>4.189471375831566e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>4.270441188257602e-07</v>
+        <v>4.270441188257594e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>4.270441188257602e-07</v>
+        <v>4.270441188257594e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>3.515945831360034e-07</v>
+        <v>3.515945831359974e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>2.44826737027524e-07</v>
+        <v>2.448267370275237e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>4.270441188257602e-07</v>
+        <v>4.270441188257594e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>7.684316695982605e-07</v>
+        <v>7.684316695982611e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>2.327167857340982e-07</v>
+        <v>2.32716785734099e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>2.137693421662605e-07</v>
+        <v>1.840095303275722e-07</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.922318950248413e-08</v>
+        <v>4.922318950248411e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.706597002734659e-08</v>
+        <v>4.706597002734646e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>4.922318950248413e-08</v>
+        <v>4.922318950248411e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.782391848251874e-08</v>
+        <v>4.782391848251854e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.782391848251874e-08</v>
+        <v>4.782391848251852e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>4.892917175940233e-08</v>
+        <v>4.892917175940223e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>4.922318950248413e-08</v>
+        <v>4.922318950248411e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.723404544650437e-08</v>
+        <v>4.72340454465042e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>4.922318950248413e-08</v>
+        <v>4.922318950248411e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>4.922318950248413e-08</v>
+        <v>4.922318950248411e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>4.922318950248413e-08</v>
+        <v>4.922318950248411e-08</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.80600115008712e-08</v>
+        <v>7.806001150087111e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.963571107334144e-08</v>
+        <v>3.963571107334104e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.196541759032972e-08</v>
+        <v>7.909685696516633e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.91691481920129e-08</v>
+        <v>3.916914819201276e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.982600125888697e-08</v>
+        <v>3.982600125888679e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>7.776599375778934e-08</v>
+        <v>4.141912523535878e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.161986200231298e-08</v>
+        <v>8.161986200231285e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.972399892246091e-08</v>
+        <v>3.972399892246072e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>7.895144976030876e-08</v>
+        <v>7.895144976030868e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.132234860991957e-08</v>
+        <v>4.132234860991781e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.170182959024686e-08</v>
+        <v>4.170182959024684e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.706528460487935e-08</v>
+        <v>7.70652846048792e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.507614054889957e-08</v>
+        <v>7.507614054889928e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.705814227114051e-08</v>
+        <v>7.705814227114037e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.50739918953103e-08</v>
+        <v>7.507399189531003e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.50739918953103e-08</v>
+        <v>7.507399189531003e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.677126686179764e-08</v>
+        <v>7.677126686179746e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.706528460487935e-08</v>
+        <v>7.70652846048792e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.507614054889957e-08</v>
+        <v>7.507614054889928e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.706528460487935e-08</v>
+        <v>7.70652846048792e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.706528460487935e-08</v>
+        <v>7.70652846048792e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.706528460487935e-08</v>
+        <v>7.70652846048792e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.237516907413767e-07</v>
+        <v>1.237516907413764e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.841875864959712e-07</v>
+        <v>1.841875864959704e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.990974214309895e-07</v>
+        <v>1.990974214309891e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.671159773671231e-07</v>
+        <v>1.671159773671224e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.237436847942729e-07</v>
+        <v>1.237436847942725e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.858632092180281e-07</v>
+        <v>1.858632092180275e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.86157226961102e-07</v>
+        <v>1.861572269611016e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.841680829051301e-07</v>
+        <v>1.841680829051296e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.861694914337248e-07</v>
+        <v>1.861694914337244e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.225924758647243e-07</v>
+        <v>1.22592475864724e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.513450278101054e-07</v>
+        <v>2.513450278101047e-07</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.451716976492691e-07</v>
+        <v>1.451716976492686e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.762685497979529e-07</v>
+        <v>1.762685497979524e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.782577409376475e-07</v>
+        <v>1.782577409376469e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.144491482718519e-07</v>
+        <v>2.144491482718514e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.762685640599329e-07</v>
+        <v>1.762685640599325e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.779636761108509e-07</v>
+        <v>1.779636761108504e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.782576938539327e-07</v>
+        <v>1.782576938539324e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.762685497979529e-07</v>
+        <v>1.762685497979524e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.782576938539327e-07</v>
+        <v>1.782576938539324e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.590875575174436e-07</v>
+        <v>1.590875575174431e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.782576938539327e-07</v>
+        <v>1.782576938539324e-07</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.533035465317533e-08</v>
+        <v>5.533035465317526e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.406250437552523e-08</v>
+        <v>3.406250437552517e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.865547604308455e-08</v>
+        <v>4.865547604308448e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.406250437552523e-08</v>
+        <v>3.406250437552517e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.406250437552523e-08</v>
+        <v>3.406250437552517e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.058624893479189e-08</v>
+        <v>5.058624893479187e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.398822836453879e-08</v>
+        <v>5.398822836453878e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.406250437552523e-08</v>
+        <v>3.406250437552517e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.14702555260157e-08</v>
+        <v>4.147025552601564e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.350306336229059e-08</v>
+        <v>5.350306336229057e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.461801456302276e-08</v>
+        <v>5.550078975124518e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1191,13 +1191,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.609584679911301e-08</v>
+        <v>5.609584679911298e-08</v>
       </c>
       <c r="C9" t="n">
         <v>3.932122701849197e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.337746495380204e-08</v>
+        <v>5.337746495380194e-08</v>
       </c>
       <c r="E9" t="n">
         <v>3.932122701849197e-08</v>
@@ -1206,7 +1206,7 @@
         <v>3.932122701849197e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.406906871779661e-08</v>
+        <v>5.406906871779654e-08</v>
       </c>
       <c r="H9" t="n">
         <v>5.555314234930188e-08</v>
@@ -1215,13 +1215,13 @@
         <v>3.932122701849197e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.045710502344482e-08</v>
+        <v>5.045710502344478e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>5.535185205902518e-08</v>
+        <v>5.535185205902521e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>5.580840000558827e-08</v>
+        <v>5.580840000558823e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.530884140316166e-07</v>
+        <v>1.530884140316175e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.072606018528206e-07</v>
+        <v>3.072606018528202e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>3.972313489377318e-06</v>
+        <v>3.972313489377313e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>2.461616584796995e-07</v>
+        <v>2.461616584797018e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.461616584796995e-07</v>
+        <v>2.461616584797018e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.856478419768109e-06</v>
+        <v>1.856478419768108e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>5.199749669447896e-07</v>
+        <v>5.199749669447886e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>2.461616584796995e-07</v>
+        <v>2.461616584797018e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.312022349256621e-06</v>
+        <v>1.312022349256623e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>3.541354347706612e-07</v>
+        <v>3.541354347706623e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>3.947599806144937e-07</v>
+        <v>3.947599806144934e-07</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.48887182878136e-08</v>
+        <v>5.488871828781371e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.995004315065273e-08</v>
+        <v>4.995004315065274e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.48887182878136e-08</v>
+        <v>5.488871828781372e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.806519814687305e-08</v>
+        <v>4.806519814687286e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.806519814687306e-08</v>
+        <v>4.80651981468729e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.452251473148072e-08</v>
+        <v>5.452251473148056e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.48887182878136e-08</v>
+        <v>5.488871828781372e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.244037742980642e-08</v>
+        <v>5.244037742980609e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.488871828781357e-08</v>
+        <v>5.488871828781372e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.48887182878136e-08</v>
+        <v>5.488871828781372e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.48887182878136e-08</v>
+        <v>5.488871828781372e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.510634847570115e-08</v>
+        <v>4.796034732623761e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.50789253777505e-08</v>
+        <v>4.507892537775046e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.364884893721388e-08</v>
+        <v>5.36485727779193e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>4.199467722369268e-08</v>
+        <v>4.199467722369273e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.528316774375232e-08</v>
+        <v>4.528316774375236e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>9.474014491936826e-08</v>
+        <v>9.474014491936811e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.044113236725795e-07</v>
+        <v>1.044113236725796e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>9.265800761769362e-08</v>
+        <v>9.265800761769368e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.772125904074978e-08</v>
+        <v>9.772125904074998e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.606215616103779e-08</v>
+        <v>4.606215616103752e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.801894937294685e-08</v>
+        <v>4.801894937294705e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.303916902300931e-08</v>
+        <v>9.303916902300959e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>9.299140403773315e-08</v>
+        <v>9.299140403773312e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>9.303225878397328e-08</v>
+        <v>9.303225878397345e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>9.05635417696991e-08</v>
+        <v>9.056354176969908e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>9.05635417696991e-08</v>
+        <v>9.056354176969908e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>9.267296546667637e-08</v>
+        <v>9.267296546667638e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>9.303916902300931e-08</v>
+        <v>9.303916902300959e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>9.0590828165002e-08</v>
+        <v>9.059082816500194e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>9.303916902300931e-08</v>
+        <v>9.303916902300959e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>9.303916902300931e-08</v>
+        <v>9.303916902300959e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>9.303916902300931e-08</v>
+        <v>9.303916902300959e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.521169163162508e-07</v>
+        <v>1.521169163162509e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.321573597362959e-07</v>
+        <v>2.321573597386613e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.488134505255813e-07</v>
+        <v>2.488134505255809e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.078509631714455e-07</v>
+        <v>2.078509631714451e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.521951323840816e-07</v>
+        <v>1.521951323840813e-07</v>
       </c>
       <c r="G6" t="n">
         <v>2.318401751972711e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.322063787539178e-07</v>
+        <v>2.322063787539174e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.297580378955968e-07</v>
+        <v>2.297580378955964e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.322221186217247e-07</v>
+        <v>2.322221186217244e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.506292134308406e-07</v>
+        <v>1.506292134308404e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.158665192423846e-07</v>
+        <v>3.158665192423839e-07</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.045086770133319e-07</v>
+        <v>2.045086770133318e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.538092376894105e-07</v>
+        <v>2.538092376894103e-07</v>
       </c>
       <c r="D7" t="n">
         <v>2.538571078399268e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>3.083556991885843e-07</v>
+        <v>3.083556991885842e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.51408678492737e-07</v>
+        <v>2.514086784927368e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.534907991183539e-07</v>
+        <v>2.534907991183536e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.538570026746869e-07</v>
+        <v>2.538570026746867e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.514086618166792e-07</v>
+        <v>2.514086618166791e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.538570026746869e-07</v>
+        <v>2.538570026746867e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.917186247654985e-07</v>
+        <v>2.252644332127579e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.538570026746869e-07</v>
+        <v>2.538570026746867e-07</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.506683340491309e-08</v>
+        <v>9.50668334049132e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.200628114844444e-08</v>
+        <v>2.200628114844446e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.023165177883673e-08</v>
+        <v>-2.023165177883684e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.049692709954896e-08</v>
+        <v>4.0496927099549e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>4.049692709954896e-08</v>
+        <v>4.049692709954899e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.565828715144598e-08</v>
+        <v>1.565828715144602e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>6.085770804277501e-08</v>
+        <v>6.08577080427751e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.049692709954896e-08</v>
+        <v>4.0496927099549e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>3.565885712383008e-08</v>
+        <v>3.565885712382999e-08</v>
       </c>
       <c r="K8" t="n">
         <v>1.008214397719928e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.472422319519187e-08</v>
+        <v>5.472422319519186e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1587,37 +1587,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.508583138697073e-08</v>
+        <v>9.508583138697078e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.510718097927427e-08</v>
+        <v>2.510718097927411e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.229859519635609e-08</v>
+        <v>3.229859519635618e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>4.236478861472986e-08</v>
+        <v>4.236478861472983e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.236478861472986e-08</v>
+        <v>4.236478861472983e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.871101453849719e-08</v>
+        <v>3.871101453849721e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.533236578173411e-08</v>
+        <v>6.533236578173422e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.236478861472986e-08</v>
+        <v>4.236478861472983e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.098802915605296e-08</v>
+        <v>5.098802915605307e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.031856342325069e-07</v>
+        <v>1.03185634232507e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>5.77353049677726e-08</v>
+        <v>5.773530496777259e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.241550746804991e-07</v>
+        <v>1.241550746804982e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.651528341159925e-07</v>
+        <v>2.651528341159891e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>2.67593693796779e-06</v>
+        <v>2.675936937967789e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>2.005635988237707e-07</v>
+        <v>2.005635988237701e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.005635988237707e-07</v>
+        <v>2.005635988237701e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.07441502122993e-06</v>
+        <v>1.074415021229922e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>3.476622679897456e-07</v>
+        <v>3.476622679897449e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>2.005635988237707e-07</v>
+        <v>2.005635988237701e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.05962486463863e-06</v>
+        <v>1.059624864638629e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>2.040571411160869e-07</v>
+        <v>2.040571411160859e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>2.176973340858183e-07</v>
+        <v>2.176973340858173e-07</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.237788405299097e-08</v>
+        <v>5.237788405299019e-08</v>
       </c>
       <c r="C3" t="n">
         <v>4.926237117237768e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.237788405299097e-08</v>
+        <v>5.237788405299019e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.862674048732741e-08</v>
+        <v>4.862674048732725e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.86267404873274e-08</v>
+        <v>4.86267404873273e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.193755406297237e-08</v>
+        <v>5.193755406297208e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.237788405299097e-08</v>
+        <v>5.237788405299019e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.942794433711449e-08</v>
+        <v>4.942794433711442e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.237788405299097e-08</v>
+        <v>5.237788405299019e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.237788405299097e-08</v>
+        <v>5.237788405299019e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.237788405299097e-08</v>
+        <v>5.237788405299019e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.623553736582304e-08</v>
+        <v>8.623553736582189e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.314359141454997e-08</v>
+        <v>4.314359141454952e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.893796394704643e-08</v>
+        <v>8.899703398776322e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.973455208376212e-08</v>
+        <v>3.97345520837621e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.182035809847553e-08</v>
+        <v>4.182035809847542e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>4.443639692598533e-08</v>
+        <v>4.44363969259848e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.529111864688772e-08</v>
+        <v>9.529111864688704e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.192678720012737e-08</v>
+        <v>4.192678720012733e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.613868545592529e-08</v>
+        <v>4.613868545592493e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.361944122660299e-08</v>
+        <v>4.361944122660258e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.488320522410448e-08</v>
+        <v>4.488320522410372e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.584078607331046e-08</v>
+        <v>8.584078607331033e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.582415668582065e-08</v>
+        <v>8.582415668582062e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.583429950187979e-08</v>
+        <v>8.583429950188e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.293248014546242e-08</v>
+        <v>8.293248014546237e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.293248014546242e-08</v>
+        <v>8.293248014546237e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.54004560832919e-08</v>
+        <v>8.540045608329195e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.584078607331046e-08</v>
+        <v>8.584078607331033e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.289084635743408e-08</v>
+        <v>8.289084635743404e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.584078607331046e-08</v>
+        <v>8.584078607331033e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.584078607331046e-08</v>
+        <v>8.584078607331033e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.584078607331046e-08</v>
+        <v>8.584078607331033e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.398583994981693e-07</v>
+        <v>1.398583994981682e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.123517982445632e-07</v>
+        <v>2.123517982469122e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.273283065376559e-07</v>
+        <v>2.273283065376552e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.89596065219569e-07</v>
+        <v>1.895960652195686e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.39233638377403e-07</v>
+        <v>1.392336383774027e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.118655247508528e-07</v>
+        <v>2.118655247508525e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.123058547415191e-07</v>
+        <v>2.123058547415184e-07</v>
       </c>
       <c r="I6" t="n">
         <v>2.09355915024995e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.123200927339716e-07</v>
+        <v>2.123200927339708e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.385126508199353e-07</v>
+        <v>1.385126508199344e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.879832796996339e-07</v>
+        <v>2.879832796996327e-07</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.68479388278621e-07</v>
+        <v>1.684793882786204e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.079109738122674e-07</v>
+        <v>2.079109738122671e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.07927680637731e-07</v>
+        <v>2.079276806377302e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.505001564403503e-07</v>
+        <v>2.5050015644035e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.049776789818446e-07</v>
+        <v>2.049776789818443e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.074872732097388e-07</v>
+        <v>2.074872732097379e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.079276031997575e-07</v>
+        <v>2.079276031997565e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.049776634838808e-07</v>
+        <v>2.049776634838807e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.079276031997575e-07</v>
+        <v>2.079276031997565e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.850711851194664e-07</v>
+        <v>1.850711851194657e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.079276031997575e-07</v>
+        <v>2.079276031997565e-07</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.437979299130287e-08</v>
+        <v>9.437979299130291e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.136241753878239e-08</v>
+        <v>2.136241753878251e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.688945101039433e-09</v>
+        <v>4.688945101039202e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>4.013631468499802e-08</v>
+        <v>4.013631468499803e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>4.013631468499802e-08</v>
+        <v>4.013631468499803e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.975255970442307e-08</v>
+        <v>2.975255970442301e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>6.238186862733671e-08</v>
+        <v>6.238186862733638e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.013631468499802e-08</v>
+        <v>4.013631468499803e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>3.780546191050813e-08</v>
+        <v>3.780546191050785e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.020777178979146e-07</v>
+        <v>1.020777178979141e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.604812043111681e-08</v>
+        <v>5.604812043111649e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.410068185057119e-08</v>
+        <v>9.410068185057087e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.410016893106083e-08</v>
+        <v>2.410016893106086e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>4.151193732344179e-08</v>
+        <v>4.151193732344175e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>4.155131036830546e-08</v>
+        <v>4.155131036830549e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.155131036830546e-08</v>
+        <v>4.155131036830549e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.321839346829932e-08</v>
+        <v>4.321839346829903e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.501420986989916e-08</v>
+        <v>6.501420986989853e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.155131036830546e-08</v>
+        <v>4.155131036830549e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.063424248894871e-08</v>
+        <v>5.063424248894848e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.025619234189168e-07</v>
+        <v>1.025619234189164e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>5.71178072627976e-08</v>
+        <v>5.711780726279733e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.041731537190036e-07</v>
+        <v>1.041731537190034e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.037519987820469e-07</v>
+        <v>2.03751998782047e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.836857284092339e-06</v>
+        <v>1.836857284092334e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>1.520894132202891e-07</v>
+        <v>1.520894132202873e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.520894132202891e-07</v>
+        <v>1.520894132202873e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>6.276954754195325e-07</v>
+        <v>6.276954754195289e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>2.729169579525119e-07</v>
+        <v>2.729169579525102e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.520894132202891e-07</v>
+        <v>1.520894132202873e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>7.757460788661345e-07</v>
+        <v>7.757460788661333e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.424974630921821e-07</v>
+        <v>1.42497463092182e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.72464386612665e-07</v>
+        <v>1.724643866126648e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.229930626123259e-08</v>
+        <v>5.229930626123263e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.000810807230977e-08</v>
+        <v>5.000810807230979e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.229930626123259e-08</v>
+        <v>5.229930626123263e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.824490359781229e-08</v>
+        <v>4.824490359781212e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.824490359781229e-08</v>
+        <v>4.824490359781214e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.191614867310613e-08</v>
+        <v>5.191614867310619e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.229930626123259e-08</v>
+        <v>5.229930626123263e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.972646631705106e-08</v>
+        <v>4.972646631705126e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.229930626123259e-08</v>
+        <v>5.229930626123263e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.229930626123259e-08</v>
+        <v>5.229930626123263e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.229930626123259e-08</v>
+        <v>5.229930626123263e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.380116463980019e-08</v>
+        <v>4.402744808220857e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.287701115780582e-08</v>
+        <v>4.287701115780248e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.686677332959667e-08</v>
+        <v>4.686677332958499e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.97267537146972e-08</v>
+        <v>3.972675371469714e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.139939473791465e-08</v>
+        <v>4.139939473791455e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>4.364429049408213e-08</v>
+        <v>8.341800705167383e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.371026110411087e-08</v>
+        <v>9.371026110411078e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.145460813802703e-08</v>
+        <v>8.122832469561887e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.515413006678802e-08</v>
+        <v>8.592719103973486e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.321662366125803e-08</v>
+        <v>4.321662366125791e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.402046030334931e-08</v>
+        <v>4.402046030335029e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.455759966678944e-08</v>
+        <v>8.455759966678947e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.45595294408136e-08</v>
+        <v>8.455952944081333e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.455111587097384e-08</v>
+        <v>8.455111587097365e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.204965344856171e-08</v>
+        <v>8.204965344856151e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.204965344856171e-08</v>
+        <v>8.204965344856151e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.417444207866341e-08</v>
+        <v>8.417444207866313e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.455759966678944e-08</v>
+        <v>8.455759966678947e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.198475972260849e-08</v>
+        <v>8.19847597226082e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.455759966678944e-08</v>
+        <v>8.455759966678947e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.455759966678944e-08</v>
+        <v>8.455759966678947e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.455759966678944e-08</v>
+        <v>8.455759966678947e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.376215384198441e-07</v>
+        <v>1.376215384198435e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.085825944521582e-07</v>
+        <v>2.08582594449413e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.231924553888095e-07</v>
+        <v>2.231924553888094e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.866132175542813e-07</v>
+        <v>1.866132175542816e-07</v>
       </c>
       <c r="F6" t="n">
         <v>1.373378941976008e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.081129865909884e-07</v>
+        <v>2.081129865909881e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.084961441802432e-07</v>
+        <v>2.084961441802433e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.059233042349333e-07</v>
+        <v>2.059233042349331e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.085100730598503e-07</v>
+        <v>2.085100730598504e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.363050062279304e-07</v>
+        <v>1.363050062279302e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.825305963325877e-07</v>
+        <v>2.825305963325878e-07</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.521402658802744e-07</v>
+        <v>1.521402658802741e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.87005784650743e-07</v>
+        <v>1.870057846507428e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.870039179454383e-07</v>
+        <v>1.870039179454379e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.246629327998859e-07</v>
+        <v>2.246629327998855e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.844310296366634e-07</v>
+        <v>1.844310296366633e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.866206972885931e-07</v>
+        <v>1.866206972885926e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.870038548767193e-07</v>
+        <v>1.87003854876719e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.844310149325379e-07</v>
+        <v>1.844310149325376e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.870038548767193e-07</v>
+        <v>1.87003854876719e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.659842359470478e-07</v>
+        <v>1.431043568555163e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.870038548767193e-07</v>
+        <v>1.87003854876719e-07</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.415305305494765e-08</v>
+        <v>9.415305305494788e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.192446920912129e-08</v>
+        <v>2.192446920912128e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.419453611154884e-08</v>
+        <v>2.41945361115489e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.027215553753085e-08</v>
+        <v>4.027215553753093e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>4.027215553753085e-08</v>
+        <v>4.027215553753093e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.887089574301417e-08</v>
+        <v>3.887089574301434e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>6.302279968638241e-08</v>
+        <v>6.302279968638253e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.027215553753085e-08</v>
+        <v>4.027215553753093e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.195314126077709e-08</v>
+        <v>4.195314126077722e-08</v>
       </c>
       <c r="K8" t="n">
         <v>1.024444062597352e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.603630490757827e-08</v>
+        <v>5.603630490757834e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.359526113477829e-08</v>
+        <v>9.359526113477815e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.380588322041696e-08</v>
+        <v>2.380588322041694e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>4.889152084600131e-08</v>
+        <v>4.889152084600141e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>4.100123875935529e-08</v>
+        <v>4.100123875935537e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.100123875935529e-08</v>
+        <v>4.100123875935537e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.608081743978801e-08</v>
+        <v>4.608081743978809e-08</v>
       </c>
       <c r="H9" t="n">
         <v>6.470933121428579e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.100123875935529e-08</v>
+        <v>4.100123875935537e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.091365036767833e-08</v>
+        <v>5.091365036767834e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.020534856588752e-07</v>
+        <v>1.020534856588754e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>5.654872961290168e-08</v>
+        <v>5.654872961290163e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2498,31 +2498,31 @@
         <v>1.311982352188964e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.230865380150212e-07</v>
+        <v>1.230865380150213e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>2.235559612580154e-06</v>
+        <v>2.235559612580159e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>2.311828981725902e-07</v>
+        <v>2.311828981725905e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.311828981725902e-07</v>
+        <v>2.311828981725905e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.157216196650617e-06</v>
+        <v>1.157216196650614e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.394780240715982e-07</v>
+        <v>4.394780240715979e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>2.311828981725902e-07</v>
+        <v>2.311828981725905e-07</v>
       </c>
       <c r="J2" t="n">
         <v>1.056842521608991e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>2.667731833987072e-07</v>
+        <v>2.667731833987068e-07</v>
       </c>
       <c r="L2" t="n">
         <v>4.338716358076107e-07</v>
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.305883975270706e-08</v>
+        <v>5.305883975270708e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.85386613630816e-08</v>
+        <v>4.853866136308164e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.305883975270706e-08</v>
+        <v>5.305883975270708e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.722898400648723e-08</v>
+        <v>4.722898400648715e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.722898400648718e-08</v>
+        <v>4.722898400648717e-08</v>
       </c>
       <c r="G3" t="n">
         <v>5.271714823305017e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.305883975270706e-08</v>
+        <v>5.305883975270708e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.076628194939307e-08</v>
+        <v>5.076628194939303e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.305883975270706e-08</v>
+        <v>5.305883975270708e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.305883975270706e-08</v>
+        <v>5.305883975270708e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.305883975270706e-08</v>
+        <v>5.305883975270708e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2575,34 +2575,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.839027683065684e-08</v>
+        <v>4.472431709766735e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.249299598364433e-08</v>
+        <v>4.249299598364427e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.780950908073067e-08</v>
+        <v>4.780950908073135e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.998555277193527e-08</v>
+        <v>3.99855527719354e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.233034998124396e-08</v>
+        <v>4.233034998124392e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>4.438262557801042e-08</v>
+        <v>4.438262557801038e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.743921735139269e-08</v>
+        <v>9.743921735139262e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>8.609771902734271e-08</v>
+        <v>4.243175929435328e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.070122302861092e-08</v>
+        <v>9.070122302861096e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.35006271482806e-08</v>
+        <v>4.350062714828057e-08</v>
       </c>
       <c r="L4" t="n">
         <v>4.480123692364424e-08</v>
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.831144195827666e-08</v>
+        <v>8.831144195827658e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.829081594302532e-08</v>
+        <v>8.829081594302524e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.830454230097965e-08</v>
+        <v>8.830454230097962e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.611419457427151e-08</v>
+        <v>8.611419457427136e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.611419457427151e-08</v>
+        <v>8.611419457427136e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.796975043861969e-08</v>
+        <v>8.796975043861963e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.831144195827666e-08</v>
+        <v>8.831144195827658e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.60188841549626e-08</v>
+        <v>8.601888415496253e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.831144195827666e-08</v>
+        <v>8.831144195827658e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.831144195827666e-08</v>
+        <v>8.831144195827658e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.831144195827666e-08</v>
+        <v>8.831144195827658e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.449877343828437e-07</v>
+        <v>1.449877343828438e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.211629995691125e-07</v>
+        <v>2.211629995691123e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.368443595965871e-07</v>
+        <v>2.368443595965868e-07</v>
       </c>
       <c r="E6" t="n">
         <v>1.980692988020612e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.451677930957156e-07</v>
+        <v>1.451677930957154e-07</v>
       </c>
       <c r="G6" t="n">
         <v>2.207268227466143e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.210685142665712e-07</v>
+        <v>2.21068514266571e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.187759564629572e-07</v>
+        <v>2.18775956462957e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.210834663145082e-07</v>
+        <v>2.210834663145081e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.435744948338364e-07</v>
+        <v>1.435744948338363e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.005412506279108e-07</v>
+        <v>3.005412506279103e-07</v>
       </c>
     </row>
     <row r="7">
@@ -2695,7 +2695,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.861893425490554e-07</v>
+        <v>1.861893425490555e-07</v>
       </c>
       <c r="C7" t="n">
         <v>2.306775780122039e-07</v>
@@ -2704,10 +2704,10 @@
         <v>2.306982865424793e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.797680236825568e-07</v>
+        <v>2.797680236825569e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.284056625927923e-07</v>
+        <v>2.284056625927921e-07</v>
       </c>
       <c r="G7" t="n">
         <v>2.303565125077983e-07</v>
@@ -2716,13 +2716,13 @@
         <v>2.306982040274551e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.284056462241412e-07</v>
+        <v>2.28405646224141e-07</v>
       </c>
       <c r="J7" t="n">
         <v>2.306982040274551e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.746535812363584e-07</v>
+        <v>1.746535812363585e-07</v>
       </c>
       <c r="L7" t="n">
         <v>2.306982040274551e-07</v>
@@ -2738,34 +2738,34 @@
         <v>9.649893865028326e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.431244566324229e-08</v>
+        <v>2.431244566324228e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.802998199430636e-08</v>
+        <v>1.802998199430641e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.935060622987181e-08</v>
+        <v>3.935060622987183e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.935060622987181e-08</v>
+        <v>3.935060622987183e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.931449686863262e-08</v>
+        <v>2.931449686863253e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>6.062614012199737e-08</v>
+        <v>6.062614012199734e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.935060622987182e-08</v>
+        <v>3.935060622987183e-08</v>
       </c>
       <c r="J8" t="n">
         <v>3.854231427555201e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.010132772526044e-07</v>
+        <v>1.01013277252604e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.21410905434994e-08</v>
+        <v>5.214109054349938e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.62127637198565e-08</v>
+        <v>9.621276371985651e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.499461585054237e-08</v>
+        <v>2.499461585054236e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>4.680695720247914e-08</v>
+        <v>4.680695720247915e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>4.104981472351881e-08</v>
+        <v>4.104981472351887e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.104981472351882e-08</v>
+        <v>4.104981472351887e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.310736852612992e-08</v>
+        <v>4.31073685261299e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.416214920275691e-08</v>
+        <v>6.416214920275692e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.104981472351882e-08</v>
+        <v>4.104981472351887e-08</v>
       </c>
       <c r="J9" t="n">
         <v>5.060043779594233e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.022220106524084e-07</v>
+        <v>1.02222010652408e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>5.564983825707917e-08</v>
+        <v>5.564983825707914e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2894,34 +2894,34 @@
         <v>1.023248337249541e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.100358726570034e-07</v>
+        <v>1.100358726570035e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.539709852106312e-07</v>
+        <v>1.539709852106311e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.901093754983884e-07</v>
+        <v>1.901093754983892e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.901093754983884e-07</v>
+        <v>1.901093754983892e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.791405198082804e-07</v>
+        <v>1.791405198082812e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.776064410510904e-07</v>
+        <v>1.776064410510907e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.901093754983884e-07</v>
+        <v>1.901093754983892e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>6.665907946515704e-07</v>
+        <v>6.665907946515702e-07</v>
       </c>
       <c r="K2" t="n">
         <v>1.298319342049669e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.968166064252029e-07</v>
+        <v>1.968166064252031e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.987711788079784e-08</v>
+        <v>4.98771178807979e-08</v>
       </c>
       <c r="C3" t="n">
         <v>4.747576497531779e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>4.987711788079784e-08</v>
+        <v>4.98771178807979e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.721357849295158e-08</v>
+        <v>4.721357849295155e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.721357849295163e-08</v>
+        <v>4.721357849295155e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>4.947042866104479e-08</v>
+        <v>4.947042866104474e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>4.987711788079784e-08</v>
+        <v>4.98771178807979e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.714111838987818e-08</v>
+        <v>4.714111838987814e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>4.987711788079784e-08</v>
+        <v>4.98771178807979e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>4.987711788079784e-08</v>
+        <v>4.98771178807979e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>4.987711788079784e-08</v>
+        <v>4.98771178807979e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.062790162026412e-08</v>
+        <v>4.062790162026408e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.990187300539378e-08</v>
+        <v>3.990187300539395e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>7.93518075743963e-08</v>
+        <v>4.073574294318836e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.706260743985758e-08</v>
+        <v>3.70626074398575e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.793832937205932e-08</v>
+        <v>3.793832937205925e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>4.022121240051107e-08</v>
+        <v>7.707331122695834e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.606383554601584e-08</v>
+        <v>8.606383554601589e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.789190212934451e-08</v>
+        <v>7.474400095579171e-08</v>
       </c>
       <c r="J4" t="n">
         <v>4.159186579318084e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.030518430816249e-08</v>
+        <v>4.030518430816244e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.063958370606582e-08</v>
+        <v>4.063958370606565e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.944158339081239e-08</v>
+        <v>7.944158339081233e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.946409599471037e-08</v>
+        <v>7.946409599471039e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.943507820906377e-08</v>
+        <v>7.943507820906379e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.684605723895671e-08</v>
+        <v>7.684605723895676e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.684605723895671e-08</v>
+        <v>7.684605723895676e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.903489417105931e-08</v>
+        <v>7.903489417105942e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.944158339081239e-08</v>
+        <v>7.944158339081233e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.670558389989272e-08</v>
+        <v>7.670558389989269e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.944158339081239e-08</v>
+        <v>7.944158339081233e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.944158339081239e-08</v>
+        <v>7.944158339081233e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.944158339081239e-08</v>
+        <v>7.944158339081233e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3054,25 +3054,25 @@
         <v>1.299678979123565e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.9696597789985e-07</v>
+        <v>1.969659778998497e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.10642968985424e-07</v>
+        <v>2.106429689854236e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.759143228404531e-07</v>
+        <v>1.759143228404527e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.294376561679358e-07</v>
+        <v>1.294376561679357e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.963808018369662e-07</v>
+        <v>1.963808018369659e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.967874910573533e-07</v>
+        <v>1.967874910573528e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.940514915657997e-07</v>
+        <v>1.94051491565799e-07</v>
       </c>
       <c r="J6" t="n">
         <v>1.96800623016759e-07</v>
@@ -3081,7 +3081,7 @@
         <v>1.287266896616744e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.665861434625295e-07</v>
+        <v>2.665861434625293e-07</v>
       </c>
     </row>
     <row r="7">
@@ -3091,34 +3091,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.465741113156578e-07</v>
+        <v>1.465741113156579e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.802725736276546e-07</v>
+        <v>1.802725736276548e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.802501095507091e-07</v>
+        <v>1.802501095507092e-07</v>
       </c>
       <c r="E7" t="n">
         <v>2.163754566132559e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.775140769691646e-07</v>
+        <v>1.775140769691647e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.798433718040035e-07</v>
+        <v>1.798433718040037e-07</v>
       </c>
       <c r="H7" t="n">
         <v>1.802500610237565e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.775140615328371e-07</v>
+        <v>1.77514061532837e-07</v>
       </c>
       <c r="J7" t="n">
         <v>1.802500610237565e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.607381039174711e-07</v>
+        <v>1.378460166283581e-07</v>
       </c>
       <c r="L7" t="n">
         <v>1.802500610237565e-07</v>
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.585942084726611e-08</v>
+        <v>9.585942084726628e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.259932102590838e-08</v>
+        <v>2.259932102590836e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>6.342495566467972e-08</v>
+        <v>6.342495566467967e-08</v>
       </c>
       <c r="E8" t="n">
         <v>3.805139830342903e-08</v>
@@ -3146,22 +3146,22 @@
         <v>3.805139830342903e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.799803515845462e-08</v>
+        <v>4.799803515845466e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>6.324746752957871e-08</v>
+        <v>6.324746752957879e-08</v>
       </c>
       <c r="I8" t="n">
         <v>3.805139830342903e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.260509289239972e-08</v>
+        <v>4.260509289239956e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.011858343440752e-07</v>
+        <v>1.011858343440756e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.374998403902572e-08</v>
+        <v>5.374998403902576e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.525862031810537e-08</v>
+        <v>9.525862031810542e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.320192422798025e-08</v>
+        <v>2.320192422798024e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>6.38286817496136e-08</v>
+        <v>6.382868174961357e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.936772627932289e-08</v>
+        <v>3.93677262793229e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.936772627932289e-08</v>
+        <v>3.93677262793229e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.894997529848858e-08</v>
+        <v>4.894997529848863e-08</v>
       </c>
       <c r="H9" t="n">
         <v>6.375880271968e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.936772627932289e-08</v>
+        <v>3.93677262793229e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.01105325636267e-08</v>
+        <v>5.011053256362656e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.006532513530792e-07</v>
+        <v>1.006532513530796e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>5.460831779931893e-08</v>
+        <v>5.460831779931896e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3290,34 +3290,34 @@
         <v>1.001830400408553e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.121555951281906e-07</v>
+        <v>1.12155595128191e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.513079827743599e-07</v>
+        <v>1.513079827743597e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.598512405416868e-07</v>
+        <v>1.598512405416855e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.598512405416868e-07</v>
+        <v>1.598512405416855e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.419087778284488e-07</v>
+        <v>1.419087778284487e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.63948282106356e-07</v>
+        <v>1.639482821063558e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.598512405416868e-07</v>
+        <v>1.598512405416855e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>4.932844787714132e-07</v>
+        <v>4.93284478771414e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.196361164240536e-07</v>
+        <v>1.196361164240533e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.655726388933617e-07</v>
+        <v>1.655726388933615e-07</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.067503295666494e-08</v>
+        <v>5.067503295666484e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.889338858515395e-08</v>
+        <v>4.889338858515399e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.067503295666494e-08</v>
+        <v>5.067503295666484e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.721677555659039e-08</v>
+        <v>4.72167755565902e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.721677555659038e-08</v>
+        <v>4.721677555659029e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.031086350306427e-08</v>
+        <v>5.031086350306755e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.067503295666494e-08</v>
+        <v>5.067503295666484e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.822288371028804e-08</v>
+        <v>4.822288371029189e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.067503295666494e-08</v>
+        <v>5.067503295666484e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.067503295666494e-08</v>
+        <v>5.067503295666484e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.067503295666494e-08</v>
+        <v>5.067503295666484e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.870311915163387e-08</v>
+        <v>7.870311915163403e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.094214461190443e-08</v>
+        <v>4.094214461190429e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.154955693188213e-08</v>
+        <v>4.154955693188221e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.813343318683272e-08</v>
+        <v>3.813343318683254e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.912320009626168e-08</v>
+        <v>3.912320009626155e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>7.833894969803326e-08</v>
+        <v>7.833894969803311e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.8260419856361e-08</v>
+        <v>8.826041985636093e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.909245579706115e-08</v>
+        <v>3.909245579706097e-08</v>
       </c>
       <c r="J4" t="n">
         <v>8.051882831397811e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.126873362224424e-08</v>
+        <v>4.126873362224433e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.154498536227758e-08</v>
+        <v>4.154498536227782e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.017906860262547e-08</v>
+        <v>8.017906860262544e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.020252729241386e-08</v>
+        <v>8.020252729241371e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.017254895498019e-08</v>
+        <v>8.017254895498008e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.784075377309771e-08</v>
+        <v>7.784075377309763e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.784075377309771e-08</v>
+        <v>7.784075377309763e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.98148991490248e-08</v>
+        <v>7.981489914902471e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.017906860262547e-08</v>
+        <v>8.017906860262544e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.772691935624853e-08</v>
+        <v>7.772691935624859e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.017906860262547e-08</v>
+        <v>8.017906860262544e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.017906860262547e-08</v>
+        <v>8.017906860262544e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.017906860262547e-08</v>
+        <v>8.017906860262544e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.30925145637732e-07</v>
+        <v>1.309251456377321e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.980535309040567e-07</v>
+        <v>1.980535309040561e-07</v>
       </c>
       <c r="D6" t="n">
         <v>2.117870461750662e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.772451119838024e-07</v>
+        <v>1.77245111983802e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.30667776459415e-07</v>
+        <v>1.306677764594149e-07</v>
       </c>
       <c r="G6" t="n">
         <v>1.975353119108923e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.978994813656173e-07</v>
+        <v>1.978994813656172e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.954473321181161e-07</v>
+        <v>1.954473321181159e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.979126437326007e-07</v>
+        <v>1.979126437326004e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.296810629638869e-07</v>
+        <v>1.296810629638868e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.678597753358448e-07</v>
+        <v>2.678597753358447e-07</v>
       </c>
     </row>
     <row r="7">
@@ -3496,28 +3496,28 @@
         <v>1.72004714442218e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.061741374759296e-07</v>
+        <v>2.061741374759294e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.695525328086008e-07</v>
+        <v>1.695525328086009e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.7164049752739e-07</v>
+        <v>1.716404975273899e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.720046669809907e-07</v>
+        <v>1.720046669809906e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.695525177346137e-07</v>
+        <v>1.695525177346142e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.720046669809907e-07</v>
+        <v>1.720046669809906e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.53617282781699e-07</v>
+        <v>1.528712814524274e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.720046669809907e-07</v>
+        <v>1.720046669809906e-07</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.722668310341755e-08</v>
+        <v>9.722668310341747e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.24341916646254e-08</v>
+        <v>2.243419166462538e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>6.33365071582384e-08</v>
+        <v>6.333650715823843e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.83059936422989e-08</v>
+        <v>3.830599364229887e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.83059936422989e-08</v>
+        <v>3.830599364229887e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.866277883544923e-08</v>
+        <v>4.866277883544917e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>6.338594527490611e-08</v>
+        <v>6.338594527490613e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.83059936422989e-08</v>
+        <v>3.830599364229887e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.540634966080825e-08</v>
+        <v>4.540634966080817e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.011185774782377e-07</v>
+        <v>1.011185774782375e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.422584840317502e-08</v>
+        <v>5.422584840317499e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.6565358217373e-08</v>
+        <v>9.656535821737293e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.305766025852526e-08</v>
+        <v>2.305766025852525e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>6.369345900896282e-08</v>
+        <v>6.369345900896276e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.91821153651354e-08</v>
+        <v>3.918211536513537e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.91821153651354e-08</v>
+        <v>3.918211536513537e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.908437344400044e-08</v>
+        <v>4.908437344400042e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.371572061594366e-08</v>
+        <v>6.371572061594362e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.91821153651354e-08</v>
+        <v>3.918211536513537e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.053962744647157e-08</v>
+        <v>5.053962744647149e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.004334612313292e-07</v>
+        <v>1.004334612313291e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>5.468658185766266e-08</v>
+        <v>5.46865818576626e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3683,13 +3683,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.227362748174472e-07</v>
+        <v>1.227362748174465e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.189065703227134e-07</v>
+        <v>1.189065703227136e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>4.266127296845136e-07</v>
+        <v>4.266127296845121e-07</v>
       </c>
       <c r="E2" t="n">
         <v>2.192598099246532e-07</v>
@@ -3698,22 +3698,22 @@
         <v>2.192598099246532e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>4.885836228001209e-07</v>
+        <v>4.885836228001161e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>3.823455434106082e-07</v>
+        <v>3.823455434106083e-07</v>
       </c>
       <c r="I2" t="n">
         <v>2.192598099246532e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>8.912787726321686e-07</v>
+        <v>8.912787726321676e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.727807752286673e-07</v>
+        <v>1.72780775228666e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>3.923162837531199e-07</v>
+        <v>3.923162837531182e-07</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.162290703509204e-08</v>
+        <v>5.162290703509128e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.760142708227325e-08</v>
+        <v>4.760142708227327e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.162290703509204e-08</v>
+        <v>5.162290703509128e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.643567113708028e-08</v>
+        <v>4.643567113708029e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.643567113708028e-08</v>
+        <v>4.643567113708029e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.130460981095134e-08</v>
+        <v>5.130460981095096e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.162290703509204e-08</v>
+        <v>5.162290703509128e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.947933372122844e-08</v>
+        <v>4.947933372122871e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.162290703509204e-08</v>
+        <v>5.162290703509128e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.162290703509204e-08</v>
+        <v>5.162290703509128e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.162290703509204e-08</v>
+        <v>5.162290703509128e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.266059435172274e-08</v>
+        <v>4.219656546407286e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.091750946320765e-08</v>
+        <v>4.091750946320807e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.251141582522721e-08</v>
+        <v>4.251141582522648e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.855915080071277e-08</v>
+        <v>3.855915080071287e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.005196759663769e-08</v>
+        <v>4.005196759663782e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.234229712758185e-08</v>
+        <v>8.234229712758095e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.150901290707577e-08</v>
+        <v>9.1509012907075e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.005299215021078e-08</v>
+        <v>8.051702103785938e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>8.467587427836681e-08</v>
+        <v>8.467587427836555e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.160170046737551e-08</v>
+        <v>4.16017004673744e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.226313257379023e-08</v>
+        <v>4.226313257378978e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.41650923115867e-08</v>
+        <v>8.416509231158649e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.417457625524414e-08</v>
+        <v>8.417457625524416e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.415820369501624e-08</v>
+        <v>8.415820369501564e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.214865515403495e-08</v>
+        <v>8.214865515403504e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.214865515403495e-08</v>
+        <v>8.214865515403504e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.384679508744595e-08</v>
+        <v>8.384679508744528e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.41650923115867e-08</v>
+        <v>8.416509231158649e-08</v>
       </c>
       <c r="I5" t="n">
         <v>8.202151899772349e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.41650923115867e-08</v>
+        <v>8.416509231158649e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.41650923115867e-08</v>
+        <v>8.416509231158649e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.41650923115867e-08</v>
+        <v>8.416509231158649e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.384813047414025e-07</v>
+        <v>1.384813047414017e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.10936211282832e-07</v>
+        <v>2.109362112828322e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.25773956284874e-07</v>
+        <v>2.257739562848737e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.889920791207441e-07</v>
+        <v>1.889920791207444e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.387095024312643e-07</v>
+        <v>1.387095024312647e-07</v>
       </c>
       <c r="G6" t="n">
         <v>2.104636498722205e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.107819470966558e-07</v>
+        <v>2.107819470966562e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.086383737824977e-07</v>
+        <v>2.086383737824985e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.107961562397697e-07</v>
+        <v>2.107961562397698e-07</v>
       </c>
       <c r="K6" t="n">
         <v>1.371382831876576e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.863060137200377e-07</v>
+        <v>2.863060137200385e-07</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.689979481507097e-07</v>
+        <v>1.689979481507089e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.089160171283162e-07</v>
+        <v>2.089160171283163e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.089065925898275e-07</v>
+        <v>2.089065925898271e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.528166928331357e-07</v>
+        <v>2.528166928331359e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.067629745354662e-07</v>
+        <v>2.067629745354665e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.085882359605178e-07</v>
+        <v>2.085882359605175e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.08906533184659e-07</v>
+        <v>2.089065331846588e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.067629598707954e-07</v>
+        <v>2.067629598707957e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.08906533184659e-07</v>
+        <v>2.089065331846588e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.84845228808168e-07</v>
+        <v>1.85783367268463e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.08906533184659e-07</v>
+        <v>2.089065331846588e-07</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.616960241481287e-08</v>
+        <v>9.616960241481242e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.344457726571737e-08</v>
+        <v>2.344457726571741e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.82385704038999e-08</v>
+        <v>5.82385704038997e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.839566365689291e-08</v>
+        <v>3.839566365689301e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.839566365689291e-08</v>
+        <v>3.839566365689301e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.239139521496798e-08</v>
+        <v>4.239139521496779e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>6.019617355133812e-08</v>
+        <v>6.019617355133787e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.83956636568929e-08</v>
+        <v>3.839566365689301e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>3.976471979067894e-08</v>
+        <v>3.976471979067908e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.014019123895944e-07</v>
+        <v>1.014019123895939e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.134448119477208e-08</v>
+        <v>5.134448119477186e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.577610190283961e-08</v>
+        <v>9.577610190283895e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.408952391925161e-08</v>
+        <v>2.408952391925167e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>6.226558081606829e-08</v>
+        <v>6.226558081606785e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.995999878226968e-08</v>
+        <v>3.995999878226978e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.995999878226968e-08</v>
+        <v>3.995999878226978e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.732671556716874e-08</v>
+        <v>4.732671556716866e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.30688831808294e-08</v>
+        <v>6.306888318082885e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.99599987822697e-08</v>
+        <v>3.995999878226978e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>4.970994537865929e-08</v>
+        <v>4.9709945378659e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.013606493365009e-07</v>
+        <v>1.013606493365008e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>5.438877760564947e-08</v>
+        <v>5.438877760564928e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.093762764317303e-07</v>
+        <v>1.093762764317298e-07</v>
       </c>
       <c r="C2" t="n">
         <v>1.122264383389446e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.53076738011378e-07</v>
+        <v>1.530767380113782e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.850240857529566e-07</v>
+        <v>1.850240857529553e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.850240857529566e-07</v>
+        <v>1.850240857529553e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.481893750036632e-07</v>
+        <v>1.481893750036602e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.691205143770054e-07</v>
+        <v>1.691205143770046e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.850240857529566e-07</v>
+        <v>1.850240857529553e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>6.795502139351482e-07</v>
+        <v>6.795502139351485e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.440315533290735e-07</v>
+        <v>1.440315533290708e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.781654125386869e-07</v>
+        <v>1.78165412538686e-07</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.978134825341904e-08</v>
+        <v>4.978134825341888e-08</v>
       </c>
       <c r="C3" t="n">
         <v>4.733596279418554e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>4.978134825341904e-08</v>
+        <v>4.978134825341888e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.721269247639692e-08</v>
+        <v>4.721269247639688e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.721269247639692e-08</v>
+        <v>4.72126924763969e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>4.937502790007022e-08</v>
+        <v>4.937502790006998e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>4.978134825341904e-08</v>
+        <v>4.978134825341888e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.704755612992637e-08</v>
+        <v>4.704755612992622e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>4.978134825341904e-08</v>
+        <v>4.978134825341888e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>4.978134825341904e-08</v>
+        <v>4.978134825341888e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>4.978134825341904e-08</v>
+        <v>4.978134825341888e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.741517145615381e-08</v>
+        <v>4.066996750756144e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.997422576561355e-08</v>
+        <v>3.997422576561396e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.081008803952125e-08</v>
+        <v>4.080982017738298e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.713038165965294e-08</v>
+        <v>3.713038165965293e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.798718982894462e-08</v>
+        <v>3.798718982894464e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>4.026364715421246e-08</v>
+        <v>4.026364715421253e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.595902130258782e-08</v>
+        <v>8.59590213025877e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.793617538406868e-08</v>
+        <v>7.468137933266104e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.163775017471702e-08</v>
+        <v>7.910152577038914e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.042712613728867e-08</v>
+        <v>4.04271261372886e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.067142741301292e-08</v>
+        <v>4.067142741301282e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.888489392929831e-08</v>
+        <v>7.888489392929806e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.890870269714247e-08</v>
+        <v>7.89087026971425e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.887841346041332e-08</v>
+        <v>7.887841346041328e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.631487917604331e-08</v>
+        <v>7.631487917604337e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.631487917604331e-08</v>
+        <v>7.631487917604337e-08</v>
       </c>
       <c r="G5" t="n">
         <v>7.847857357594919e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.888489392929831e-08</v>
+        <v>7.888489392929806e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.615110180580542e-08</v>
+        <v>7.615110180580554e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.888489392929831e-08</v>
+        <v>7.888489392929806e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.888489392929831e-08</v>
+        <v>7.888489392929806e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.888489392929831e-08</v>
+        <v>7.888489392929806e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.290261069888075e-07</v>
+        <v>1.290261069888072e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.954667253916936e-07</v>
+        <v>1.954667253916934e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.089998491826744e-07</v>
+        <v>2.089998491826738e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.745725213556118e-07</v>
+        <v>1.745725213556116e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.284935468666354e-07</v>
+        <v>1.28493546866635e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.948585000887316e-07</v>
+        <v>1.948585000887307e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.952648204426999e-07</v>
+        <v>1.952648204426993e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.925310283185877e-07</v>
+        <v>1.925310283185871e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.952778382413053e-07</v>
+        <v>1.952778382413049e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.277956888767241e-07</v>
+        <v>1.277956888767239e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.644566954369524e-07</v>
+        <v>2.644566954369518e-07</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.456249423522776e-07</v>
+        <v>1.456249423522774e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.790698314578055e-07</v>
+        <v>1.790698314578051e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.790460702009391e-07</v>
+        <v>1.790460702009387e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.148795111305621e-07</v>
+        <v>2.148795111305618e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.76312246203956e-07</v>
+        <v>1.763122462039557e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.786397023366122e-07</v>
+        <v>1.786397023366119e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.79046022689961e-07</v>
+        <v>1.790460226899606e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.763122305664682e-07</v>
+        <v>1.763122305664679e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.79046022689961e-07</v>
+        <v>1.790460226899606e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.369629045892561e-07</v>
+        <v>1.596817374705283e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.79046022689961e-07</v>
+        <v>1.790460226899606e-07</v>
       </c>
     </row>
     <row r="8">
@@ -4322,34 +4322,34 @@
         <v>1.027666620866105e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>2.286513726043568e-08</v>
+        <v>2.286513726043569e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>6.319000012985804e-08</v>
+        <v>6.319000012985813e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.813791832997743e-08</v>
+        <v>3.813791832997747e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.813791832997743e-08</v>
+        <v>3.813791832997747e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.932796598865921e-08</v>
+        <v>4.932796598865922e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>6.317347635835301e-08</v>
+        <v>6.317347635835305e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.813791832997743e-08</v>
+        <v>3.813791832997747e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.205267644276246e-08</v>
+        <v>4.205267644276228e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.013338560231964e-07</v>
+        <v>1.01333856023197e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.392130999471517e-08</v>
+        <v>5.392130999471515e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4359,13 +4359,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.021541023352769e-07</v>
+        <v>1.021541023352768e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>2.349373583166147e-08</v>
+        <v>2.349373583166148e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>6.358580650618849e-08</v>
+        <v>6.358580650618864e-08</v>
       </c>
       <c r="E9" t="n">
         <v>3.93831658276147e-08</v>
@@ -4374,22 +4374,22 @@
         <v>3.93831658276147e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.983694152669789e-08</v>
+        <v>4.983694152669785e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.358131975784355e-08</v>
+        <v>6.358131975784357e-08</v>
       </c>
       <c r="I9" t="n">
         <v>3.93831658276147e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>4.974105624047112e-08</v>
+        <v>4.974105624047118e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.009990495883462e-07</v>
+        <v>1.009990495883463e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>5.455051870662914e-08</v>
+        <v>5.455051870662913e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.04551759710255e-07</v>
+        <v>1.045517597102552e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.120880802422145e-07</v>
+        <v>1.120880802422143e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.486424718639444e-07</v>
+        <v>1.486424718639445e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.602233677194294e-07</v>
+        <v>1.602233677194293e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.602233677194294e-07</v>
+        <v>1.602233677194293e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.423011942901609e-07</v>
+        <v>1.423011942901592e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.64085702048891e-07</v>
+        <v>1.640857020488912e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.602233677194294e-07</v>
+        <v>1.602233677194293e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>4.977464822505849e-07</v>
+        <v>4.977464822505853e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.361668700297878e-07</v>
+        <v>1.361668700297879e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.660452078642487e-07</v>
+        <v>1.660452078642488e-07</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.067575311114637e-08</v>
+        <v>5.067575311114649e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.879059450894728e-08</v>
+        <v>4.879059450894712e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.067575311114637e-08</v>
+        <v>5.067575311114649e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.721612287098858e-08</v>
+        <v>4.721612287098866e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.721612287098855e-08</v>
+        <v>4.721612287098868e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.030978228397961e-08</v>
+        <v>5.030978228397973e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.067575311114637e-08</v>
+        <v>5.067575311114649e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.821173431145127e-08</v>
+        <v>4.821173431145134e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.067575311114637e-08</v>
+        <v>5.067575311114649e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.067575311114637e-08</v>
+        <v>5.067575311114649e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.067575311114637e-08</v>
+        <v>5.067575311114649e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.899880417969087e-08</v>
+        <v>4.174221718875864e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.111479249240728e-08</v>
+        <v>4.111479249240774e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.175387740247923e-08</v>
+        <v>4.175387740247925e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.829637599148658e-08</v>
+        <v>3.829637599148663e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.93085355673562e-08</v>
+        <v>3.930853556735617e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>7.863283335252409e-08</v>
+        <v>7.86328333525241e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.851252397581243e-08</v>
+        <v>8.85125239758125e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.927819838906345e-08</v>
+        <v>7.653478537999577e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>8.080716278664058e-08</v>
+        <v>4.267539711137778e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.151791359903885e-08</v>
+        <v>4.151791359903884e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.174337176085617e-08</v>
+        <v>4.174337176085572e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.982652642884778e-08</v>
+        <v>7.982652642884781e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.984950006813127e-08</v>
+        <v>7.984950006813114e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.982003811098102e-08</v>
+        <v>7.982003811098105e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.748134467696704e-08</v>
+        <v>7.748134467696708e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.748134467696704e-08</v>
+        <v>7.748134467696708e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.946055560168096e-08</v>
+        <v>7.946055560168091e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.982652642884778e-08</v>
+        <v>7.982652642884781e-08</v>
       </c>
       <c r="I5" t="n">
         <v>7.736250762915265e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.982652642884778e-08</v>
+        <v>7.982652642884781e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.982652642884778e-08</v>
+        <v>7.982652642884781e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.982652642884778e-08</v>
+        <v>7.982652642884781e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.303065004677607e-07</v>
+        <v>1.303065004677609e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.9704401031108e-07</v>
+        <v>1.970440103110802e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.106914369029926e-07</v>
+        <v>2.106914369029929e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.763317709836496e-07</v>
+        <v>1.763317709836501e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.300277049394183e-07</v>
+        <v>1.300277049394184e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.965198170975732e-07</v>
+        <v>1.965198170975734e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.968857879258505e-07</v>
+        <v>1.968857879258508e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.944217691250448e-07</v>
+        <v>1.944217691250449e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.968988726528565e-07</v>
+        <v>1.968988726528568e-07</v>
       </c>
       <c r="K6" t="n">
         <v>1.290697560184939e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.664334209433343e-07</v>
+        <v>2.664334209433346e-07</v>
       </c>
     </row>
     <row r="7">
@@ -4678,34 +4678,34 @@
         <v>1.400678749335833e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.717692304704787e-07</v>
+        <v>1.717692304704786e-07</v>
       </c>
       <c r="D7" t="n">
         <v>1.717463043056903e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.058384812692894e-07</v>
+        <v>2.058384812692892e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.69282253473261e-07</v>
+        <v>1.692822534732609e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.713802860040285e-07</v>
+        <v>1.713802860040283e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.717462568311954e-07</v>
+        <v>1.717462568311952e-07</v>
       </c>
       <c r="I7" t="n">
         <v>1.692822380315001e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.717462568311954e-07</v>
+        <v>1.717462568311952e-07</v>
       </c>
       <c r="K7" t="n">
         <v>1.526470283501596e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.717462568311954e-07</v>
+        <v>1.717462568311952e-07</v>
       </c>
     </row>
     <row r="8">
@@ -4715,13 +4715,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.226113046498165e-07</v>
+        <v>1.226113046498163e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>2.299365169181238e-08</v>
+        <v>2.299365169181235e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>6.326156558507476e-08</v>
+        <v>6.326156558507471e-08</v>
       </c>
       <c r="E8" t="n">
         <v>3.825720324387168e-08</v>
@@ -4730,22 +4730,22 @@
         <v>3.825720324387168e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.101129802349974e-08</v>
+        <v>5.101129802349965e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>6.324305549218823e-08</v>
+        <v>6.324305549218821e-08</v>
       </c>
       <c r="I8" t="n">
         <v>3.825720324387168e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.513781322319206e-08</v>
+        <v>4.513781322319213e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.010842988015424e-07</v>
+        <v>1.010842988015418e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.407516294090695e-08</v>
+        <v>5.407516294090691e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4755,10 +4755,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.216125130228672e-07</v>
+        <v>1.216125130228671e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>2.360740274912371e-08</v>
+        <v>2.360740274912364e-08</v>
       </c>
       <c r="D9" t="n">
         <v>6.35827620084384e-08</v>
@@ -4770,22 +4770,22 @@
         <v>3.914000670721945e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.140208459683699e-08</v>
+        <v>5.140208459683694e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.357735369441525e-08</v>
+        <v>6.357735369441529e-08</v>
       </c>
       <c r="I9" t="n">
         <v>3.914000670721945e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.03355696133107e-08</v>
+        <v>5.033556961331066e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.006321112781061e-07</v>
+        <v>1.006321112781055e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>5.454458947966182e-08</v>
+        <v>5.454458947966178e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.341837292572506e-07</v>
+        <v>3.341837292572497e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.743915809930678e-07</v>
+        <v>2.743915809930685e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>7.175064273197391e-06</v>
+        <v>7.175064273197396e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>2.743915809930678e-07</v>
+        <v>2.743915809930685e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.743915809930678e-07</v>
+        <v>2.743915809930685e-07</v>
       </c>
       <c r="G2" t="n">
         <v>3.744213244059109e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>7.398971486803637e-07</v>
+        <v>7.39897148680367e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>2.743915809930678e-07</v>
+        <v>2.743915809930685e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.051700586331191e-06</v>
+        <v>1.051700586331189e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.415060926222096e-07</v>
+        <v>5.415060926222118e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>4.824037088658697e-07</v>
+        <v>4.824037088658689e-07</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.708051490568681e-08</v>
+        <v>5.70805149056867e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.903636380012875e-08</v>
+        <v>4.903636380012859e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.708051490568681e-08</v>
+        <v>5.70805149056867e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.022531758062959e-08</v>
+        <v>5.022531758062952e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.022531758062959e-08</v>
+        <v>5.022531758062951e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.661627283992024e-08</v>
+        <v>5.661627283992012e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.708051490568681e-08</v>
+        <v>5.70805149056867e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.399408660719529e-08</v>
+        <v>5.39940866071953e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.708051490568681e-08</v>
+        <v>5.70805149056867e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.708051490568681e-08</v>
+        <v>5.70805149056867e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.708051490568681e-08</v>
+        <v>5.70805149056867e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.103134727460202e-07</v>
+        <v>1.103134727460201e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>4.54776458872285e-08</v>
+        <v>4.547764588722823e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.405640199333673e-08</v>
+        <v>6.405640199333379e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>4.489084153012547e-08</v>
+        <v>4.489084153012528e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.043407685297189e-08</v>
+        <v>5.043407685297167e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.357443976624422e-08</v>
+        <v>1.098492306802536e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>5.419329307989197e-08</v>
+        <v>1.154838216815642e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.072270444475289e-07</v>
+        <v>1.072270444475287e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.129297141988517e-07</v>
+        <v>1.129297141988516e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>5.011784770370838e-08</v>
+        <v>5.011784770370821e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.433090206823988e-08</v>
+        <v>5.433090206823977e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4994,25 +4994,25 @@
         <v>1.007369300270199e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>9.76505017285286e-08</v>
+        <v>9.765050172852845e-08</v>
       </c>
       <c r="D5" t="n">
         <v>1.00729319840299e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>9.75446561801645e-08</v>
+        <v>9.754465618016431e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>9.75446561801645e-08</v>
+        <v>9.754465618016431e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.002726879612533e-07</v>
+        <v>1.002726879612532e-07</v>
       </c>
       <c r="H5" t="n">
         <v>1.007369300270199e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>9.76505017285286e-08</v>
+        <v>9.765050172852845e-08</v>
       </c>
       <c r="J5" t="n">
         <v>1.007369300270199e-07</v>
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.633074026762554e-07</v>
+        <v>1.633074026762552e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.466642534666861e-07</v>
+        <v>2.466642534666864e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.677649908340922e-07</v>
+        <v>2.677649908340925e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.230080407234042e-07</v>
+        <v>2.230080407234046e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.629048465507621e-07</v>
+        <v>1.629048465507622e-07</v>
       </c>
       <c r="G6" t="n">
         <v>2.493607607660384e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.498250028317808e-07</v>
+        <v>2.498250028317815e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.467385745333135e-07</v>
+        <v>2.467385745333136e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.498420060106142e-07</v>
+        <v>2.498420060106144e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.617002938331745e-07</v>
+        <v>1.617002938331747e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.401998706750486e-07</v>
+        <v>3.40199870675049e-07</v>
       </c>
     </row>
     <row r="7">
@@ -5071,13 +5071,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.536637237231952e-07</v>
+        <v>2.536637237231949e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>3.132227195178388e-07</v>
+        <v>3.132227195178387e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>3.163093162580334e-07</v>
+        <v>3.163093162580335e-07</v>
       </c>
       <c r="E7" t="n">
         <v>3.855143860501478e-07</v>
@@ -5086,22 +5086,22 @@
         <v>3.132227380447554e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>3.158449057505636e-07</v>
+        <v>3.158449057505634e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>3.163091478163305e-07</v>
+        <v>3.163091478163303e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>3.132227195178388e-07</v>
+        <v>3.132227195178387e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>3.163091478163305e-07</v>
+        <v>3.163091478163303e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.800122139151259e-07</v>
+        <v>2.80012213915126e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>3.163091478163305e-07</v>
+        <v>3.163091478163303e-07</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.272022290944942e-08</v>
+        <v>6.272022290944938e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.579018799153187e-08</v>
+        <v>4.579018799153194e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>-9.567683112520678e-08</v>
+        <v>-9.567683112520695e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.579018799153187e-08</v>
+        <v>4.579018799153194e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>4.579018799153187e-08</v>
+        <v>4.579018799153194e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.493545116431371e-08</v>
+        <v>-1.493545116431358e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.52944865122388e-08</v>
+        <v>5.529448651223872e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.579018799153187e-08</v>
+        <v>4.579018799153194e-08</v>
       </c>
       <c r="J8" t="n">
         <v>4.756449117548124e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.800130741289502e-08</v>
+        <v>5.800130741289497e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.950427983914425e-08</v>
+        <v>6.038249559099624e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5154,34 +5154,34 @@
         <v>6.540964139405293e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>4.806410406091119e-08</v>
+        <v>4.806410406091122e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>8.99898461408706e-10</v>
+        <v>8.998984614086397e-10</v>
       </c>
       <c r="E9" t="n">
-        <v>4.806410406091119e-08</v>
+        <v>4.806410406091122e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.806410406091119e-08</v>
+        <v>4.806410406091122e-08</v>
       </c>
       <c r="G9" t="n">
         <v>3.334318229953849e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.239796835809118e-08</v>
+        <v>6.239796835809114e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.806410406091119e-08</v>
+        <v>4.806410406091122e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.924499551473503e-08</v>
+        <v>5.924499551473505e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.348824040150723e-08</v>
+        <v>6.348824040150716e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.004165672374659e-08</v>
+        <v>6.446395006275785e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.354753810628179e-07</v>
+        <v>2.354753810628174e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.636150955602721e-07</v>
+        <v>2.636150955602728e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>6.094988997790074e-06</v>
+        <v>6.094988997790051e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>2.636150955602721e-07</v>
+        <v>2.636150955602728e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.636150955602721e-07</v>
+        <v>2.636150955602728e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>3.360796403415839e-06</v>
+        <v>3.360796403415842e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>6.272739429722347e-07</v>
+        <v>6.27273942972235e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>2.636150955602721e-07</v>
+        <v>2.636150955602728e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>7.957293993714314e-07</v>
+        <v>7.95729399371431e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>4.778667664144546e-07</v>
+        <v>4.778667664144548e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>9.493593918736511e-07</v>
+        <v>5.516244298327436e-07</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.473054962707777e-08</v>
+        <v>5.473054962707765e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.84232510280661e-08</v>
+        <v>4.842325102806611e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.473054962707777e-08</v>
+        <v>5.473054962707766e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.945814139428704e-08</v>
+        <v>4.9458141394287e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.945814139428707e-08</v>
+        <v>4.945814139428701e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.429761458391029e-08</v>
+        <v>5.429761458391017e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.473054962707777e-08</v>
+        <v>5.473054962707766e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.185154927503727e-08</v>
+        <v>5.185154927503719e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.473054962707777e-08</v>
+        <v>5.473054962707766e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.473054962707777e-08</v>
+        <v>5.473054962707766e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.473054962707777e-08</v>
+        <v>5.473054962707766e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.197927044348805e-08</v>
+        <v>1.040590941199275e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>4.422501505293206e-08</v>
+        <v>4.422501505293198e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.039905003636659e-08</v>
+        <v>6.039905003636292e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>4.365682386554448e-08</v>
+        <v>4.36568238655445e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.860437185249974e-08</v>
+        <v>4.860437185249967e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.154633540032054e-08</v>
+        <v>1.036261590767602e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.084187021655169e-07</v>
+        <v>1.084187021655168e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>4.910027009144745e-08</v>
+        <v>1.011800937678873e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>5.338428836708941e-08</v>
+        <v>1.063586480080209e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>4.836207657252307e-08</v>
+        <v>4.836207657252293e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.23287181588192e-08</v>
+        <v>5.232871815881928e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.425358606502054e-08</v>
+        <v>9.425358606502051e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>9.137458571298002e-08</v>
+        <v>9.137458571297996e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>9.424648871445405e-08</v>
+        <v>9.424648871445406e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>9.125525782474419e-08</v>
+        <v>9.125525782474424e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>9.125525782474419e-08</v>
+        <v>9.125525782474424e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>9.382065102185313e-08</v>
+        <v>9.382065102185299e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>9.425358606502054e-08</v>
+        <v>9.425358606502051e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>9.137458571298002e-08</v>
+        <v>9.137458571297996e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>9.425358606502054e-08</v>
+        <v>9.425358606502051e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>9.425358606502054e-08</v>
+        <v>9.425358606502051e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>9.425358606502054e-08</v>
+        <v>9.425358606502051e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.514803356863422e-07</v>
+        <v>1.514803356863417e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.275099288335355e-07</v>
+        <v>2.275099288354525e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.468590379723543e-07</v>
+        <v>2.468590379723539e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.05912030225549e-07</v>
+        <v>2.059120302255489e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.51038497741877e-07</v>
+        <v>1.510384977418768e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.30045361186542e-07</v>
+        <v>2.300453611865416e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.30478296229665e-07</v>
+        <v>2.304782962296643e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.27599295877669e-07</v>
+        <v>2.275992958776688e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.304938215827443e-07</v>
+        <v>2.304938215827436e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.500129080099901e-07</v>
+        <v>1.500129080099898e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.129982717144953e-07</v>
+        <v>3.129982717144946e-07</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.195913864167199e-07</v>
+        <v>2.195913864167196e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.699328323344834e-07</v>
+        <v>2.699328323344828e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.728119866215755e-07</v>
+        <v>2.728119866215754e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>3.313482604411777e-07</v>
+        <v>3.31348260441177e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.699328502649229e-07</v>
+        <v>2.699328502649223e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.72378897643356e-07</v>
+        <v>2.723788976433559e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.72811832686524e-07</v>
+        <v>2.728118326865235e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.699328323344834e-07</v>
+        <v>2.699328323344828e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.72811832686524e-07</v>
+        <v>2.728118326865235e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.057977511201263e-07</v>
+        <v>2.05797751120126e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.72811832686524e-07</v>
+        <v>2.728118326865235e-07</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.398976362672651e-08</v>
+        <v>6.398976362672655e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.493597626678507e-08</v>
+        <v>4.49359762667851e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>-8.425606442271914e-08</v>
+        <v>-8.425606442271888e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.493597626678507e-08</v>
+        <v>4.49359762667851e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>4.493597626678507e-08</v>
+        <v>4.49359762667851e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.354038242147009e-08</v>
+        <v>-1.354038242147001e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.600437404402961e-08</v>
+        <v>5.600437404402968e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.493597626678507e-08</v>
+        <v>4.49359762667851e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.120062542061674e-08</v>
+        <v>5.120062542061675e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.755088608411512e-08</v>
+        <v>5.755088608411515e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.973432290670828e-08</v>
+        <v>5.740805446559483e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5547,34 +5547,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.552496952103546e-08</v>
+        <v>6.552496952103552e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>4.734311947730593e-08</v>
+        <v>4.734311947730594e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.149434993529895e-09</v>
+        <v>5.14943499353018e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>4.734311947730593e-08</v>
+        <v>4.734311947730594e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.734311947730593e-08</v>
+        <v>4.734311947730594e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.352308853628751e-08</v>
+        <v>3.352308853628755e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.228404789824512e-08</v>
+        <v>6.228404789824516e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.734311947730593e-08</v>
+        <v>4.734311947730594e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>6.032257072354236e-08</v>
+        <v>6.032257072354243e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.290302611981454e-08</v>
+        <v>6.290302611981451e-08</v>
       </c>
       <c r="L9" t="n">
         <v>6.285243483162715e-08</v>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.123997817056831e-07</v>
+        <v>2.123997817056794e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.951342442699996e-07</v>
+        <v>2.951342442699962e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>5.01167127564151e-06</v>
+        <v>5.011671275641505e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>2.951342442699996e-07</v>
+        <v>2.951342442699962e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.951342442699996e-07</v>
+        <v>2.951342442699962e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>2.871572986309951e-06</v>
+        <v>2.871572986309942e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>5.97632385423175e-07</v>
+        <v>5.97632385423179e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>2.951342442699996e-07</v>
+        <v>2.951342442699962e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>5.019149751398631e-07</v>
+        <v>5.019149751398596e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>4.103965068834952e-07</v>
+        <v>4.103965068834885e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>8.303754349828108e-07</v>
+        <v>8.303754349828152e-07</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.415721722656032e-08</v>
+        <v>5.415721722655998e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.905293511181099e-08</v>
+        <v>4.905293511181081e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.415721722656032e-08</v>
+        <v>5.415721722656e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.003038269914348e-08</v>
+        <v>5.003038269914338e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.003038269914351e-08</v>
+        <v>5.003038269914335e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.375900618144078e-08</v>
+        <v>5.37590061814407e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.415721722656032e-08</v>
+        <v>5.415721722656e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.15046600823819e-08</v>
+        <v>5.150466008238172e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.415721722656032e-08</v>
+        <v>5.415721722656e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.415721722656032e-08</v>
+        <v>5.415721722656e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.415721722656032e-08</v>
+        <v>5.415721722656e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5743,34 +5743,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.075332001722471e-08</v>
+        <v>5.075332001722495e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.397631622250575e-08</v>
+        <v>4.397631622250545e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.03495824032593e-07</v>
+        <v>1.034958240325928e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>4.341885110673838e-08</v>
+        <v>4.341885110673814e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.770655143440908e-08</v>
+        <v>4.770655143440894e-08</v>
       </c>
       <c r="G4" t="n">
         <v>5.03551089721058e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.048513251119232e-07</v>
+        <v>1.048513251119226e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>9.802025251807362e-08</v>
+        <v>9.80202525180735e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>1.027325433580552e-07</v>
+        <v>5.202475565891793e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.754328966723229e-08</v>
+        <v>4.75432896672322e-08</v>
       </c>
       <c r="L4" t="n">
         <v>5.091773832542264e-08</v>
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.2164132640397e-08</v>
+        <v>9.216413264039703e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.951157549621895e-08</v>
+        <v>8.951157549621868e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>9.215703966352152e-08</v>
+        <v>9.215703966352123e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.939523896342289e-08</v>
+        <v>8.939523896342277e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.939523896342289e-08</v>
+        <v>8.939523896342277e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>9.176592159527781e-08</v>
+        <v>9.176592159527749e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>9.2164132640397e-08</v>
+        <v>9.216413264039698e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.951157549621895e-08</v>
+        <v>8.951157549621868e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>9.2164132640397e-08</v>
+        <v>9.216413264039698e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>9.2164132640397e-08</v>
+        <v>9.216413264039698e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>9.2164132640397e-08</v>
+        <v>9.216413264039698e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5826,34 +5826,34 @@
         <v>1.476085115512156e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.214630237697729e-07</v>
+        <v>2.214630237697722e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.400848302645745e-07</v>
+        <v>2.400848302645739e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.005223130278398e-07</v>
+        <v>2.005223130278394e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.473186982708331e-07</v>
+        <v>1.473186982708327e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.238043451074762e-07</v>
+        <v>2.238043451074757e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.242025561525486e-07</v>
+        <v>2.24202556152548e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.215499990084173e-07</v>
+        <v>2.215499990084168e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.242176090670752e-07</v>
+        <v>2.242176090670749e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.461857378476605e-07</v>
+        <v>1.461857378476603e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.042114404236286e-07</v>
+        <v>3.042114404236275e-07</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.993082033744454e-07</v>
+        <v>1.993082033744453e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.442911509677189e-07</v>
+        <v>2.442911509677187e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.469438459924833e-07</v>
+        <v>2.469438459924834e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.992616588566091e-07</v>
+        <v>2.992616588566088e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.442911676209883e-07</v>
+        <v>2.442911676209878e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.465454970667778e-07</v>
+        <v>2.465454970667785e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.469437081118969e-07</v>
+        <v>2.469437081118971e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.442911509677189e-07</v>
+        <v>2.442911509677187e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.469437081118969e-07</v>
+        <v>2.469437081118971e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.19343567579992e-07</v>
+        <v>2.193435675799921e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.469437081118969e-07</v>
+        <v>2.469437081118971e-07</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.283252782029416e-08</v>
+        <v>6.283252782029422e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.268311924754117e-08</v>
+        <v>4.268311924754129e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>-6.318426971460047e-08</v>
+        <v>-6.318426971460051e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.268311924754117e-08</v>
+        <v>4.268311924754129e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>4.268311924754117e-08</v>
+        <v>4.268311924754129e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.922168432349315e-09</v>
+        <v>-4.9221684323496e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>5.457292522066061e-08</v>
+        <v>5.457292522066069e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.268311924754117e-08</v>
+        <v>4.268311924754129e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.632120025520531e-08</v>
+        <v>5.63212002552054e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.722323588051578e-08</v>
+        <v>5.7223235880516e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.029338008965594e-08</v>
+        <v>5.02933800896561e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.40591429599856e-08</v>
+        <v>6.405914295998572e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>4.565828620378299e-08</v>
+        <v>4.565828620378292e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.273674679074039e-08</v>
+        <v>1.273674679074043e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>4.565828620378299e-08</v>
+        <v>4.565828620378292e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.565828620378299e-08</v>
+        <v>4.565828620378292e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.608724314893659e-08</v>
+        <v>3.608724314893656e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.070627761051534e-08</v>
+        <v>6.070627761051536e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.565828620378299e-08</v>
+        <v>4.565828620378292e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>6.141105078944311e-08</v>
+        <v>6.141105078944317e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.177501140987308e-08</v>
+        <v>6.177501140987312e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>5.89643959988618e-08</v>
+        <v>5.896439599886197e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6062,34 +6062,34 @@
         <v>2.23640750468628e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.043781854830419e-07</v>
+        <v>2.043781854830418e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.733232771032255e-06</v>
+        <v>1.733232771032254e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>2.043781854830419e-07</v>
+        <v>2.043781854830418e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.043781854830419e-07</v>
+        <v>2.043781854830418e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>9.731014902652528e-07</v>
+        <v>9.731014902652523e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>3.780542697514781e-07</v>
+        <v>3.780542697514775e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>2.043781854830419e-07</v>
+        <v>2.043781854830418e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>4.255508539246245e-07</v>
+        <v>4.255508539246236e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>3.767306759699553e-07</v>
+        <v>3.767306759699546e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>7.127120525413886e-07</v>
+        <v>3.25486433262449e-06</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.130304696422694e-08</v>
+        <v>5.130304696422668e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.585095511957503e-08</v>
+        <v>4.585095511957498e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.130304696422694e-08</v>
+        <v>5.130304696422668e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.685840397788114e-08</v>
+        <v>4.68584039778811e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.685840397788112e-08</v>
+        <v>4.685840397788109e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.093231664332308e-08</v>
+        <v>5.093231664332294e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.130304696422694e-08</v>
+        <v>5.130304696422668e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.881222704817553e-08</v>
+        <v>4.881222704817552e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.130304696422694e-08</v>
+        <v>5.130304696422668e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.130304696422694e-08</v>
+        <v>5.130304696422668e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.130304696422694e-08</v>
+        <v>5.130304696422668e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.351597415419491e-08</v>
+        <v>4.351597415419478e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.923139320590162e-08</v>
+        <v>3.923139320590176e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.613492311033092e-08</v>
+        <v>8.892156884114624e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.880335000359876e-08</v>
+        <v>3.880335000359864e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.085054759164498e-08</v>
+        <v>4.085054759164495e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.673163783514892e-08</v>
+        <v>4.314524383329094e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.16291803376063e-08</v>
+        <v>9.162918033760588e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>8.461154824000144e-08</v>
+        <v>4.102515423814365e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>8.853869022554303e-08</v>
+        <v>8.853869022554285e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.262116281607968e-08</v>
+        <v>4.262116281607957e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.446523389828728e-08</v>
+        <v>4.446523389828706e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.38537714342072e-08</v>
+        <v>8.385377143420712e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.136295151815601e-08</v>
+        <v>8.136295151815603e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.3846197634409e-08</v>
+        <v>8.384619763440884e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.132834271317386e-08</v>
+        <v>8.132834271317385e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.132834271317386e-08</v>
+        <v>8.132834271317385e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.348304111330352e-08</v>
+        <v>8.348304111330331e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.38537714342072e-08</v>
+        <v>8.385377143420712e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.136295151815601e-08</v>
+        <v>8.136295151815603e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.38537714342072e-08</v>
+        <v>8.385377143420712e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.38537714342072e-08</v>
+        <v>8.385377143420712e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.38537714342072e-08</v>
+        <v>8.385377143420712e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6222,25 +6222,25 @@
         <v>1.367373478013124e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.052718618130237e-07</v>
+        <v>2.052718618109942e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.225014384216044e-07</v>
+        <v>2.225014384216045e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.858431939217617e-07</v>
+        <v>1.85843193921762e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.364820874203522e-07</v>
+        <v>1.364820874203524e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.074012204310448e-07</v>
+        <v>2.074012204310451e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.077719507519374e-07</v>
+        <v>2.077719507519376e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.052811308358974e-07</v>
+        <v>2.052811308358977e-07</v>
       </c>
       <c r="J6" t="n">
         <v>2.0778591108219e-07</v>
@@ -6249,7 +6249,7 @@
         <v>1.354178435798747e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.819735333514087e-07</v>
+        <v>2.819735333514089e-07</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.833270832990445e-07</v>
+        <v>1.833270832990441e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.246388834142855e-07</v>
+        <v>2.246388834142853e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.271297747992274e-07</v>
+        <v>2.271297747992273e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.751862565319653e-07</v>
+        <v>2.751862565319652e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.246388944229047e-07</v>
+        <v>2.246388944229046e-07</v>
       </c>
       <c r="G7" t="n">
         <v>2.267589730094326e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.271297033303366e-07</v>
+        <v>2.271297033303364e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.246388834142855e-07</v>
+        <v>2.246388834142853e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.271297033303366e-07</v>
+        <v>2.271297033303364e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.719743674477211e-07</v>
+        <v>2.017503233175793e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.271297033303366e-07</v>
+        <v>2.271297033303364e-07</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.636847184636545e-08</v>
+        <v>5.636847184636537e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.115960522503641e-08</v>
+        <v>4.115960522503642e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.744414188569648e-08</v>
+        <v>1.744414188569634e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.115960522503641e-08</v>
+        <v>4.115960522503642e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>4.115960522503641e-08</v>
+        <v>4.115960522503642e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.804337693440966e-08</v>
+        <v>3.804337693440954e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.338872800745627e-08</v>
+        <v>5.338872800745621e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.115960522503641e-08</v>
+        <v>4.115960522503642e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.225775348638816e-08</v>
+        <v>5.225775348638804e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.253730930285869e-08</v>
+        <v>5.253730930285859e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.159406390670965e-09</v>
+        <v>4.659008212969133e-08</v>
       </c>
     </row>
     <row r="9">
@@ -6339,13 +6339,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.771396691783787e-08</v>
+        <v>5.771396691783773e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>4.266601772213392e-08</v>
+        <v>4.26660177221339e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>4.18614711461704e-08</v>
+        <v>4.186147114617028e-08</v>
       </c>
       <c r="E9" t="n">
         <v>4.266601772213392e-08</v>
@@ -6354,22 +6354,22 @@
         <v>4.266601772213392e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.00617825052643e-08</v>
+        <v>5.006178250526422e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.650673982662642e-08</v>
+        <v>5.65067398266263e-08</v>
       </c>
       <c r="I9" t="n">
         <v>4.266601772213392e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.604275308502223e-08</v>
+        <v>5.604275308502211e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>5.615396781900251e-08</v>
+        <v>5.615396781900236e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>5.374149960912004e-08</v>
+        <v>3.270361249865413e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.738051003272915e-07</v>
+        <v>2.738051003272916e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.600714768771023e-07</v>
+        <v>2.600714768771022e-07</v>
       </c>
       <c r="D2" t="n">
         <v>3.281462800268663e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>2.600714768771023e-07</v>
+        <v>2.600714768771022e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.600714768771023e-07</v>
+        <v>2.600714768771022e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>3.510480031175248e-07</v>
+        <v>3.51048003117521e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>2.132504707786717e-07</v>
+        <v>2.132504707786718e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>2.600714768771023e-07</v>
+        <v>2.600714768771022e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>5.455443963966093e-07</v>
+        <v>5.455443963966087e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>4.236142788337387e-07</v>
+        <v>4.236142788337393e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>2.937927886613285e-07</v>
+        <v>2.937927886613286e-07</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.833834699930851e-08</v>
+        <v>4.833834699930862e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.517157828980064e-08</v>
+        <v>4.517157828980058e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>4.833834699930851e-08</v>
+        <v>4.833834699930862e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.597479132205105e-08</v>
+        <v>4.597479132205102e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.597479132205105e-08</v>
+        <v>4.597479132205106e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>4.802031741401063e-08</v>
+        <v>4.802031741401052e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>4.833834699930851e-08</v>
+        <v>4.833834699930862e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.619108010696147e-08</v>
+        <v>4.61910801069614e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>4.833834699930851e-08</v>
+        <v>4.833834699930862e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>4.833834699930851e-08</v>
+        <v>4.833834699930862e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>4.833834699930851e-08</v>
+        <v>4.833834699930862e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.049824889457965e-08</v>
+        <v>7.71676830134956e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.776628916047664e-08</v>
+        <v>3.776628916047658e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.070274728317749e-08</v>
+        <v>4.070256630779355e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.734492037933366e-08</v>
+        <v>3.734492037933362e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.830963655977412e-08</v>
+        <v>3.830963655977414e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>4.018021930928163e-08</v>
+        <v>4.018021930928171e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.072628283995928e-08</v>
+        <v>4.044978896662072e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.835098200223257e-08</v>
+        <v>3.835098200223246e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.135448085457843e-08</v>
+        <v>7.8031330559898e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.049665620774803e-08</v>
+        <v>4.049665620774818e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.059758362576478e-08</v>
+        <v>4.059758362576483e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.575248338972233e-08</v>
+        <v>7.575248338972235e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.360521649737529e-08</v>
+        <v>7.360521649737522e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.574538270686555e-08</v>
+        <v>7.574538270686549e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.359083262330297e-08</v>
+        <v>7.359083262330293e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.359083262330297e-08</v>
+        <v>7.359083262330293e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.543445380442432e-08</v>
+        <v>7.543445380442439e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.575248338972233e-08</v>
+        <v>7.575248338972235e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.360521649737529e-08</v>
+        <v>7.360521649737522e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.575248338972233e-08</v>
+        <v>7.575248338972235e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.575248338972233e-08</v>
+        <v>7.575248338972235e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.575248338972233e-08</v>
+        <v>7.575248338972235e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.223430046070687e-07</v>
+        <v>1.223430046070688e-07</v>
       </c>
       <c r="C6" t="n">
         <v>1.822206866593779e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.972199690137143e-07</v>
+        <v>1.972199690137141e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.652565329210215e-07</v>
+        <v>1.652565329210214e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.221572448828966e-07</v>
+        <v>1.221572448828965e-07</v>
       </c>
       <c r="G6" t="n">
         <v>1.84042252862671e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.843602824479593e-07</v>
+        <v>1.843602824479592e-07</v>
       </c>
       <c r="I6" t="n">
         <v>1.822130155556217e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.84372470616595e-07</v>
+        <v>1.843724706165949e-07</v>
       </c>
       <c r="K6" t="n">
         <v>1.211910018291592e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.491425149545223e-07</v>
+        <v>2.491425149545219e-07</v>
       </c>
     </row>
     <row r="7">
@@ -6655,16 +6655,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.491348919582106e-07</v>
+        <v>1.491348919582104e-07</v>
       </c>
       <c r="C7" t="n">
         <v>1.813902492954938e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.835375652141607e-07</v>
+        <v>1.835375652141604e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.210902096991443e-07</v>
+        <v>2.21090209699144e-07</v>
       </c>
       <c r="F7" t="n">
         <v>1.813902630373861e-07</v>
@@ -6673,19 +6673,19 @@
         <v>1.832194866025428e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.835375161878408e-07</v>
+        <v>1.835375161878405e-07</v>
       </c>
       <c r="I7" t="n">
         <v>1.813902492954938e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.835375161878408e-07</v>
+        <v>1.835375161878405e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.627958124458903e-07</v>
+        <v>1.627958124458901e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.835375161878408e-07</v>
+        <v>1.835375161878405e-07</v>
       </c>
     </row>
     <row r="8">
@@ -6695,13 +6695,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.268097816033348e-08</v>
+        <v>5.268097816033346e-08</v>
       </c>
       <c r="C8" t="n">
         <v>3.78802958484329e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.081796064600653e-08</v>
+        <v>5.081796064600655e-08</v>
       </c>
       <c r="E8" t="n">
         <v>3.78802958484329e-08</v>
@@ -6713,7 +6713,7 @@
         <v>5.033720995863938e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.459578743348108e-08</v>
+        <v>5.459578743348112e-08</v>
       </c>
       <c r="I8" t="n">
         <v>3.78802958484329e-08</v>
@@ -6722,10 +6722,10 @@
         <v>4.61497000437508e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.841670897451186e-08</v>
+        <v>4.841670897451185e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.610154545660765e-08</v>
+        <v>5.610154545660769e-08</v>
       </c>
     </row>
     <row r="9">
@@ -6735,13 +6735,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.502538052657485e-08</v>
+        <v>5.502538052657481e-08</v>
       </c>
       <c r="C9" t="n">
         <v>4.056946185924328e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.426678223586413e-08</v>
+        <v>5.426678223586415e-08</v>
       </c>
       <c r="E9" t="n">
         <v>4.056946185924328e-08</v>
@@ -6750,22 +6750,22 @@
         <v>4.056946185924328e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.395437160877899e-08</v>
+        <v>5.395437160877895e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.580865677079819e-08</v>
+        <v>5.580865677079821e-08</v>
       </c>
       <c r="I9" t="n">
         <v>4.056946185924328e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.236984265090152e-08</v>
+        <v>5.236984265090155e-08</v>
       </c>
       <c r="K9" t="n">
         <v>5.328909026198596e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>5.502717635913874e-08</v>
+        <v>5.642016973387483e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.899632162372708e-07</v>
+        <v>3.899632162372701e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>4.702013376485047e-07</v>
+        <v>4.702013376485056e-07</v>
       </c>
       <c r="D2" t="n">
         <v>2.467482580094149e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>4.702013376485047e-07</v>
+        <v>4.702013376485056e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>4.702013376485047e-07</v>
+        <v>4.702013376485056e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>3.120076437273582e-07</v>
+        <v>3.120076437273619e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>2.008481128580151e-07</v>
+        <v>2.008481128580155e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>4.702013376485047e-07</v>
+        <v>4.702013376485056e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>6.514204025428526e-07</v>
+        <v>6.514204025428518e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>3.506531682883771e-07</v>
+        <v>3.50653168288378e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>3.227731686162928e-07</v>
+        <v>2.057659720823207e-07</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.921767146142109e-08</v>
+        <v>4.921767146142076e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.713042368886887e-08</v>
+        <v>4.713042368886893e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>4.921767146142109e-08</v>
+        <v>4.921767146142076e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.788467649190277e-08</v>
+        <v>4.788467649190289e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.788467649190279e-08</v>
+        <v>4.788467649190286e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>4.892655464672873e-08</v>
+        <v>4.892655464672947e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>4.921767146142109e-08</v>
+        <v>4.921767146142076e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.724697550851787e-08</v>
+        <v>4.724697550851801e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>4.921767146142109e-08</v>
+        <v>4.921767146142076e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>4.921767146142109e-08</v>
+        <v>4.921767146142076e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>4.921767146142109e-08</v>
+        <v>4.921767146142076e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.186308100518675e-08</v>
+        <v>4.186308100518541e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.982474911003942e-08</v>
+        <v>3.982474911003985e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>7.898405511734395e-08</v>
+        <v>4.1654299735257e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.935781367178316e-08</v>
+        <v>3.935781367178314e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.992534752121796e-08</v>
+        <v>3.992534752121809e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>4.157196419049336e-08</v>
+        <v>7.787850968201744e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.153932102630637e-08</v>
+        <v>8.1539321026307e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.989238505228263e-08</v>
+        <v>3.989238505228284e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.272956103155758e-08</v>
+        <v>7.887705533406101e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.165659449547944e-08</v>
+        <v>4.165659449547838e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.176225137432853e-08</v>
+        <v>4.176225137432861e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.660260631286028e-08</v>
+        <v>7.660260631286164e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.463191035995864e-08</v>
+        <v>7.463191035995882e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.659546641002565e-08</v>
+        <v>7.659546641002586e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.462814655832685e-08</v>
+        <v>7.462814655832702e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.462814655832685e-08</v>
+        <v>7.462814655832702e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.631148949817082e-08</v>
+        <v>7.631148949817032e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.660260631286028e-08</v>
+        <v>7.660260631286164e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.463191035995864e-08</v>
+        <v>7.463191035995882e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.660260631286028e-08</v>
+        <v>7.660260631286164e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.660260631286028e-08</v>
+        <v>7.660260631286164e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.660260631286028e-08</v>
+        <v>7.660260631286164e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.228490731394901e-07</v>
+        <v>1.228490731394895e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.826539214908237e-07</v>
+        <v>1.826539214926969e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.97412654035761e-07</v>
+        <v>1.974126540357607e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.657596641178407e-07</v>
+        <v>1.657596641178409e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.228380154349694e-07</v>
+        <v>1.228380154349696e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.843156724648792e-07</v>
+        <v>1.843156724648783e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.846067892795646e-07</v>
+        <v>1.846067892795648e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.826360933266664e-07</v>
+        <v>1.826360933266668e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.846189264368182e-07</v>
+        <v>1.846189264368162e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.217018918534168e-07</v>
+        <v>1.217018918534156e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.491178878853925e-07</v>
+        <v>2.49117887885392e-07</v>
       </c>
     </row>
     <row r="7">
@@ -7054,34 +7054,34 @@
         <v>1.443305657907741e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.751809057204277e-07</v>
+        <v>1.75180905720428e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.771516472794794e-07</v>
+        <v>1.771516472794796e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.130557453459689e-07</v>
+        <v>2.130557453459693e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.751809208471885e-07</v>
+        <v>1.751809208471888e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.768604848586392e-07</v>
+        <v>1.768604848586393e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.771516016733311e-07</v>
+        <v>1.771516016733308e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.751809057204277e-07</v>
+        <v>1.75180905720428e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.771516016733311e-07</v>
+        <v>1.771516016733308e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.581349837665907e-07</v>
+        <v>1.573634537062303e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.771516016733311e-07</v>
+        <v>1.771516016733308e-07</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.95140390283537e-08</v>
+        <v>4.95140390283535e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.27541498646327e-08</v>
+        <v>3.275414986463272e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.313129456686066e-08</v>
+        <v>5.313129456686027e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.27541498646327e-08</v>
+        <v>3.275414986463272e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.27541498646327e-08</v>
+        <v>3.275414986463272e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.142682612464753e-08</v>
+        <v>5.142682612464688e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.484740693678986e-08</v>
+        <v>5.484740693678979e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.27541498646327e-08</v>
+        <v>3.275414986463272e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.362297655902231e-08</v>
+        <v>4.36229765590222e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.00990614504958e-08</v>
+        <v>5.009906145049572e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.191910967245515e-08</v>
+        <v>5.19191096724549e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.36450682360315e-08</v>
+        <v>5.36450682360317e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.867089383702054e-08</v>
+        <v>3.867089383702058e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.511848473937823e-08</v>
+        <v>5.511848473937775e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.867089383702054e-08</v>
+        <v>3.867089383702058e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.867089383702054e-08</v>
+        <v>3.867089383702058e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.433839262961536e-08</v>
+        <v>5.433839262961527e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.582031971010899e-08</v>
+        <v>5.58203197101093e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.867089383702054e-08</v>
+        <v>3.867089383702058e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.125118962105974e-08</v>
+        <v>5.125118962105991e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>5.388376622477494e-08</v>
+        <v>5.388376622477439e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>5.46292328878565e-08</v>
+        <v>5.58245179483831e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.043024615722347e-07</v>
+        <v>3.043024615722352e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.539560559860094e-07</v>
+        <v>2.539560559860093e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>6.522590371209831e-06</v>
+        <v>6.522590371209841e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>2.539560559860094e-07</v>
+        <v>2.539560559860093e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.539560559860094e-07</v>
+        <v>2.539560559860093e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>3.031772942680522e-06</v>
+        <v>3.031772942680516e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>7.243151289713632e-07</v>
+        <v>7.243151289713652e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>2.539560559860094e-07</v>
+        <v>2.539560559860093e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>4.72156134950731e-07</v>
+        <v>4.72156134950732e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>5.046604805376329e-07</v>
+        <v>5.046604805376343e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>9.278654220897353e-07</v>
+        <v>9.278654220897362e-07</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.558275668573662e-08</v>
+        <v>5.558275668573661e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.81200487230744e-08</v>
+        <v>4.812004872307451e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.558275668573662e-08</v>
+        <v>5.558275668573661e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.926738036668908e-08</v>
+        <v>4.926738036668917e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.926738036668906e-08</v>
+        <v>4.926738036668915e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.513907237189514e-08</v>
+        <v>5.513907237189523e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.558275668573662e-08</v>
+        <v>5.558275668573661e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.26270768034625e-08</v>
+        <v>5.262707680346259e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.558275668573662e-08</v>
+        <v>5.558275668573661e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.558275668573662e-08</v>
+        <v>5.558275668573661e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.558275668573662e-08</v>
+        <v>5.558275668573661e-08</v>
       </c>
     </row>
     <row r="4">
@@ -7327,37 +7327,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.13509000586511e-08</v>
+        <v>5.135090005865116e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.376381663076252e-08</v>
+        <v>4.37638166307626e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.144081877976993e-08</v>
+        <v>6.1440818779777e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>4.323546039298999e-08</v>
+        <v>4.323546039298977e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.796093456687053e-08</v>
+        <v>4.796093456687052e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.040610114267865e-07</v>
+        <v>1.040610114267867e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.096451592357833e-07</v>
+        <v>1.096451592357834e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>4.839522017637697e-08</v>
+        <v>1.015490158583541e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.069370062153881e-07</v>
+        <v>1.069370062153883e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>4.814467393527884e-08</v>
+        <v>4.814467393527886e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.160311677514531e-08</v>
+        <v>5.160311677514545e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.616280738336003e-08</v>
+        <v>9.616280738336006e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>9.320712750108586e-08</v>
+        <v>9.320712750108605e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>9.615521432944759e-08</v>
+        <v>9.615521432944765e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>9.311726430376359e-08</v>
+        <v>9.31172643037637e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>9.311726430376359e-08</v>
+        <v>9.31172643037637e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>9.571912306951845e-08</v>
+        <v>9.571912306951853e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>9.616280738336003e-08</v>
+        <v>9.616280738336006e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>9.320712750108586e-08</v>
+        <v>9.320712750108605e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>9.616280738336003e-08</v>
+        <v>9.616280738336006e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>9.616280738336003e-08</v>
+        <v>9.616280738336006e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>9.616280738336003e-08</v>
+        <v>9.616280738336006e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.561083322489443e-07</v>
+        <v>1.561083322489444e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.35369279620692e-07</v>
+        <v>2.353692796227592e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.554454185704996e-07</v>
+        <v>2.554454185704997e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.128714327238527e-07</v>
+        <v>2.12871432723853e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.557116127148459e-07</v>
+        <v>1.557116127148463e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.379411628972811e-07</v>
+        <v>2.379411628972812e-07</v>
       </c>
       <c r="H6" t="n">
         <v>2.383848472111031e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.354291673288485e-07</v>
+        <v>2.354291673288488e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.384010168959392e-07</v>
+        <v>2.384010168959395e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.545800037406237e-07</v>
+        <v>1.545800037406239e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.243295469368633e-07</v>
+        <v>3.243295469368636e-07</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.373764988860231e-07</v>
+        <v>2.373764988860233e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.927069436802557e-07</v>
+        <v>2.927069436802562e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.956627687637544e-07</v>
+        <v>2.95662768763755e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>3.599680472494953e-07</v>
+        <v>3.599680472494959e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.927069599196067e-07</v>
+        <v>2.927069599196074e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.952189392486886e-07</v>
+        <v>2.95218939248689e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.956626235625297e-07</v>
+        <v>2.956626235625303e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.927069436802557e-07</v>
+        <v>2.927069436802562e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.956626235625297e-07</v>
+        <v>2.956626235625303e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.605213310448293e-07</v>
+        <v>2.618914750887554e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.956626235625297e-07</v>
+        <v>2.956626235625303e-07</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.094455765244673e-08</v>
+        <v>6.094455765244681e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.427923158467114e-08</v>
+        <v>4.427923158467116e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>-9.033000861124593e-08</v>
+        <v>-9.033000861124587e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.427923158467114e-08</v>
+        <v>4.427923158467116e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>4.427923158467114e-08</v>
+        <v>4.427923158467116e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.231366287156986e-09</v>
+        <v>-3.231366287156972e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>5.236509968593774e-08</v>
+        <v>5.236509968593772e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.427923158467114e-08</v>
+        <v>4.427923158467116e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.766709270179515e-08</v>
+        <v>5.766709270179518e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.621170203553718e-08</v>
+        <v>5.62117020355372e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.440062688259948e-08</v>
+        <v>4.960104991894102e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.32689090693392e-08</v>
+        <v>6.326890906933924e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>4.631206457011904e-08</v>
+        <v>4.631206457011908e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.659903678575031e-09</v>
+        <v>1.659903678575084e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>4.631206457011904e-08</v>
+        <v>4.631206457011908e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.631206457011904e-08</v>
+        <v>4.631206457011908e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.674911117442955e-08</v>
+        <v>3.674911117442961e-08</v>
       </c>
       <c r="H9" t="n">
         <v>5.978779408147323e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.631206457011904e-08</v>
+        <v>4.631206457011908e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>6.19374227584871e-08</v>
+        <v>6.193742275848714e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.134179627423312e-08</v>
+        <v>6.134179627423316e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.061270624817436e-08</v>
+        <v>5.866163863518912e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7646,34 +7646,34 @@
         <v>1.948050669451564e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.495200800165705e-07</v>
+        <v>2.495200800165707e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>4.480366187130271e-06</v>
+        <v>4.480366187130282e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>2.495200800165705e-07</v>
+        <v>2.495200800165707e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.495200800165705e-07</v>
+        <v>2.495200800165707e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.456864673547176e-06</v>
+        <v>1.456864673547177e-06</v>
       </c>
       <c r="H2" t="n">
         <v>3.06442615588497e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>2.495200800165705e-07</v>
+        <v>2.495200800165707e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>5.314001165844475e-07</v>
+        <v>5.314001165844473e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>2.46216017477533e-07</v>
+        <v>2.462160174775328e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.796440860699802e-05</v>
+        <v>2.855361572788791e-07</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.128332230086859e-08</v>
+        <v>5.128332230086853e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.68859914745181e-08</v>
+        <v>4.688599147451801e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.128332230086859e-08</v>
+        <v>5.128332230086853e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.777960402368342e-08</v>
+        <v>4.777960402368336e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.777960402368342e-08</v>
+        <v>4.777960402368335e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.091771410119051e-08</v>
+        <v>5.091771410119038e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.128332230086856e-08</v>
+        <v>5.128332230086853e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.88323896568306e-08</v>
+        <v>4.883238965683053e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.128332230086859e-08</v>
+        <v>5.128332230086853e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.128332230086859e-08</v>
+        <v>5.128332230086853e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.128332230086859e-08</v>
+        <v>5.128332230086853e-08</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.522059160327011e-08</v>
+        <v>9.365468093836154e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.053756920039489e-08</v>
+        <v>4.053756920039496e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.328982492040612e-08</v>
+        <v>5.328982492040211e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>4.007078544090281e-08</v>
+        <v>4.007078544090276e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.256274707141352e-08</v>
+        <v>4.25627470714134e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>9.328907273868354e-08</v>
+        <v>4.485498340359202e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.732691341766281e-08</v>
+        <v>9.732691341766279e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>9.120374829432357e-08</v>
+        <v>9.120374829432351e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.487793763894504e-08</v>
+        <v>4.625729923917579e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.342814848038399e-08</v>
+        <v>4.342814848038427e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.081647907960246e-08</v>
+        <v>5.081647907960258e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7766,25 +7766,25 @@
         <v>8.337434994921482e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.092341730517683e-08</v>
+        <v>8.092341730517686e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.336725389779219e-08</v>
+        <v>8.336725389779202e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.087286720327682e-08</v>
+        <v>8.087286720327693e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.087286720327682e-08</v>
+        <v>8.087286720327693e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.300874174953679e-08</v>
+        <v>8.300874174953675e-08</v>
       </c>
       <c r="H5" t="n">
         <v>8.337434994921482e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.092341730517683e-08</v>
+        <v>8.092341730517686e-08</v>
       </c>
       <c r="J5" t="n">
         <v>8.337434994921482e-08</v>
@@ -7803,25 +7803,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.349843906937531e-07</v>
+        <v>1.349843906937533e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.016770136173152e-07</v>
+        <v>2.01677013619204e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.184961227956459e-07</v>
+        <v>2.184961227956454e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.827604377403774e-07</v>
+        <v>1.827604377403773e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.347000884413934e-07</v>
+        <v>1.347000884413932e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.037878565048208e-07</v>
+        <v>2.037878565048207e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.041534647044774e-07</v>
+        <v>2.041534647044773e-07</v>
       </c>
       <c r="I6" t="n">
         <v>2.017025320604606e-07</v>
@@ -7843,19 +7843,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.782359923126424e-07</v>
+        <v>1.782359923126423e-07</v>
       </c>
       <c r="C7" t="n">
         <v>2.178525264554485e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.203035278343195e-07</v>
+        <v>2.203035278343197e-07</v>
       </c>
       <c r="E7" t="n">
         <v>2.66397546300448e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.178525208654669e-07</v>
+        <v>2.17852520865467e-07</v>
       </c>
       <c r="G7" t="n">
         <v>2.199378508998085e-07</v>
@@ -7870,7 +7870,7 @@
         <v>2.203034590994866e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.959294325411015e-07</v>
+        <v>1.673329915839979e-07</v>
       </c>
       <c r="L7" t="n">
         <v>2.203034590994866e-07</v>
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.874448081747574e-08</v>
+        <v>5.874448081747577e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.112041293156136e-08</v>
+        <v>4.112041293156131e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.833367247433192e-08</v>
+        <v>-5.833367247433216e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.112041293156136e-08</v>
+        <v>4.112041293156131e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>4.112041293156136e-08</v>
+        <v>4.112041293156131e-08</v>
       </c>
       <c r="G8" t="n">
         <v>2.577265939421824e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.659642937537094e-08</v>
+        <v>5.659642937537093e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.112041293156136e-08</v>
+        <v>4.112041293156131e-08</v>
       </c>
       <c r="J8" t="n">
         <v>5.110706383928958e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.735858308808081e-08</v>
+        <v>5.735858308808083e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.706625111142142e-08</v>
+        <v>-3.262023142031458e-07</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.97926335844266e-08</v>
+        <v>5.979263358442657e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>4.345629007776929e-08</v>
+        <v>4.345629007776926e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.211064339995041e-08</v>
+        <v>1.211064339995024e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>4.345629007776929e-08</v>
+        <v>4.345629007776926e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.345629007776929e-08</v>
+        <v>4.345629007776926e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.612609660839309e-08</v>
+        <v>4.612609660839313e-08</v>
       </c>
       <c r="H9" t="n">
         <v>5.892293010469568e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.345629007776929e-08</v>
+        <v>4.345629007776926e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.668618095882725e-08</v>
+        <v>5.668618095882722e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>5.922842064077099e-08</v>
+        <v>5.9228420640771e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>5.911290698727799e-08</v>
+        <v>-9.669956295315784e-08</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Hydrogen/hydrogen particulate matter results.xlsx
+++ b/Results/Hydrogen/hydrogen particulate matter results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.366392414758979e-07</v>
+        <v>4.366392414759077e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.936670559190912e-07</v>
+        <v>3.936670559190901e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>8.051541435880191e-06</v>
+        <v>8.051541435880207e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>3.936670559190912e-07</v>
+        <v>3.936670559190901e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>3.936670559190912e-07</v>
+        <v>3.936670559190901e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>4.036299184806348e-06</v>
+        <v>4.036299184806343e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>1.455499789368524e-06</v>
+        <v>1.45549978936852e-06</v>
       </c>
       <c r="I2" t="n">
-        <v>3.936670559190912e-07</v>
+        <v>3.936670559190901e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>7.900681948354687e-07</v>
+        <v>7.900681948354725e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>6.980655527460446e-07</v>
+        <v>6.980655527460443e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.178281530338768e-06</v>
+        <v>1.349530518736892e-06</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.025740673436641e-08</v>
+        <v>6.025740673436631e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.30173093258935e-08</v>
+        <v>5.301730932589345e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>6.025740673436641e-08</v>
+        <v>6.025740673436631e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.423340778795521e-08</v>
+        <v>5.42334077879551e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.423340778795514e-08</v>
+        <v>5.42334077879551e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.981712675539083e-08</v>
+        <v>5.981712675539091e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>6.025740673436641e-08</v>
+        <v>6.025740673436631e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.732999974403968e-08</v>
+        <v>5.732999974403962e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>6.025740673436641e-08</v>
+        <v>6.025740673436631e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>6.025740673436641e-08</v>
+        <v>6.025740673436631e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>6.025740673436641e-08</v>
+        <v>6.025740673436631e-08</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.705250091532254e-08</v>
+        <v>5.705250091532245e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.850617043672366e-08</v>
+        <v>4.850617043672319e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.813218453849867e-08</v>
+        <v>6.813238218081976e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>4.786910075493031e-08</v>
+        <v>4.786910075493029e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>5.361911658513975e-08</v>
+        <v>5.361911658513965e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.175196236549868e-07</v>
+        <v>1.175196236549867e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.236006816988417e-07</v>
+        <v>1.236006816988418e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>5.412509392499581e-08</v>
+        <v>1.150324966436354e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>5.867853001226714e-08</v>
+        <v>1.204898880987073e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>5.336612535878896e-08</v>
+        <v>5.336612535878888e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.736812362766006e-08</v>
+        <v>5.736812362766005e-08</v>
       </c>
     </row>
     <row r="5">
@@ -638,25 +638,25 @@
         <v>1.078869942230716e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>1.049595872327451e-07</v>
+        <v>1.049595872327449e-07</v>
       </c>
       <c r="D5" t="n">
-        <v>1.078787258132966e-07</v>
+        <v>1.078787258132965e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>1.048637168607972e-07</v>
+        <v>1.04863716860797e-07</v>
       </c>
       <c r="F5" t="n">
-        <v>1.048637168607972e-07</v>
+        <v>1.04863716860797e-07</v>
       </c>
       <c r="G5" t="n">
-        <v>1.074467142440962e-07</v>
+        <v>1.074467142440961e-07</v>
       </c>
       <c r="H5" t="n">
         <v>1.078869942230716e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>1.049595872327451e-07</v>
+        <v>1.049595872327449e-07</v>
       </c>
       <c r="J5" t="n">
         <v>1.078869942230716e-07</v>
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.756872942155771e-07</v>
+        <v>1.756872942155769e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.6652421774104e-07</v>
+        <v>2.665242177432859e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.8896973525512e-07</v>
+        <v>2.889697352551192e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.408675538367471e-07</v>
+        <v>2.408675538367467e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.756817942100692e-07</v>
+        <v>1.756817942100689e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.690738497145979e-07</v>
+        <v>2.690738497145974e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.69514129693563e-07</v>
+        <v>2.695141296935627e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.665867227032467e-07</v>
+        <v>2.665867227032463e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.695325693471075e-07</v>
+        <v>2.69532569347107e-07</v>
       </c>
       <c r="K6" t="n">
         <v>1.739444125735331e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.675241050203674e-07</v>
+        <v>3.675241050203671e-07</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.957102060853321e-07</v>
+        <v>2.95710206085332e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>3.668140388495851e-07</v>
+        <v>3.668140388495846e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>3.69741615596493e-07</v>
+        <v>3.697416155964926e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>4.522446861720689e-07</v>
+        <v>4.522446861720684e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>3.668140491737306e-07</v>
+        <v>3.668140491737304e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>3.693011658609367e-07</v>
+        <v>3.693011658609361e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>3.697414458399119e-07</v>
+        <v>3.697414458399116e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>3.668140388495851e-07</v>
+        <v>3.668140388495846e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>3.697414458399119e-07</v>
+        <v>3.697414458399116e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>3.268475261819505e-07</v>
+        <v>2.765228564620834e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>3.697414458399119e-07</v>
+        <v>3.697414458399116e-07</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.175206072869816e-08</v>
+        <v>6.175206072869755e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.46529883320137e-08</v>
+        <v>4.465298833201357e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.014685898710429e-07</v>
+        <v>-1.014685898710431e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>4.46529883320137e-08</v>
+        <v>4.465298833201357e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>4.46529883320137e-08</v>
+        <v>4.465298833201357e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.411858998049847e-08</v>
+        <v>-1.411858998049846e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>4.348035064442417e-08</v>
+        <v>4.348035064442428e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.46529883320137e-08</v>
+        <v>4.465298833201357e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.51083140301593e-08</v>
+        <v>5.510831403015922e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.626853763347752e-08</v>
+        <v>5.626853763347773e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.839385479320794e-08</v>
+        <v>4.839385479320784e-08</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.547041665342214e-08</v>
+        <v>6.547041665342225e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>4.823331797743095e-08</v>
+        <v>4.823331797743089e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.003772026235194e-09</v>
+        <v>-1.00377202623524e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>4.823331797743095e-08</v>
+        <v>4.823331797743089e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.823331797743095e-08</v>
+        <v>4.823331797743089e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.414392736774902e-08</v>
+        <v>3.414392736774885e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.805297594335385e-08</v>
+        <v>5.805297594335384e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.823331797743095e-08</v>
+        <v>4.823331797743089e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>6.277006888440386e-08</v>
+        <v>6.277006888440382e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.323772897618405e-08</v>
+        <v>6.323772897618394e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.004568779204599e-08</v>
+        <v>5.919748026318883e-08</v>
       </c>
     </row>
   </sheetData>
@@ -911,28 +911,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.690265430143051e-07</v>
+        <v>1.690265430143054e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>4.270441188257594e-07</v>
+        <v>4.270441188257596e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>4.189471375831566e-07</v>
+        <v>4.189471375831564e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>4.270441188257594e-07</v>
+        <v>4.270441188257596e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>4.270441188257594e-07</v>
+        <v>4.270441188257596e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>3.515945831359974e-07</v>
+        <v>3.515945831359966e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>2.448267370275237e-07</v>
+        <v>2.448267370275241e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>4.270441188257594e-07</v>
+        <v>4.270441188257596e-07</v>
       </c>
       <c r="J2" t="n">
         <v>7.684316695982611e-07</v>
@@ -941,7 +941,7 @@
         <v>2.32716785734099e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.840095303275722e-07</v>
+        <v>1.840095303275719e-07</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.922318950248411e-08</v>
+        <v>4.922318950248407e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.706597002734646e-08</v>
+        <v>4.706597002734644e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>4.922318950248411e-08</v>
+        <v>4.922318950248407e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.782391848251854e-08</v>
+        <v>4.782391848251858e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.782391848251852e-08</v>
+        <v>4.782391848251856e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>4.892917175940223e-08</v>
+        <v>4.892917175940224e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>4.922318950248411e-08</v>
+        <v>4.922318950248407e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.72340454465042e-08</v>
+        <v>4.723404544650428e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>4.922318950248411e-08</v>
+        <v>4.922318950248407e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>4.922318950248411e-08</v>
+        <v>4.922318950248407e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>4.922318950248411e-08</v>
+        <v>4.922318950248407e-08</v>
       </c>
     </row>
     <row r="4">
@@ -991,37 +991,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.806001150087111e-08</v>
+        <v>4.171314297844069e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.963571107334104e-08</v>
+        <v>3.963571107334136e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>7.909685696516633e-08</v>
+        <v>7.909685696516611e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.916914819201276e-08</v>
+        <v>3.916914819201256e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.982600125888679e-08</v>
+        <v>3.982600125888682e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>4.141912523535878e-08</v>
+        <v>7.776599375778939e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.161986200231285e-08</v>
+        <v>8.161986200231294e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.972399892246072e-08</v>
+        <v>3.972399892246078e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>7.895144976030868e-08</v>
+        <v>4.271169151584162e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.132234860991781e-08</v>
+        <v>4.132234860991958e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.170182959024684e-08</v>
+        <v>4.170182959024688e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.70652846048792e-08</v>
+        <v>7.706528460487932e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.507614054889928e-08</v>
+        <v>7.507614054889929e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.705814227114037e-08</v>
+        <v>7.705814227114054e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.507399189531003e-08</v>
+        <v>7.507399189531014e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.507399189531003e-08</v>
+        <v>7.507399189531014e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.677126686179746e-08</v>
+        <v>7.677126686179748e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.70652846048792e-08</v>
+        <v>7.706528460487932e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.507614054889928e-08</v>
+        <v>7.507614054889929e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.70652846048792e-08</v>
+        <v>7.706528460487932e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.70652846048792e-08</v>
+        <v>7.706528460487932e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.70652846048792e-08</v>
+        <v>7.706528460487932e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.237516907413764e-07</v>
+        <v>1.237516907413763e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.841875864959704e-07</v>
+        <v>1.841875864978448e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.990974214309891e-07</v>
+        <v>1.990974214309898e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.671159773671224e-07</v>
+        <v>1.671159773671226e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.237436847942725e-07</v>
+        <v>1.237436847942726e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.858632092180275e-07</v>
+        <v>1.85863209218028e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.861572269611016e-07</v>
+        <v>1.861572269611019e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.841680829051296e-07</v>
+        <v>1.8416808290513e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.861694914337244e-07</v>
+        <v>1.861694914337246e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.22592475864724e-07</v>
+        <v>1.225924758647243e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.513450278101047e-07</v>
+        <v>2.513450278101053e-07</v>
       </c>
     </row>
     <row r="7">
@@ -1114,34 +1114,34 @@
         <v>1.451716976492686e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.762685497979524e-07</v>
+        <v>1.762685497979525e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.782577409376469e-07</v>
+        <v>1.78257740937647e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.144491482718514e-07</v>
+        <v>2.144491482718516e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.762685640599325e-07</v>
+        <v>1.762685640599321e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.779636761108504e-07</v>
+        <v>1.779636761108506e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.782576938539324e-07</v>
+        <v>1.782576938539325e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.762685497979524e-07</v>
+        <v>1.762685497979525e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.782576938539324e-07</v>
+        <v>1.782576938539325e-07</v>
       </c>
       <c r="K7" t="n">
         <v>1.590875575174431e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.782576938539324e-07</v>
+        <v>1.782576938539325e-07</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.533035465317526e-08</v>
+        <v>5.533035465317524e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.406250437552517e-08</v>
+        <v>3.406250437552523e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.865547604308448e-08</v>
+        <v>4.865547604308445e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.406250437552517e-08</v>
+        <v>3.406250437552523e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.406250437552517e-08</v>
+        <v>3.406250437552523e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.058624893479187e-08</v>
+        <v>5.05862489347918e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.398822836453878e-08</v>
+        <v>5.398822836453866e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.406250437552517e-08</v>
+        <v>3.406250437552523e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.147025552601564e-08</v>
+        <v>4.147025552601567e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.350306336229057e-08</v>
+        <v>5.350306336229037e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.550078975124518e-08</v>
+        <v>5.550078975124497e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1191,37 +1191,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.609584679911298e-08</v>
+        <v>5.609584679911294e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.932122701849197e-08</v>
+        <v>3.932122701849201e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.337746495380194e-08</v>
+        <v>5.337746495380191e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.932122701849197e-08</v>
+        <v>3.932122701849201e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.932122701849197e-08</v>
+        <v>3.932122701849201e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.406906871779654e-08</v>
+        <v>5.406906871779652e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.555314234930188e-08</v>
+        <v>5.555314234930175e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.932122701849197e-08</v>
+        <v>3.932122701849201e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.045710502344478e-08</v>
+        <v>5.045710502344472e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>5.535185205902521e-08</v>
+        <v>5.535185205902514e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>5.580840000558823e-08</v>
+        <v>5.616731891011427e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.530884140316175e-07</v>
+        <v>1.53088414031617e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>3.072606018528202e-07</v>
+        <v>3.072606018528199e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>3.972313489377313e-06</v>
+        <v>3.972313489377312e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>2.461616584797018e-07</v>
+        <v>2.461616584797014e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.461616584797018e-07</v>
+        <v>2.461616584797014e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.856478419768108e-06</v>
+        <v>1.85647841976811e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>5.199749669447886e-07</v>
+        <v>5.199749669447885e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>2.461616584797018e-07</v>
+        <v>2.461616584797014e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.312022349256623e-06</v>
+        <v>1.312022349256621e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>3.541354347706623e-07</v>
+        <v>3.541354347706611e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>3.947599806144934e-07</v>
+        <v>3.947599806144932e-07</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.488871828781371e-08</v>
+        <v>5.488871828781379e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.995004315065274e-08</v>
+        <v>4.995004315065272e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.488871828781372e-08</v>
+        <v>5.488871828781377e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.806519814687286e-08</v>
+        <v>4.806519814687295e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.80651981468729e-08</v>
+        <v>4.806519814687295e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.452251473148056e-08</v>
+        <v>5.45225147314808e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.488871828781372e-08</v>
+        <v>5.488871828781379e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.244037742980609e-08</v>
+        <v>5.244037742980614e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.488871828781372e-08</v>
+        <v>5.488871828781379e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.488871828781372e-08</v>
+        <v>5.488871828781377e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.488871828781372e-08</v>
+        <v>5.488871828781377e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1387,34 +1387,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.796034732623761e-08</v>
+        <v>9.51063484757013e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.507892537775046e-08</v>
+        <v>4.50789253777505e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.36485727779193e-08</v>
+        <v>5.364884893721439e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>4.199467722369273e-08</v>
+        <v>4.199467722369271e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.528316774375236e-08</v>
+        <v>4.528316774375229e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>9.474014491936811e-08</v>
+        <v>4.759414376990441e-08</v>
       </c>
       <c r="H4" t="n">
         <v>1.044113236725796e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>9.265800761769368e-08</v>
+        <v>4.551200646822991e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.772125904074998e-08</v>
+        <v>9.772125904075009e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.606215616103752e-08</v>
+        <v>4.606215616103756e-08</v>
       </c>
       <c r="L4" t="n">
         <v>4.801894937294705e-08</v>
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.303916902300959e-08</v>
+        <v>9.303916902300963e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>9.299140403773312e-08</v>
+        <v>9.299140403773319e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>9.303225878397345e-08</v>
+        <v>9.303225878397343e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>9.056354176969908e-08</v>
+        <v>9.05635417696991e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>9.056354176969908e-08</v>
+        <v>9.05635417696991e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>9.267296546667638e-08</v>
+        <v>9.267296546667645e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>9.303916902300959e-08</v>
+        <v>9.303916902300963e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>9.059082816500194e-08</v>
+        <v>9.0590828165002e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>9.303916902300959e-08</v>
+        <v>9.303916902300963e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>9.303916902300959e-08</v>
+        <v>9.303916902300963e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>9.303916902300959e-08</v>
+        <v>9.303916902300963e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.521169163162509e-07</v>
+        <v>1.521169163162513e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.321573597386613e-07</v>
+        <v>2.321573597386614e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.488134505255809e-07</v>
+        <v>2.488134505255817e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.078509631714451e-07</v>
+        <v>2.078509631714454e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.521951323840813e-07</v>
+        <v>1.521951323840816e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.318401751972711e-07</v>
+        <v>2.318401751972714e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.322063787539174e-07</v>
+        <v>2.32206378753918e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.297580378955964e-07</v>
+        <v>2.297580378955967e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.322221186217244e-07</v>
+        <v>2.322221186217251e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.506292134308404e-07</v>
+        <v>1.506292134308406e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.158665192423839e-07</v>
+        <v>3.158665192423846e-07</v>
       </c>
     </row>
     <row r="7">
@@ -1513,31 +1513,31 @@
         <v>2.538092376894103e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.538571078399268e-07</v>
+        <v>2.538571078399273e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>3.083556991885842e-07</v>
+        <v>3.083556991885841e-07</v>
       </c>
       <c r="F7" t="n">
         <v>2.514086784927368e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.534907991183536e-07</v>
+        <v>2.534907991183537e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.538570026746867e-07</v>
+        <v>2.53857002674687e-07</v>
       </c>
       <c r="I7" t="n">
         <v>2.514086618166791e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.538570026746867e-07</v>
+        <v>2.53857002674687e-07</v>
       </c>
       <c r="K7" t="n">
         <v>2.252644332127579e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.538570026746867e-07</v>
+        <v>2.53857002674687e-07</v>
       </c>
     </row>
     <row r="8">
@@ -1547,37 +1547,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.50668334049132e-08</v>
+        <v>9.506683340491321e-08</v>
       </c>
       <c r="C8" t="n">
         <v>2.200628114844446e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.023165177883684e-08</v>
+        <v>-2.023165177883683e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.0496927099549e-08</v>
+        <v>4.049692709954898e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>4.049692709954899e-08</v>
+        <v>4.049692709954898e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>1.565828715144602e-08</v>
+        <v>1.565828715144605e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>6.08577080427751e-08</v>
+        <v>6.085770804277507e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.0496927099549e-08</v>
+        <v>4.049692709954898e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>3.565885712382999e-08</v>
+        <v>3.565885712382998e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.008214397719928e-07</v>
+        <v>1.008214397719929e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.472422319519186e-08</v>
+        <v>5.472422319519187e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1587,13 +1587,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.508583138697078e-08</v>
+        <v>9.508583138697087e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.510718097927411e-08</v>
+        <v>2.510718097927413e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>3.229859519635618e-08</v>
+        <v>3.229859519635616e-08</v>
       </c>
       <c r="E9" t="n">
         <v>4.236478861472983e-08</v>
@@ -1602,22 +1602,22 @@
         <v>4.236478861472983e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.871101453849721e-08</v>
+        <v>3.871101453849722e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.533236578173422e-08</v>
+        <v>6.533236578173419e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.236478861472983e-08</v>
+        <v>4.236478861472982e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.098802915605307e-08</v>
+        <v>5.098802915605303e-08</v>
       </c>
       <c r="K9" t="n">
         <v>1.03185634232507e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>5.773530496777259e-08</v>
+        <v>5.773530496777261e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.241550746804982e-07</v>
+        <v>1.241550746804986e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.651528341159891e-07</v>
+        <v>2.651528341159905e-07</v>
       </c>
       <c r="D2" t="n">
         <v>2.675936937967789e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>2.005635988237701e-07</v>
+        <v>2.005635988237706e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.005635988237701e-07</v>
+        <v>2.005635988237706e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.074415021229922e-06</v>
+        <v>1.074415021229929e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>3.476622679897449e-07</v>
+        <v>3.476622679897456e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>2.005635988237701e-07</v>
+        <v>2.005635988237706e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>1.059624864638629e-06</v>
+        <v>1.05962486463863e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>2.040571411160859e-07</v>
+        <v>2.040571411160863e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>2.176973340858173e-07</v>
+        <v>2.176973340858179e-07</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.237788405299019e-08</v>
+        <v>5.237788405299081e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.926237117237768e-08</v>
+        <v>4.926237117237769e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.237788405299019e-08</v>
+        <v>5.237788405299081e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.862674048732725e-08</v>
+        <v>4.862674048732737e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.86267404873273e-08</v>
+        <v>4.862674048732738e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.193755406297208e-08</v>
+        <v>5.193755406297226e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.237788405299019e-08</v>
+        <v>5.237788405299081e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.942794433711442e-08</v>
+        <v>4.942794433711447e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.237788405299019e-08</v>
+        <v>5.237788405299081e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.237788405299019e-08</v>
+        <v>5.237788405299081e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.237788405299019e-08</v>
+        <v>5.237788405299081e-08</v>
       </c>
     </row>
     <row r="4">
@@ -1783,37 +1783,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.623553736582189e-08</v>
+        <v>8.623553736582241e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.314359141454952e-08</v>
+        <v>4.314359141454922e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>8.899703398776322e-08</v>
+        <v>8.89970339877642e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.97345520837621e-08</v>
+        <v>3.973455208376208e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.182035809847542e-08</v>
+        <v>4.182035809847546e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>4.44363969259848e-08</v>
+        <v>8.579520737580384e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.529111864688704e-08</v>
+        <v>9.529111864688733e-08</v>
       </c>
       <c r="I4" t="n">
         <v>4.192678720012733e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.613868545592493e-08</v>
+        <v>4.613868545592488e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.361944122660258e-08</v>
+        <v>4.361944122660295e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.488320522410372e-08</v>
+        <v>4.488320522410399e-08</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.584078607331033e-08</v>
+        <v>8.584078607331042e-08</v>
       </c>
       <c r="C5" t="n">
         <v>8.582415668582062e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.583429950188e-08</v>
+        <v>8.583429950187965e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.293248014546237e-08</v>
+        <v>8.29324801454624e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.293248014546237e-08</v>
+        <v>8.29324801454624e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.540045608329195e-08</v>
+        <v>8.540045608329182e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.584078607331033e-08</v>
+        <v>8.584078607331042e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.289084635743404e-08</v>
+        <v>8.289084635743405e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.584078607331033e-08</v>
+        <v>8.584078607331042e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.584078607331033e-08</v>
+        <v>8.584078607331042e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.584078607331033e-08</v>
+        <v>8.584078607331042e-08</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.398583994981682e-07</v>
+        <v>1.39858399498169e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.123517982469122e-07</v>
+        <v>2.123517982445633e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.273283065376552e-07</v>
+        <v>2.273283065376555e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.895960652195686e-07</v>
+        <v>1.895960652195689e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.392336383774027e-07</v>
+        <v>1.392336383774029e-07</v>
       </c>
       <c r="G6" t="n">
         <v>2.118655247508525e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.123058547415184e-07</v>
+        <v>2.12305854741519e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.09355915024995e-07</v>
+        <v>2.093559150249948e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.123200927339708e-07</v>
+        <v>2.123200927339714e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.385126508199344e-07</v>
+        <v>1.385126508199346e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.879832796996327e-07</v>
+        <v>2.879832796996333e-07</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.684793882786204e-07</v>
+        <v>1.684793882786209e-07</v>
       </c>
       <c r="C7" t="n">
         <v>2.079109738122671e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.079276806377302e-07</v>
+        <v>2.07927680637731e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.5050015644035e-07</v>
+        <v>2.505001564403504e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.049776789818443e-07</v>
+        <v>2.049776789818446e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.074872732097379e-07</v>
+        <v>2.074872732097383e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.079276031997565e-07</v>
+        <v>2.079276031997574e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.049776634838807e-07</v>
+        <v>2.049776634838809e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.079276031997565e-07</v>
+        <v>2.079276031997574e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.850711851194657e-07</v>
+        <v>1.85071185119466e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.079276031997565e-07</v>
+        <v>2.079276031997574e-07</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.437979299130291e-08</v>
+        <v>9.4379792991303e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.136241753878251e-08</v>
+        <v>2.136241753878252e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>4.688945101039202e-09</v>
+        <v>4.6889451010394e-09</v>
       </c>
       <c r="E8" t="n">
-        <v>4.013631468499803e-08</v>
+        <v>4.013631468499808e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>4.013631468499803e-08</v>
+        <v>4.013631468499808e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.975255970442301e-08</v>
+        <v>2.97525597044229e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>6.238186862733638e-08</v>
+        <v>6.238186862733656e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.013631468499803e-08</v>
+        <v>4.013631468499808e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>3.780546191050785e-08</v>
+        <v>3.780546191050799e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.020777178979141e-07</v>
+        <v>1.020777178979146e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.604812043111649e-08</v>
+        <v>5.604812043111669e-08</v>
       </c>
     </row>
     <row r="9">
@@ -1983,37 +1983,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.410068185057087e-08</v>
+        <v>9.410068185057104e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.410016893106086e-08</v>
+        <v>2.410016893106089e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>4.151193732344175e-08</v>
+        <v>4.151193732344165e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>4.155131036830549e-08</v>
+        <v>4.155131036830552e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.155131036830549e-08</v>
+        <v>4.155131036830552e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.321839346829903e-08</v>
+        <v>4.321839346829909e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.501420986989853e-08</v>
+        <v>6.501420986989895e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.155131036830549e-08</v>
+        <v>4.155131036830552e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.063424248894848e-08</v>
+        <v>5.063424248894866e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.025619234189164e-07</v>
+        <v>1.025619234189166e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>5.711780726279733e-08</v>
+        <v>5.71178072627975e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.041731537190034e-07</v>
+        <v>1.041731537190035e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.03751998782047e-07</v>
+        <v>2.037519987820467e-07</v>
       </c>
       <c r="D2" t="n">
         <v>1.836857284092334e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>1.520894132202873e-07</v>
+        <v>1.520894132202871e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.520894132202873e-07</v>
+        <v>1.520894132202871e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>6.276954754195289e-07</v>
+        <v>6.276954754195297e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>2.729169579525102e-07</v>
+        <v>2.729169579525103e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.520894132202873e-07</v>
+        <v>1.520894132202871e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>7.757460788661333e-07</v>
+        <v>7.757460788661339e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.42497463092182e-07</v>
+        <v>1.424974630921816e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.724643866126648e-07</v>
+        <v>1.724643866126646e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2142,34 +2142,34 @@
         <v>5.229930626123263e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.000810807230979e-08</v>
+        <v>5.000810807230971e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.229930626123263e-08</v>
+        <v>5.229930626123261e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.824490359781212e-08</v>
+        <v>4.824490359781211e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.824490359781214e-08</v>
+        <v>4.824490359781211e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.191614867310619e-08</v>
+        <v>5.191614867310623e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.229930626123263e-08</v>
+        <v>5.229930626123261e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.972646631705126e-08</v>
+        <v>4.972646631705128e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.229930626123263e-08</v>
+        <v>5.229930626123261e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.229930626123263e-08</v>
+        <v>5.229930626123261e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.229930626123263e-08</v>
+        <v>5.229930626123261e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2179,37 +2179,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.402744808220857e-08</v>
+        <v>4.402744808220838e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.287701115780248e-08</v>
+        <v>4.287701115780258e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.686677332958499e-08</v>
+        <v>4.686648619128194e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.972675371469714e-08</v>
+        <v>3.972675371469693e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.139939473791455e-08</v>
+        <v>4.139939473791443e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.341800705167383e-08</v>
+        <v>8.341800705167387e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.371026110411078e-08</v>
+        <v>9.371026110411061e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>8.122832469561887e-08</v>
+        <v>8.12283246956188e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>8.592719103973486e-08</v>
+        <v>8.592719103973482e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.321662366125791e-08</v>
+        <v>4.321662366125641e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.402046030335029e-08</v>
+        <v>4.402046030334954e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2225,22 +2225,22 @@
         <v>8.455952944081333e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.455111587097365e-08</v>
+        <v>8.455111587097352e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.204965344856151e-08</v>
+        <v>8.204965344856139e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.204965344856151e-08</v>
+        <v>8.204965344856139e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.417444207866313e-08</v>
+        <v>8.417444207866306e-08</v>
       </c>
       <c r="H5" t="n">
         <v>8.455759966678947e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.19847597226082e-08</v>
+        <v>8.198475972260816e-08</v>
       </c>
       <c r="J5" t="n">
         <v>8.455759966678947e-08</v>
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.376215384198435e-07</v>
+        <v>1.376215384198434e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.08582594449413e-07</v>
+        <v>2.085825944521582e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.231924553888094e-07</v>
+        <v>2.231924553888093e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.866132175542816e-07</v>
+        <v>1.866132175542814e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.373378941976008e-07</v>
+        <v>1.373378941976006e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.081129865909881e-07</v>
+        <v>2.08112986590988e-07</v>
       </c>
       <c r="H6" t="n">
         <v>2.084961441802433e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.059233042349331e-07</v>
+        <v>2.05923304234933e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.085100730598504e-07</v>
+        <v>2.085100730598503e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.363050062279302e-07</v>
+        <v>1.363050062279301e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.825305963325878e-07</v>
+        <v>2.825305963325874e-07</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.521402658802741e-07</v>
+        <v>1.521402658802744e-07</v>
       </c>
       <c r="C7" t="n">
         <v>1.870057846507428e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.870039179454379e-07</v>
+        <v>1.870039179454378e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.246629327998855e-07</v>
+        <v>2.246629327998853e-07</v>
       </c>
       <c r="F7" t="n">
         <v>1.844310296366633e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.866206972885926e-07</v>
+        <v>1.866206972885924e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.87003854876719e-07</v>
+        <v>1.870038548767191e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.844310149325376e-07</v>
+        <v>1.844310149325375e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.87003854876719e-07</v>
+        <v>1.870038548767191e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.431043568555163e-07</v>
+        <v>1.659842359470475e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.87003854876719e-07</v>
+        <v>1.870038548767191e-07</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.415305305494788e-08</v>
+        <v>9.41530530549478e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.192446920912128e-08</v>
+        <v>2.192446920912125e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>2.41945361115489e-08</v>
+        <v>2.419453611154883e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.027215553753093e-08</v>
+        <v>4.02721555375309e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>4.027215553753093e-08</v>
+        <v>4.02721555375309e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.887089574301434e-08</v>
+        <v>3.887089574301428e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>6.302279968638253e-08</v>
+        <v>6.302279968638249e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.027215553753093e-08</v>
+        <v>4.02721555375309e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.195314126077722e-08</v>
+        <v>4.195314126077713e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.024444062597352e-07</v>
+        <v>1.02444406259735e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.603630490757834e-08</v>
+        <v>5.603630490757832e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2379,37 +2379,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.359526113477815e-08</v>
+        <v>9.359526113477823e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.380588322041694e-08</v>
+        <v>2.380588322041693e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>4.889152084600141e-08</v>
+        <v>4.889152084600131e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>4.100123875935537e-08</v>
+        <v>4.100123875935532e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.100123875935537e-08</v>
+        <v>4.100123875935532e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.608081743978809e-08</v>
+        <v>4.608081743978807e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.470933121428579e-08</v>
+        <v>6.470933121428577e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.100123875935537e-08</v>
+        <v>4.100123875935532e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.091365036767834e-08</v>
+        <v>5.09136503676783e-08</v>
       </c>
       <c r="K9" t="n">
         <v>1.020534856588754e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>5.654872961290163e-08</v>
+        <v>5.654872961290165e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2498,34 +2498,34 @@
         <v>1.311982352188964e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.230865380150213e-07</v>
+        <v>1.230865380150212e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>2.235559612580159e-06</v>
+        <v>2.235559612580156e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>2.311828981725905e-07</v>
+        <v>2.311828981725897e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.311828981725905e-07</v>
+        <v>2.311828981725897e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.157216196650614e-06</v>
+        <v>1.157216196650619e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>4.394780240715979e-07</v>
+        <v>4.394780240715981e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>2.311828981725905e-07</v>
+        <v>2.311828981725897e-07</v>
       </c>
       <c r="J2" t="n">
         <v>1.056842521608991e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>2.667731833987068e-07</v>
+        <v>2.66773183398707e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>4.338716358076107e-07</v>
+        <v>4.338716358076104e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.305883975270708e-08</v>
+        <v>5.305883975270714e-08</v>
       </c>
       <c r="C3" t="n">
         <v>4.853866136308164e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.305883975270708e-08</v>
+        <v>5.305883975270714e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.722898400648715e-08</v>
+        <v>4.722898400648722e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.722898400648717e-08</v>
+        <v>4.722898400648722e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.271714823305017e-08</v>
+        <v>5.271714823305021e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.305883975270708e-08</v>
+        <v>5.305883975270714e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.076628194939303e-08</v>
+        <v>5.076628194939309e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.305883975270708e-08</v>
+        <v>5.305883975270714e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.305883975270708e-08</v>
+        <v>5.305883975270714e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.305883975270708e-08</v>
+        <v>5.305883975270714e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2575,37 +2575,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.472431709766735e-08</v>
+        <v>4.472431709766736e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.249299598364427e-08</v>
+        <v>4.249299598364385e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.780950908073135e-08</v>
+        <v>4.780923465562937e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.99855527719354e-08</v>
+        <v>3.998555277193534e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.233034998124392e-08</v>
+        <v>4.233034998124393e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>4.438262557801038e-08</v>
+        <v>4.438262557801046e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.743921735139262e-08</v>
+        <v>9.743921735139269e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.243175929435328e-08</v>
+        <v>8.609771902734273e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>9.070122302861096e-08</v>
+        <v>4.598718604161584e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.350062714828057e-08</v>
+        <v>4.35006271482806e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.480123692364424e-08</v>
+        <v>4.480123692364427e-08</v>
       </c>
     </row>
     <row r="5">
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.831144195827658e-08</v>
+        <v>8.831144195827666e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.829081594302524e-08</v>
+        <v>8.829081594302537e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.830454230097962e-08</v>
+        <v>8.830454230097967e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.611419457427136e-08</v>
+        <v>8.611419457427141e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.611419457427136e-08</v>
+        <v>8.611419457427141e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.796975043861963e-08</v>
+        <v>8.796975043861969e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.831144195827658e-08</v>
+        <v>8.831144195827666e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.601888415496253e-08</v>
+        <v>8.601888415496257e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.831144195827658e-08</v>
+        <v>8.831144195827666e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.831144195827658e-08</v>
+        <v>8.831144195827666e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.831144195827658e-08</v>
+        <v>8.831144195827666e-08</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.449877343828438e-07</v>
+        <v>1.44987734382844e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.211629995691123e-07</v>
+        <v>2.211629995714622e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.368443595965868e-07</v>
+        <v>2.368443595965869e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.980692988020612e-07</v>
+        <v>1.980692988020615e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.451677930957154e-07</v>
+        <v>1.451677930957156e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.207268227466143e-07</v>
+        <v>2.207268227466146e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.21068514266571e-07</v>
+        <v>2.210685142665716e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.18775956462957e-07</v>
+        <v>2.187759564629575e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.210834663145081e-07</v>
+        <v>2.210834663145083e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.435744948338363e-07</v>
+        <v>1.435744948338365e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.005412506279103e-07</v>
+        <v>3.005412506279109e-07</v>
       </c>
     </row>
     <row r="7">
@@ -2695,19 +2695,19 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.861893425490555e-07</v>
+        <v>1.861893425490552e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.306775780122039e-07</v>
+        <v>2.306775780122037e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.306982865424793e-07</v>
+        <v>2.306982865424791e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.797680236825569e-07</v>
+        <v>2.797680236825564e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.284056625927921e-07</v>
+        <v>2.28405662592792e-07</v>
       </c>
       <c r="G7" t="n">
         <v>2.303565125077983e-07</v>
@@ -2716,16 +2716,16 @@
         <v>2.306982040274551e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.28405646224141e-07</v>
+        <v>2.284056462241411e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.306982040274551e-07</v>
+        <v>2.30698204027455e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.746535812363585e-07</v>
+        <v>2.049096295925802e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.306982040274551e-07</v>
+        <v>2.30698204027455e-07</v>
       </c>
     </row>
     <row r="8">
@@ -2735,37 +2735,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.649893865028326e-08</v>
+        <v>9.649893865028339e-08</v>
       </c>
       <c r="C8" t="n">
         <v>2.431244566324228e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.802998199430641e-08</v>
+        <v>1.802998199430649e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.935060622987183e-08</v>
+        <v>3.935060622987188e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.935060622987183e-08</v>
+        <v>3.935060622987188e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.931449686863253e-08</v>
+        <v>2.931449686863259e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>6.062614012199734e-08</v>
+        <v>6.062614012199741e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.935060622987183e-08</v>
+        <v>3.935060622987188e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>3.854231427555201e-08</v>
+        <v>3.8542314275552e-08</v>
       </c>
       <c r="K8" t="n">
         <v>1.01013277252604e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.214109054349938e-08</v>
+        <v>5.214109054349939e-08</v>
       </c>
     </row>
     <row r="9">
@@ -2775,37 +2775,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.621276371985651e-08</v>
+        <v>9.621276371985654e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.499461585054236e-08</v>
+        <v>2.499461585054237e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>4.680695720247915e-08</v>
+        <v>4.680695720247914e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>4.104981472351887e-08</v>
+        <v>4.104981472351884e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.104981472351887e-08</v>
+        <v>4.104981472351884e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.31073685261299e-08</v>
+        <v>4.310736852612991e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.416214920275692e-08</v>
+        <v>6.416214920275694e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.104981472351887e-08</v>
+        <v>4.104981472351884e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.060043779594233e-08</v>
+        <v>5.06004377959423e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.02222010652408e-07</v>
+        <v>1.022220106524079e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>5.564983825707914e-08</v>
+        <v>5.564983825707918e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2891,37 +2891,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.023248337249541e-07</v>
+        <v>1.023248337249542e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.100358726570035e-07</v>
+        <v>1.100358726570036e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.539709852106311e-07</v>
+        <v>1.539709852106313e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.901093754983892e-07</v>
+        <v>1.901093754983884e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.901093754983892e-07</v>
+        <v>1.901093754983884e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.791405198082812e-07</v>
+        <v>1.791405198082798e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.776064410510907e-07</v>
+        <v>1.776064410510904e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.901093754983892e-07</v>
+        <v>1.901093754983884e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>6.665907946515702e-07</v>
+        <v>6.665907946515706e-07</v>
       </c>
       <c r="K2" t="n">
         <v>1.298319342049669e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.968166064252031e-07</v>
+        <v>1.968166064252032e-07</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.98771178807979e-08</v>
+        <v>4.987711788079796e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.747576497531779e-08</v>
+        <v>4.747576497531786e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>4.98771178807979e-08</v>
+        <v>4.987711788079796e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.721357849295155e-08</v>
+        <v>4.721357849295159e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.721357849295155e-08</v>
+        <v>4.721357849295159e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>4.947042866104474e-08</v>
+        <v>4.94704286610448e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>4.98771178807979e-08</v>
+        <v>4.987711788079796e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.714111838987814e-08</v>
+        <v>4.714111838987816e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>4.98771178807979e-08</v>
+        <v>4.987711788079796e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>4.98771178807979e-08</v>
+        <v>4.987711788079796e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>4.98771178807979e-08</v>
+        <v>4.987711788079796e-08</v>
       </c>
     </row>
     <row r="4">
@@ -2971,37 +2971,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.062790162026408e-08</v>
+        <v>4.062790162026407e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.990187300539395e-08</v>
+        <v>3.990187300539363e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.073574294318836e-08</v>
+        <v>7.935180757439641e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.70626074398575e-08</v>
+        <v>3.70626074398574e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.793832937205925e-08</v>
+        <v>3.793832937205919e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>7.707331122695834e-08</v>
+        <v>4.022121240051097e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.606383554601589e-08</v>
+        <v>8.606383554601551e-08</v>
       </c>
       <c r="I4" t="n">
         <v>7.474400095579171e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.159186579318084e-08</v>
+        <v>7.917638298077978e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.030518430816244e-08</v>
+        <v>4.030518430816234e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.063958370606565e-08</v>
+        <v>4.063958370606556e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.944158339081233e-08</v>
+        <v>7.944158339081244e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.946409599471039e-08</v>
+        <v>7.946409599471044e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.943507820906379e-08</v>
+        <v>7.94350782090638e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.684605723895676e-08</v>
+        <v>7.684605723895671e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.684605723895676e-08</v>
+        <v>7.684605723895671e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.903489417105942e-08</v>
+        <v>7.903489417105937e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.944158339081233e-08</v>
+        <v>7.944158339081244e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.670558389989269e-08</v>
+        <v>7.67055838998928e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.944158339081233e-08</v>
+        <v>7.944158339081244e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.944158339081233e-08</v>
+        <v>7.944158339081244e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.944158339081233e-08</v>
+        <v>7.944158339081244e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3054,25 +3054,25 @@
         <v>1.299678979123565e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.969659778998497e-07</v>
+        <v>1.969659778975277e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.106429689854236e-07</v>
+        <v>2.10642968985424e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.759143228404527e-07</v>
+        <v>1.759143228404528e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.294376561679357e-07</v>
+        <v>1.294376561679356e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.963808018369659e-07</v>
+        <v>1.963808018369662e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.967874910573528e-07</v>
+        <v>1.96787491057353e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.94051491565799e-07</v>
+        <v>1.940514915657997e-07</v>
       </c>
       <c r="J6" t="n">
         <v>1.96800623016759e-07</v>
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.465741113156579e-07</v>
+        <v>1.465741113156581e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.802725736276548e-07</v>
+        <v>1.802725736276547e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.802501095507092e-07</v>
+        <v>1.802501095507091e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.163754566132559e-07</v>
+        <v>2.163754566132561e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.775140769691647e-07</v>
+        <v>1.77514076969165e-07</v>
       </c>
       <c r="G7" t="n">
         <v>1.798433718040037e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.802500610237565e-07</v>
+        <v>1.802500610237566e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.77514061532837e-07</v>
+        <v>1.775140615328372e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.802500610237565e-07</v>
+        <v>1.802500610237566e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.378460166283581e-07</v>
+        <v>1.607381039174713e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.802500610237565e-07</v>
+        <v>1.802500610237566e-07</v>
       </c>
     </row>
     <row r="8">
@@ -3131,37 +3131,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.585942084726628e-08</v>
+        <v>9.585942084726616e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.259932102590836e-08</v>
+        <v>2.259932102590835e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>6.342495566467967e-08</v>
+        <v>6.342495566467972e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.805139830342903e-08</v>
+        <v>3.805139830342909e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.805139830342903e-08</v>
+        <v>3.805139830342909e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.799803515845466e-08</v>
+        <v>4.799803515845464e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>6.324746752957879e-08</v>
+        <v>6.324746752957876e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.805139830342903e-08</v>
+        <v>3.805139830342909e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.260509289239956e-08</v>
+        <v>4.260509289239975e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.011858343440756e-07</v>
+        <v>1.011858343440749e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.374998403902576e-08</v>
+        <v>5.374998403902574e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3171,37 +3171,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.525862031810542e-08</v>
+        <v>9.525862031810546e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.320192422798024e-08</v>
+        <v>2.320192422798033e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>6.382868174961357e-08</v>
+        <v>6.382868174961359e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.93677262793229e-08</v>
+        <v>3.936772627932294e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.93677262793229e-08</v>
+        <v>3.936772627932294e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.894997529848863e-08</v>
+        <v>4.894997529848855e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.375880271968e-08</v>
+        <v>6.375880271968007e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.93677262793229e-08</v>
+        <v>3.936772627932294e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.011053256362656e-08</v>
+        <v>5.01105325636267e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.006532513530796e-07</v>
+        <v>1.00653251353079e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>5.460831779931896e-08</v>
+        <v>5.460831779931893e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.001830400408553e-07</v>
+        <v>1.00183040040855e-07</v>
       </c>
       <c r="C2" t="n">
         <v>1.12155595128191e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.513079827743597e-07</v>
+        <v>1.513079827743596e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.598512405416855e-07</v>
+        <v>1.59851240541686e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.598512405416855e-07</v>
+        <v>1.59851240541686e-07</v>
       </c>
       <c r="G2" t="n">
         <v>1.419087778284487e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.639482821063558e-07</v>
+        <v>1.639482821063557e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.598512405416855e-07</v>
+        <v>1.59851240541686e-07</v>
       </c>
       <c r="J2" t="n">
         <v>4.93284478771414e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.196361164240533e-07</v>
+        <v>1.196361164240528e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.655726388933615e-07</v>
+        <v>1.655726388933614e-07</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.067503295666484e-08</v>
+        <v>5.067503295666443e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.889338858515399e-08</v>
+        <v>4.8893388585154e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.067503295666484e-08</v>
+        <v>5.067503295666443e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.72167755565902e-08</v>
+        <v>4.721677555659023e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.721677555659029e-08</v>
+        <v>4.721677555659023e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.031086350306755e-08</v>
+        <v>5.031086350306292e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.067503295666484e-08</v>
+        <v>5.067503295666443e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.822288371029189e-08</v>
+        <v>4.822288371028779e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.067503295666484e-08</v>
+        <v>5.067503295666443e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.067503295666484e-08</v>
+        <v>5.067503295666443e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.067503295666484e-08</v>
+        <v>5.067503295666443e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.870311915163403e-08</v>
+        <v>7.870311915163364e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.094214461190429e-08</v>
+        <v>4.094214461190412e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.154955693188221e-08</v>
+        <v>4.154955693188209e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.813343318683254e-08</v>
+        <v>3.813343318683268e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.912320009626155e-08</v>
+        <v>3.912320009626188e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>7.833894969803311e-08</v>
+        <v>7.833894969803315e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.826041985636093e-08</v>
+        <v>4.155619903954523e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.909245579706097e-08</v>
+        <v>7.625096990525686e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>8.051882831397811e-08</v>
+        <v>4.248708513391592e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.126873362224433e-08</v>
+        <v>4.126873362224431e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.154498536227782e-08</v>
+        <v>4.154498536227719e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.017906860262544e-08</v>
+        <v>8.017906860262552e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.020252729241371e-08</v>
+        <v>8.020252729241389e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.017254895498008e-08</v>
+        <v>8.017254895498012e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.784075377309763e-08</v>
+        <v>7.784075377309767e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.784075377309763e-08</v>
+        <v>7.784075377309767e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.981489914902471e-08</v>
+        <v>7.981489914902454e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.017906860262544e-08</v>
+        <v>8.017906860262552e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.772691935624859e-08</v>
+        <v>7.772691935624864e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.017906860262544e-08</v>
+        <v>8.017906860262552e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.017906860262544e-08</v>
+        <v>8.017906860262552e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.017906860262544e-08</v>
+        <v>8.017906860262552e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.309251456377321e-07</v>
+        <v>1.309251456377319e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.980535309040561e-07</v>
+        <v>1.980535309067919e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.117870461750662e-07</v>
+        <v>2.117870461750657e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.77245111983802e-07</v>
+        <v>1.772451119838022e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.306677764594149e-07</v>
+        <v>1.306677764594148e-07</v>
       </c>
       <c r="G6" t="n">
         <v>1.975353119108923e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.978994813656172e-07</v>
+        <v>1.97899481365617e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.954473321181159e-07</v>
+        <v>1.954473321181158e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.979126437326004e-07</v>
+        <v>1.979126437326e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.296810629638868e-07</v>
+        <v>1.296810629638865e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.678597753358447e-07</v>
+        <v>2.678597753358449e-07</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.402696315508948e-07</v>
+        <v>1.40269631550895e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.72028125670779e-07</v>
+        <v>1.720281256707793e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.72004714442218e-07</v>
+        <v>1.720047144422182e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.061741374759294e-07</v>
+        <v>2.061741374759298e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.695525328086009e-07</v>
+        <v>1.69552532808601e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.716404975273899e-07</v>
+        <v>1.716404975273901e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.720046669809906e-07</v>
+        <v>1.720046669809905e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.695525177346142e-07</v>
+        <v>1.695525177346139e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.720046669809906e-07</v>
+        <v>1.720046669809905e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.528712814524274e-07</v>
+        <v>1.536172827816996e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.720046669809906e-07</v>
+        <v>1.720046669809905e-07</v>
       </c>
     </row>
     <row r="8">
@@ -3527,37 +3527,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.722668310341747e-08</v>
+        <v>9.722668310341742e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.243419166462538e-08</v>
+        <v>2.243419166462542e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>6.333650715823843e-08</v>
+        <v>6.333650715823837e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.830599364229887e-08</v>
+        <v>3.83059936422989e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.830599364229887e-08</v>
+        <v>3.83059936422989e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.866277883544917e-08</v>
+        <v>4.866277883544905e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>6.338594527490613e-08</v>
+        <v>6.338594527490598e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.830599364229887e-08</v>
+        <v>3.83059936422989e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.540634966080817e-08</v>
+        <v>4.540634966080819e-08</v>
       </c>
       <c r="K8" t="n">
         <v>1.011185774782375e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.422584840317499e-08</v>
+        <v>5.422584840317511e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3567,37 +3567,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.656535821737293e-08</v>
+        <v>9.656535821737301e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.305766025852525e-08</v>
+        <v>2.305766025852528e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>6.369345900896276e-08</v>
+        <v>6.369345900896296e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.918211536513537e-08</v>
+        <v>3.918211536513538e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.918211536513537e-08</v>
+        <v>3.918211536513538e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.908437344400042e-08</v>
+        <v>4.908437344400027e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.371572061594362e-08</v>
+        <v>6.371572061594352e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.918211536513537e-08</v>
+        <v>3.918211536513538e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.053962744647149e-08</v>
+        <v>5.053962744647162e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.004334612313291e-07</v>
+        <v>1.00433461231329e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>5.46865818576626e-08</v>
+        <v>5.468658185766244e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.227362748174465e-07</v>
+        <v>1.227362748174471e-07</v>
       </c>
       <c r="C2" t="n">
         <v>1.189065703227136e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>4.266127296845121e-07</v>
+        <v>4.266127296845137e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>2.192598099246532e-07</v>
+        <v>2.192598099246536e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.192598099246532e-07</v>
+        <v>2.192598099246536e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>4.885836228001161e-07</v>
+        <v>4.885836228001124e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>3.823455434106083e-07</v>
+        <v>3.823455434106101e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>2.192598099246532e-07</v>
+        <v>2.192598099246536e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>8.912787726321676e-07</v>
+        <v>8.912787726321672e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.72780775228666e-07</v>
+        <v>1.727807752286674e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>3.923162837531182e-07</v>
+        <v>3.923162837531198e-07</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.162290703509128e-08</v>
+        <v>5.162290703509224e-08</v>
       </c>
       <c r="C3" t="n">
         <v>4.760142708227327e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.162290703509128e-08</v>
+        <v>5.162290703509224e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.643567113708029e-08</v>
+        <v>4.643567113708026e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.643567113708029e-08</v>
+        <v>4.643567113708026e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.130460981095096e-08</v>
+        <v>5.130460981095087e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.162290703509128e-08</v>
+        <v>5.162290703509224e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.947933372122871e-08</v>
+        <v>4.947933372122877e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.162290703509128e-08</v>
+        <v>5.162290703509224e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.162290703509128e-08</v>
+        <v>5.162290703509224e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.162290703509128e-08</v>
+        <v>5.162290703509224e-08</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.219656546407286e-08</v>
+        <v>4.219656546407438e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.091750946320807e-08</v>
+        <v>4.091750946320765e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.251141582522648e-08</v>
+        <v>4.251141582522722e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.855915080071287e-08</v>
+        <v>3.855915080071279e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.005196759663782e-08</v>
+        <v>4.005196759663763e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>8.234229712758095e-08</v>
+        <v>4.187826823993305e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.1509012907075e-08</v>
+        <v>9.15090129070758e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>8.051702103785938e-08</v>
+        <v>4.005299215021073e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>8.467587427836555e-08</v>
+        <v>4.330793549013562e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.16017004673744e-08</v>
+        <v>4.160170046737533e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.226313257378978e-08</v>
+        <v>4.226313257379024e-08</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.416509231158649e-08</v>
+        <v>8.416509231158724e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.417457625524416e-08</v>
+        <v>8.417457625524411e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.415820369501564e-08</v>
+        <v>8.415820369501657e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.214865515403504e-08</v>
+        <v>8.214865515403499e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.214865515403504e-08</v>
+        <v>8.214865515403499e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.384679508744528e-08</v>
+        <v>8.384679508744618e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.416509231158649e-08</v>
+        <v>8.416509231158724e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.202151899772349e-08</v>
+        <v>8.202151899772346e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.416509231158649e-08</v>
+        <v>8.416509231158724e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.416509231158649e-08</v>
+        <v>8.416509231158724e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.416509231158649e-08</v>
+        <v>8.416509231158724e-08</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.384813047414017e-07</v>
+        <v>1.384813047414026e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.109362112828322e-07</v>
+        <v>2.10936211280496e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.257739562848737e-07</v>
+        <v>2.257739562848744e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.889920791207444e-07</v>
+        <v>1.889920791207445e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.387095024312647e-07</v>
+        <v>1.387095024312648e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.104636498722205e-07</v>
+        <v>2.104636498722218e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.107819470966562e-07</v>
+        <v>2.107819470966565e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.086383737824985e-07</v>
+        <v>2.086383737824986e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.107961562397698e-07</v>
+        <v>2.107961562397707e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.371382831876576e-07</v>
+        <v>1.37138283187658e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.863060137200385e-07</v>
+        <v>2.863060137200394e-07</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.689979481507089e-07</v>
+        <v>1.689979481507096e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.089160171283163e-07</v>
+        <v>2.08916017128316e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.089065925898271e-07</v>
+        <v>2.089065925898281e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.528166928331359e-07</v>
+        <v>2.528166928331353e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.067629745354665e-07</v>
+        <v>2.067629745354662e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.085882359605175e-07</v>
+        <v>2.085882359605178e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.089065331846588e-07</v>
+        <v>2.089065331846592e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.067629598707957e-07</v>
+        <v>2.067629598707952e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.089065331846588e-07</v>
+        <v>2.089065331846592e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.85783367268463e-07</v>
+        <v>1.857833672684631e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.089065331846588e-07</v>
+        <v>2.089065331846592e-07</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.616960241481242e-08</v>
+        <v>9.616960241481308e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>2.344457726571741e-08</v>
+        <v>2.344457726571739e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.82385704038997e-08</v>
+        <v>5.823857040389997e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.839566365689301e-08</v>
+        <v>3.839566365689299e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.839566365689301e-08</v>
+        <v>3.839566365689299e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.239139521496779e-08</v>
+        <v>4.239139521496821e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>6.019617355133787e-08</v>
+        <v>6.019617355133824e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.839566365689301e-08</v>
+        <v>3.839566365689299e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>3.976471979067908e-08</v>
+        <v>3.976471979067894e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.014019123895939e-07</v>
+        <v>1.014019123895945e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.134448119477186e-08</v>
+        <v>5.134448119477221e-08</v>
       </c>
     </row>
     <row r="9">
@@ -3963,37 +3963,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>9.577610190283895e-08</v>
+        <v>9.57761019028399e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>2.408952391925167e-08</v>
+        <v>2.408952391925166e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>6.226558081606785e-08</v>
+        <v>6.22655808160684e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.995999878226978e-08</v>
+        <v>3.995999878226977e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.995999878226978e-08</v>
+        <v>3.995999878226977e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.732671556716866e-08</v>
+        <v>4.732671556716872e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.306888318082885e-08</v>
+        <v>6.306888318082959e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.995999878226978e-08</v>
+        <v>3.995999878226977e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>4.9709945378659e-08</v>
+        <v>4.97099453786592e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.013606493365008e-07</v>
+        <v>1.013606493365011e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>5.438877760564928e-08</v>
+        <v>5.438877760564972e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4079,13 +4079,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.093762764317298e-07</v>
+        <v>1.093762764317297e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.122264383389446e-07</v>
+        <v>1.122264383389444e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.530767380113782e-07</v>
+        <v>1.530767380113777e-07</v>
       </c>
       <c r="E2" t="n">
         <v>1.850240857529553e-07</v>
@@ -4094,22 +4094,22 @@
         <v>1.850240857529553e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.481893750036602e-07</v>
+        <v>1.481893750036532e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.691205143770046e-07</v>
+        <v>1.691205143770042e-07</v>
       </c>
       <c r="I2" t="n">
         <v>1.850240857529553e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>6.795502139351485e-07</v>
+        <v>6.795502139351482e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.440315533290708e-07</v>
+        <v>1.440315533290705e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.78165412538686e-07</v>
+        <v>1.781654125386858e-07</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.978134825341888e-08</v>
+        <v>4.978134825341883e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.733596279418554e-08</v>
+        <v>4.733596279418545e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>4.978134825341888e-08</v>
+        <v>4.978134825341883e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.721269247639688e-08</v>
+        <v>4.721269247639687e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.72126924763969e-08</v>
+        <v>4.721269247639687e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>4.937502790006998e-08</v>
+        <v>4.937502790006995e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>4.978134825341888e-08</v>
+        <v>4.978134825341883e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.704755612992622e-08</v>
+        <v>4.704755612992626e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>4.978134825341888e-08</v>
+        <v>4.978134825341883e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>4.978134825341888e-08</v>
+        <v>4.978134825341883e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>4.978134825341888e-08</v>
+        <v>4.978134825341883e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4159,37 +4159,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.066996750756144e-08</v>
+        <v>7.741517145615333e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.997422576561396e-08</v>
+        <v>3.997422576561337e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.080982017738298e-08</v>
+        <v>4.081008803952631e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.713038165965293e-08</v>
+        <v>3.713038165965295e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.798718982894464e-08</v>
+        <v>3.798718982894441e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>4.026364715421253e-08</v>
+        <v>4.026364715421237e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.59590213025877e-08</v>
+        <v>8.595902130258754e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>7.468137933266104e-08</v>
+        <v>7.468137933266063e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>7.910152577038914e-08</v>
+        <v>4.163775017471686e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.04271261372886e-08</v>
+        <v>4.042712613728842e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.067142741301282e-08</v>
+        <v>4.067142741301268e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.888489392929806e-08</v>
+        <v>7.888489392929793e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.89087026971425e-08</v>
+        <v>7.890870269714235e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.887841346041328e-08</v>
+        <v>7.887841346041313e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.631487917604337e-08</v>
+        <v>7.631487917604324e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.631487917604337e-08</v>
+        <v>7.631487917604324e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.847857357594919e-08</v>
+        <v>7.847857357594905e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.888489392929806e-08</v>
+        <v>7.888489392929793e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.615110180580554e-08</v>
+        <v>7.615110180580543e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.888489392929806e-08</v>
+        <v>7.888489392929793e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.888489392929806e-08</v>
+        <v>7.888489392929793e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.888489392929806e-08</v>
+        <v>7.888489392929793e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.290261069888072e-07</v>
+        <v>1.290261069888069e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.954667253916934e-07</v>
+        <v>1.954667253916927e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.089998491826738e-07</v>
+        <v>2.089998491826729e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.745725213556116e-07</v>
+        <v>1.745725213556114e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.28493546866635e-07</v>
+        <v>1.284935468666349e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.948585000887307e-07</v>
+        <v>1.948585000887304e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.952648204426993e-07</v>
+        <v>1.952648204426987e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.925310283185871e-07</v>
+        <v>1.925310283185868e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.952778382413049e-07</v>
+        <v>1.952778382413041e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.277956888767239e-07</v>
+        <v>1.277956888767236e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.644566954369518e-07</v>
+        <v>2.644566954369511e-07</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.456249423522774e-07</v>
+        <v>1.45624942352277e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.790698314578051e-07</v>
+        <v>1.790698314578047e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.790460702009387e-07</v>
+        <v>1.790460702009379e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.148795111305618e-07</v>
+        <v>2.148795111305613e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.763122462039557e-07</v>
+        <v>1.763122462039555e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.786397023366119e-07</v>
+        <v>1.786397023366114e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.790460226899606e-07</v>
+        <v>1.7904602268996e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.763122305664679e-07</v>
+        <v>1.763122305664677e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.790460226899606e-07</v>
+        <v>1.7904602268996e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.596817374705283e-07</v>
+        <v>1.369629045892557e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.790460226899606e-07</v>
+        <v>1.7904602268996e-07</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.027666620866105e-07</v>
+        <v>1.027666620866104e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>2.286513726043569e-08</v>
+        <v>2.286513726043568e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>6.319000012985813e-08</v>
+        <v>6.319000012985801e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.813791832997747e-08</v>
+        <v>3.813791832997739e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.813791832997747e-08</v>
+        <v>3.813791832997739e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>4.932796598865922e-08</v>
+        <v>4.932796598865919e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>6.317347635835305e-08</v>
+        <v>6.317347635835296e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.813791832997747e-08</v>
+        <v>3.813791832997739e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.205267644276228e-08</v>
+        <v>4.205267644276223e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.01333856023197e-07</v>
+        <v>1.013338560231964e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.392130999471515e-08</v>
+        <v>5.392130999471512e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4362,34 +4362,34 @@
         <v>1.021541023352768e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>2.349373583166148e-08</v>
+        <v>2.349373583166145e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>6.358580650618864e-08</v>
+        <v>6.358580650618859e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.93831658276147e-08</v>
+        <v>3.938316582761464e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.93831658276147e-08</v>
+        <v>3.938316582761464e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.983694152669785e-08</v>
+        <v>4.983694152669777e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.358131975784357e-08</v>
+        <v>6.35813197578435e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.93831658276147e-08</v>
+        <v>3.938316582761464e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>4.974105624047118e-08</v>
+        <v>4.9741056240471e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.009990495883463e-07</v>
+        <v>1.00999049588346e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>5.455051870662913e-08</v>
+        <v>5.455051870662907e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.045517597102552e-07</v>
+        <v>1.045517597102551e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.120880802422143e-07</v>
+        <v>1.120880802422139e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>1.486424718639445e-07</v>
+        <v>1.486424718639444e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>1.602233677194293e-07</v>
+        <v>1.60223367719429e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.602233677194293e-07</v>
+        <v>1.60223367719429e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.423011942901592e-07</v>
+        <v>1.42301194290159e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>1.640857020488912e-07</v>
+        <v>1.640857020488908e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>1.602233677194293e-07</v>
+        <v>1.60223367719429e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>4.977464822505853e-07</v>
+        <v>4.977464822505849e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>1.361668700297879e-07</v>
+        <v>1.361668700297881e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.660452078642488e-07</v>
+        <v>1.660452078642489e-07</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.067575311114649e-08</v>
+        <v>5.067575311114652e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.879059450894712e-08</v>
+        <v>4.879059450894706e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.067575311114649e-08</v>
+        <v>5.067575311114652e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.721612287098866e-08</v>
+        <v>4.721612287098855e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.721612287098868e-08</v>
+        <v>4.721612287098856e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.030978228397973e-08</v>
+        <v>5.03097822839797e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.067575311114649e-08</v>
+        <v>5.067575311114652e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.821173431145134e-08</v>
+        <v>4.821173431145123e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.067575311114649e-08</v>
+        <v>5.067575311114652e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.067575311114649e-08</v>
+        <v>5.067575311114652e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.067575311114649e-08</v>
+        <v>5.067575311114652e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4555,37 +4555,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.174221718875864e-08</v>
+        <v>7.899880417969121e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.111479249240774e-08</v>
+        <v>4.111479249240773e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.175387740247925e-08</v>
+        <v>4.175360762882951e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.829637599148663e-08</v>
+        <v>3.829637599148661e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.930853556735617e-08</v>
+        <v>3.930853556735618e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>7.86328333525241e-08</v>
+        <v>4.137624636159182e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.85125239758125e-08</v>
+        <v>8.851252397581256e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>7.653478537999577e-08</v>
+        <v>3.927819838906343e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.267539711137778e-08</v>
+        <v>8.080716278664068e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.151791359903884e-08</v>
+        <v>4.151791359903878e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.174337176085572e-08</v>
+        <v>4.174337176085609e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.982652642884781e-08</v>
+        <v>7.982652642884782e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.984950006813114e-08</v>
+        <v>7.98495000681311e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.982003811098105e-08</v>
+        <v>7.982003811098141e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.748134467696708e-08</v>
+        <v>7.748134467696702e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.748134467696708e-08</v>
+        <v>7.748134467696702e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.946055560168091e-08</v>
+        <v>7.946055560168108e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.982652642884781e-08</v>
+        <v>7.982652642884782e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.736250762915265e-08</v>
+        <v>7.736250762915256e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.982652642884781e-08</v>
+        <v>7.982652642884782e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.982652642884781e-08</v>
+        <v>7.982652642884782e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.982652642884781e-08</v>
+        <v>7.982652642884782e-08</v>
       </c>
     </row>
     <row r="6">
@@ -4638,34 +4638,34 @@
         <v>1.303065004677609e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.970440103110802e-07</v>
+        <v>1.970440103083444e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.106914369029929e-07</v>
+        <v>2.106914369029926e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.763317709836501e-07</v>
+        <v>1.763317709836495e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.300277049394184e-07</v>
+        <v>1.300277049394182e-07</v>
       </c>
       <c r="G6" t="n">
         <v>1.965198170975734e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.968857879258508e-07</v>
+        <v>1.968857879258506e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.944217691250449e-07</v>
+        <v>1.944217691250446e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.968988726528568e-07</v>
+        <v>1.968988726528563e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.290697560184939e-07</v>
+        <v>1.290697560184937e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.664334209433346e-07</v>
+        <v>2.664334209433344e-07</v>
       </c>
     </row>
     <row r="7">
@@ -4675,28 +4675,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.400678749335833e-07</v>
+        <v>1.400678749335832e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.717692304704786e-07</v>
+        <v>1.717692304704784e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.717463043056903e-07</v>
+        <v>1.7174630430569e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.058384812692892e-07</v>
+        <v>2.058384812692889e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.692822534732609e-07</v>
+        <v>1.692822534732608e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.713802860040283e-07</v>
+        <v>1.713802860040282e-07</v>
       </c>
       <c r="H7" t="n">
         <v>1.717462568311952e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.692822380315001e-07</v>
+        <v>1.692822380314997e-07</v>
       </c>
       <c r="J7" t="n">
         <v>1.717462568311952e-07</v>
@@ -4715,37 +4715,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.226113046498163e-07</v>
+        <v>1.226113046498165e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>2.299365169181235e-08</v>
+        <v>2.299365169181234e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>6.326156558507471e-08</v>
+        <v>6.326156558507476e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.825720324387168e-08</v>
+        <v>3.825720324387161e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.825720324387168e-08</v>
+        <v>3.825720324387161e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.101129802349965e-08</v>
+        <v>5.101129802349958e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>6.324305549218821e-08</v>
+        <v>6.324305549218837e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.825720324387168e-08</v>
+        <v>3.825720324387161e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.513781322319213e-08</v>
+        <v>4.513781322319226e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>1.010842988015418e-07</v>
+        <v>1.01084298801542e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.407516294090691e-08</v>
+        <v>5.407516294090689e-08</v>
       </c>
     </row>
     <row r="9">
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1.216125130228671e-07</v>
+        <v>1.216125130228672e-07</v>
       </c>
       <c r="C9" t="n">
         <v>2.360740274912364e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>6.35827620084384e-08</v>
+        <v>6.358276200843842e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.914000670721945e-08</v>
+        <v>3.91400067072194e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.914000670721945e-08</v>
+        <v>3.91400067072194e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.140208459683694e-08</v>
+        <v>5.140208459683698e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.357735369441529e-08</v>
+        <v>6.357735369441526e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.914000670721945e-08</v>
+        <v>3.91400067072194e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.033556961331066e-08</v>
+        <v>5.033556961331077e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>1.006321112781055e-07</v>
+        <v>1.006321112781056e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>5.454458947966178e-08</v>
+        <v>5.454458947966194e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.341837292572497e-07</v>
+        <v>3.341837292572536e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.743915809930685e-07</v>
+        <v>2.743915809930676e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>7.175064273197396e-06</v>
+        <v>7.17506427319739e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>2.743915809930685e-07</v>
+        <v>2.743915809930676e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.743915809930685e-07</v>
+        <v>2.743915809930676e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>3.744213244059109e-06</v>
+        <v>3.744213244059114e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>7.39897148680367e-07</v>
+        <v>7.398971486803651e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>2.743915809930685e-07</v>
+        <v>2.743915809930676e-07</v>
       </c>
       <c r="J2" t="n">
         <v>1.051700586331189e-06</v>
       </c>
       <c r="K2" t="n">
-        <v>5.415060926222118e-07</v>
+        <v>5.415060926222116e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>4.824037088658689e-07</v>
+        <v>4.824037088658687e-07</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.70805149056867e-08</v>
+        <v>5.708051490568686e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.903636380012859e-08</v>
+        <v>4.903636380012861e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.70805149056867e-08</v>
+        <v>5.708051490568686e-08</v>
       </c>
       <c r="E3" t="n">
         <v>5.022531758062952e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.022531758062951e-08</v>
+        <v>5.022531758062952e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.661627283992012e-08</v>
+        <v>5.661627283992013e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.70805149056867e-08</v>
+        <v>5.708051490568686e-08</v>
       </c>
       <c r="I3" t="n">
         <v>5.39940866071953e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.70805149056867e-08</v>
+        <v>5.708051490568686e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.70805149056867e-08</v>
+        <v>5.708051490568686e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.70805149056867e-08</v>
+        <v>5.708051490568686e-08</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.103134727460201e-07</v>
+        <v>5.403868183201082e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.547764588722823e-08</v>
+        <v>4.54776458872284e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.405640199333379e-08</v>
+        <v>6.405657244387115e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>4.489084153012528e-08</v>
+        <v>4.48908415301253e-08</v>
       </c>
       <c r="F4" t="n">
         <v>5.043407685297167e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.098492306802536e-07</v>
+        <v>5.357443976624415e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.154838216815642e-07</v>
+        <v>1.154838216815643e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.072270444475287e-07</v>
+        <v>1.072270444475289e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.129297141988516e-07</v>
+        <v>5.565741469572436e-08</v>
       </c>
       <c r="K4" t="n">
         <v>5.011784770370821e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.433090206823977e-08</v>
+        <v>5.433090206823987e-08</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.007369300270199e-07</v>
+        <v>1.007369300270198e-07</v>
       </c>
       <c r="C5" t="n">
-        <v>9.765050172852845e-08</v>
+        <v>9.765050172852843e-08</v>
       </c>
       <c r="D5" t="n">
         <v>1.00729319840299e-07</v>
       </c>
       <c r="E5" t="n">
-        <v>9.754465618016431e-08</v>
+        <v>9.754465618016432e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>9.754465618016431e-08</v>
+        <v>9.754465618016432e-08</v>
       </c>
       <c r="G5" t="n">
         <v>1.002726879612532e-07</v>
       </c>
       <c r="H5" t="n">
-        <v>1.007369300270199e-07</v>
+        <v>1.007369300270198e-07</v>
       </c>
       <c r="I5" t="n">
-        <v>9.765050172852845e-08</v>
+        <v>9.765050172852843e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.007369300270199e-07</v>
+        <v>1.007369300270198e-07</v>
       </c>
       <c r="K5" t="n">
-        <v>1.007369300270199e-07</v>
+        <v>1.007369300270198e-07</v>
       </c>
       <c r="L5" t="n">
-        <v>1.007369300270199e-07</v>
+        <v>1.007369300270198e-07</v>
       </c>
     </row>
     <row r="6">
@@ -5034,34 +5034,34 @@
         <v>1.633074026762552e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.466642534666864e-07</v>
+        <v>2.466642534687652e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.677649908340925e-07</v>
+        <v>2.677649908340922e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.230080407234046e-07</v>
+        <v>2.230080407234044e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.629048465507622e-07</v>
+        <v>1.629048465507621e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.493607607660384e-07</v>
+        <v>2.493607607660383e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.498250028317815e-07</v>
+        <v>2.498250028317814e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.467385745333136e-07</v>
+        <v>2.467385745333135e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.498420060106144e-07</v>
+        <v>2.498420060106142e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.617002938331747e-07</v>
+        <v>1.617002938331745e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.40199870675049e-07</v>
+        <v>3.401998706750486e-07</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.536637237231949e-07</v>
+        <v>2.536637237231948e-07</v>
       </c>
       <c r="C7" t="n">
         <v>3.132227195178387e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>3.163093162580335e-07</v>
+        <v>3.163093162580337e-07</v>
       </c>
       <c r="E7" t="n">
         <v>3.855143860501478e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>3.132227380447554e-07</v>
+        <v>3.132227380447555e-07</v>
       </c>
       <c r="G7" t="n">
         <v>3.158449057505634e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>3.163091478163303e-07</v>
+        <v>3.163091478163302e-07</v>
       </c>
       <c r="I7" t="n">
         <v>3.132227195178387e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>3.163091478163303e-07</v>
+        <v>3.163091478163302e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.80012213915126e-07</v>
+        <v>2.800122139151261e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>3.163091478163303e-07</v>
+        <v>3.163091478163302e-07</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.272022290944938e-08</v>
+        <v>6.27202229094495e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.579018799153194e-08</v>
+        <v>4.57901879915319e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>-9.567683112520695e-08</v>
+        <v>-9.56768311252067e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.579018799153194e-08</v>
+        <v>4.57901879915319e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>4.579018799153194e-08</v>
+        <v>4.57901879915319e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.493545116431358e-08</v>
+        <v>-1.493545116431378e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.529448651223872e-08</v>
+        <v>5.529448651223884e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.579018799153194e-08</v>
+        <v>4.57901879915319e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.756449117548124e-08</v>
+        <v>4.756449117548126e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.800130741289497e-08</v>
+        <v>5.800130741289512e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>6.038249559099624e-08</v>
+        <v>6.038249559099635e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5154,34 +5154,34 @@
         <v>6.540964139405293e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>4.806410406091122e-08</v>
+        <v>4.806410406091119e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>8.998984614086397e-10</v>
+        <v>8.998984614087457e-10</v>
       </c>
       <c r="E9" t="n">
-        <v>4.806410406091122e-08</v>
+        <v>4.806410406091119e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.806410406091122e-08</v>
+        <v>4.806410406091119e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.334318229953849e-08</v>
+        <v>3.334318229953845e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.239796835809114e-08</v>
+        <v>6.239796835809115e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.806410406091122e-08</v>
+        <v>4.806410406091119e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.924499551473505e-08</v>
+        <v>5.924499551473516e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.348824040150716e-08</v>
+        <v>6.348824040150717e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.446395006275785e-08</v>
+        <v>6.004165672374655e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.354753810628174e-07</v>
+        <v>2.354753810628175e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.636150955602728e-07</v>
+        <v>2.636150955602723e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>6.094988997790051e-06</v>
+        <v>6.094988997790073e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>2.636150955602728e-07</v>
+        <v>2.636150955602723e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.636150955602728e-07</v>
+        <v>2.636150955602723e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>3.360796403415842e-06</v>
+        <v>3.360796403415851e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>6.27273942972235e-07</v>
+        <v>6.272739429722324e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>2.636150955602728e-07</v>
+        <v>2.636150955602723e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>7.95729399371431e-07</v>
+        <v>7.957293993714327e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>4.778667664144548e-07</v>
+        <v>4.778667664144549e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>5.516244298327436e-07</v>
+        <v>5.516244298327425e-07</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.473054962707765e-08</v>
+        <v>5.473054962707794e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.842325102806611e-08</v>
+        <v>4.842325102806614e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.473054962707766e-08</v>
+        <v>5.473054962707789e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.9458141394287e-08</v>
+        <v>4.945814139428703e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.945814139428701e-08</v>
+        <v>4.945814139428705e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.429761458391017e-08</v>
+        <v>5.429761458391053e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.473054962707766e-08</v>
+        <v>5.473054962707789e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.185154927503719e-08</v>
+        <v>5.185154927503721e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.473054962707766e-08</v>
+        <v>5.473054962707789e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.473054962707766e-08</v>
+        <v>5.473054962707789e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.473054962707766e-08</v>
+        <v>5.473054962707789e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5347,37 +5347,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1.040590941199275e-07</v>
+        <v>5.197927044348811e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.422501505293198e-08</v>
+        <v>4.4225015052932e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.039905003636292e-08</v>
+        <v>6.039905003636657e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>4.36568238655445e-08</v>
+        <v>4.365682386554454e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.860437185249967e-08</v>
+        <v>4.860437185249986e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>1.036261590767602e-07</v>
+        <v>5.15463354003205e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>1.084187021655168e-07</v>
+        <v>1.084187021655169e-07</v>
       </c>
       <c r="I4" t="n">
         <v>1.011800937678873e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.063586480080209e-07</v>
+        <v>5.33842883670887e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.836207657252293e-08</v>
+        <v>4.836207657252313e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.232871815881928e-08</v>
+        <v>5.232871815881931e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.425358606502051e-08</v>
+        <v>9.425358606502092e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>9.137458571297996e-08</v>
+        <v>9.137458571298002e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>9.424648871445406e-08</v>
+        <v>9.424648871445416e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>9.125525782474424e-08</v>
+        <v>9.125525782474427e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>9.125525782474424e-08</v>
+        <v>9.125525782474427e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>9.382065102185299e-08</v>
+        <v>9.382065102185307e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>9.425358606502051e-08</v>
+        <v>9.425358606502091e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>9.137458571297996e-08</v>
+        <v>9.137458571298002e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>9.425358606502051e-08</v>
+        <v>9.425358606502091e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>9.425358606502051e-08</v>
+        <v>9.425358606502091e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>9.425358606502051e-08</v>
+        <v>9.425358606502091e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.514803356863417e-07</v>
+        <v>1.514803356863422e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.275099288354525e-07</v>
+        <v>2.275099288354529e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.468590379723539e-07</v>
+        <v>2.468590379723543e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.059120302255489e-07</v>
+        <v>2.059120302255493e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.510384977418768e-07</v>
+        <v>1.510384977418771e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.300453611865416e-07</v>
+        <v>2.300453611865419e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.304782962296643e-07</v>
+        <v>2.304782962296647e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.275992958776688e-07</v>
+        <v>2.275992958776689e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.304938215827436e-07</v>
+        <v>2.304938215827445e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.500129080099898e-07</v>
+        <v>1.5001290800999e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.129982717144946e-07</v>
+        <v>3.129982717144951e-07</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.195913864167196e-07</v>
+        <v>2.195913864167202e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.699328323344828e-07</v>
+        <v>2.699328323344834e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.728119866215754e-07</v>
+        <v>2.728119866215755e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>3.31348260441177e-07</v>
+        <v>3.313482604411776e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.699328502649223e-07</v>
+        <v>2.699328502649229e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.723788976433559e-07</v>
+        <v>2.723788976433563e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.728118326865235e-07</v>
+        <v>2.728118326865243e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.699328323344828e-07</v>
+        <v>2.699328323344834e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.728118326865235e-07</v>
+        <v>2.728118326865243e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.05797751120126e-07</v>
+        <v>2.419757618494618e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.728118326865235e-07</v>
+        <v>2.728118326865243e-07</v>
       </c>
     </row>
     <row r="8">
@@ -5507,37 +5507,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.398976362672655e-08</v>
+        <v>6.39897636267267e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.49359762667851e-08</v>
+        <v>4.493597626678514e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>-8.425606442271888e-08</v>
+        <v>-8.425606442271906e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.49359762667851e-08</v>
+        <v>4.493597626678514e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>4.49359762667851e-08</v>
+        <v>4.493597626678514e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.354038242147001e-08</v>
+        <v>-1.354038242147016e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.600437404402968e-08</v>
+        <v>5.600437404402981e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.49359762667851e-08</v>
+        <v>4.493597626678514e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.120062542061675e-08</v>
+        <v>5.120062542061679e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.755088608411515e-08</v>
+        <v>5.755088608411535e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.740805446559483e-08</v>
+        <v>5.74080544655948e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.552496952103552e-08</v>
+        <v>6.552496952103557e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>4.734311947730594e-08</v>
+        <v>4.734311947730597e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.14943499353018e-09</v>
+        <v>5.149434993530028e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>4.734311947730594e-08</v>
+        <v>4.734311947730597e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.734311947730594e-08</v>
+        <v>4.734311947730597e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.352308853628755e-08</v>
+        <v>3.35230885362875e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.228404789824516e-08</v>
+        <v>6.228404789824522e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.734311947730594e-08</v>
+        <v>4.734311947730597e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>6.032257072354243e-08</v>
+        <v>6.032257072354248e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.290302611981451e-08</v>
+        <v>6.290302611981475e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>6.285243483162715e-08</v>
+        <v>5.97329054430464e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.123997817056794e-07</v>
+        <v>2.123997817056847e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.951342442699962e-07</v>
+        <v>2.951342442699999e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>5.011671275641505e-06</v>
+        <v>5.011671275641508e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>2.951342442699962e-07</v>
+        <v>2.951342442699999e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.951342442699962e-07</v>
+        <v>2.951342442699999e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>2.871572986309942e-06</v>
+        <v>2.87157298630995e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>5.97632385423179e-07</v>
+        <v>5.976323854231771e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>2.951342442699962e-07</v>
+        <v>2.951342442699999e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>5.019149751398596e-07</v>
+        <v>5.019149751398626e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>4.103965068834885e-07</v>
+        <v>4.103965068834804e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>8.303754349828152e-07</v>
+        <v>3.196448738298212e-07</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.415721722655998e-08</v>
+        <v>5.415721722656026e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.905293511181081e-08</v>
+        <v>4.905293511181093e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.415721722656e-08</v>
+        <v>5.415721722656025e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.003038269914338e-08</v>
+        <v>5.003038269914346e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.003038269914335e-08</v>
+        <v>5.003038269914342e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.37590061814407e-08</v>
+        <v>5.375900618144072e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.415721722656e-08</v>
+        <v>5.415721722656025e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.150466008238172e-08</v>
+        <v>5.150466008238184e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.415721722656e-08</v>
+        <v>5.415721722656025e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.415721722656e-08</v>
+        <v>5.415721722656025e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.415721722656e-08</v>
+        <v>5.415721722656025e-08</v>
       </c>
     </row>
     <row r="4">
@@ -5743,37 +5743,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.075332001722495e-08</v>
+        <v>5.075332001722527e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.397631622250545e-08</v>
+        <v>4.397631622250618e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>1.034958240325928e-07</v>
+        <v>5.767139834006181e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>4.341885110673814e-08</v>
+        <v>4.341885110673823e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.770655143440894e-08</v>
+        <v>4.77065514344089e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>5.03551089721058e-08</v>
+        <v>1.002745986171328e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.048513251119226e-07</v>
+        <v>1.048513251119231e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>9.80202525180735e-08</v>
+        <v>4.810076287304702e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>5.202475565891793e-08</v>
+        <v>1.027325433580553e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>4.75432896672322e-08</v>
+        <v>4.754328966723237e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.091773832542264e-08</v>
+        <v>5.091773832542276e-08</v>
       </c>
     </row>
     <row r="5">
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.216413264039703e-08</v>
+        <v>9.21641326403972e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.951157549621868e-08</v>
+        <v>8.951157549621883e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>9.215703966352123e-08</v>
+        <v>9.215703966352142e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.939523896342277e-08</v>
+        <v>8.939523896342285e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.939523896342277e-08</v>
+        <v>8.939523896342285e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>9.176592159527749e-08</v>
+        <v>9.176592159527766e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>9.216413264039698e-08</v>
+        <v>9.216413264039714e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.951157549621868e-08</v>
+        <v>8.951157549621883e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>9.216413264039698e-08</v>
+        <v>9.216413264039714e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>9.216413264039698e-08</v>
+        <v>9.216413264039714e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>9.216413264039698e-08</v>
+        <v>9.216413264039714e-08</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.476085115512156e-07</v>
+        <v>1.476085115512159e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.214630237697722e-07</v>
+        <v>2.214630237697725e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.400848302645739e-07</v>
+        <v>2.400848302645744e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.005223130278394e-07</v>
+        <v>2.005223130278398e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.473186982708327e-07</v>
+        <v>1.473186982708329e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.238043451074757e-07</v>
+        <v>2.238043451074761e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.24202556152548e-07</v>
+        <v>2.242025561525486e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.215499990084168e-07</v>
+        <v>2.215499990084172e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.242176090670749e-07</v>
+        <v>2.242176090670754e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.461857378476603e-07</v>
+        <v>1.461857378476607e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.042114404236275e-07</v>
+        <v>3.042114404236281e-07</v>
       </c>
     </row>
     <row r="7">
@@ -5866,34 +5866,34 @@
         <v>1.993082033744453e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.442911509677187e-07</v>
+        <v>2.44291150967719e-07</v>
       </c>
       <c r="D7" t="n">
         <v>2.469438459924834e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.992616588566088e-07</v>
+        <v>2.992616588566084e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.442911676209878e-07</v>
+        <v>2.442911676209882e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.465454970667785e-07</v>
+        <v>2.465454970667779e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.469437081118971e-07</v>
+        <v>2.469437081118969e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.442911509677187e-07</v>
+        <v>2.44291150967719e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.469437081118971e-07</v>
+        <v>2.469437081118969e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.193435675799921e-07</v>
+        <v>2.193435675799919e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.469437081118971e-07</v>
+        <v>2.469437081118969e-07</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.283252782029422e-08</v>
+        <v>6.283252782029427e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.268311924754129e-08</v>
+        <v>4.26831192475412e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>-6.318426971460051e-08</v>
+        <v>-6.318426971460047e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.268311924754129e-08</v>
+        <v>4.26831192475412e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>4.268311924754129e-08</v>
+        <v>4.26831192475412e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.9221684323496e-09</v>
+        <v>-4.922168432349335e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>5.457292522066069e-08</v>
+        <v>5.457292522066073e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.268311924754129e-08</v>
+        <v>4.26831192475412e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.63212002552054e-08</v>
+        <v>5.632120025520552e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.7223235880516e-08</v>
+        <v>5.722323588051622e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.02933800896561e-08</v>
+        <v>5.029338008965608e-08</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.405914295998572e-08</v>
+        <v>6.405914295998579e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>4.565828620378292e-08</v>
+        <v>4.565828620378301e-08</v>
       </c>
       <c r="D9" t="n">
         <v>1.273674679074043e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>4.565828620378292e-08</v>
+        <v>4.565828620378301e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.565828620378292e-08</v>
+        <v>4.565828620378301e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.608724314893656e-08</v>
+        <v>3.608724314893673e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>6.070627761051536e-08</v>
+        <v>6.070627761051543e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.565828620378292e-08</v>
+        <v>4.565828620378301e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>6.141105078944317e-08</v>
+        <v>6.141105078944322e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.177501140987312e-08</v>
+        <v>6.177501140987324e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>5.896439599886197e-08</v>
+        <v>5.896439599886198e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.23640750468628e-07</v>
+        <v>2.236407504686309e-07</v>
       </c>
       <c r="C2" t="n">
         <v>2.043781854830418e-07</v>
@@ -6074,22 +6074,22 @@
         <v>2.043781854830418e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>9.731014902652523e-07</v>
+        <v>9.731014902652515e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>3.780542697514775e-07</v>
+        <v>3.780542697514776e-07</v>
       </c>
       <c r="I2" t="n">
         <v>2.043781854830418e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>4.255508539246236e-07</v>
+        <v>4.255508539246241e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>3.767306759699546e-07</v>
+        <v>3.767306759699556e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>3.25486433262449e-06</v>
+        <v>3.254864332624493e-06</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.130304696422668e-08</v>
+        <v>5.130304696422687e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.585095511957498e-08</v>
+        <v>4.585095511957495e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.130304696422668e-08</v>
+        <v>5.130304696422687e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.68584039778811e-08</v>
+        <v>4.685840397788099e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.685840397788109e-08</v>
+        <v>4.685840397788101e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.093231664332294e-08</v>
+        <v>5.093231664332297e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.130304696422668e-08</v>
+        <v>5.130304696422687e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.881222704817552e-08</v>
+        <v>4.881222704817558e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.130304696422668e-08</v>
+        <v>5.130304696422687e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.130304696422668e-08</v>
+        <v>5.130304696422687e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.130304696422668e-08</v>
+        <v>5.130304696422687e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.351597415419478e-08</v>
+        <v>8.710236815605257e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.923139320590176e-08</v>
+        <v>3.923139320590187e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>8.892156884114624e-08</v>
+        <v>8.892156884114622e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.880335000359864e-08</v>
+        <v>3.880335000359866e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.085054759164495e-08</v>
+        <v>4.085054759164486e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>4.314524383329094e-08</v>
+        <v>8.673163783514883e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.162918033760588e-08</v>
+        <v>4.352581871580315e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>4.102515423814365e-08</v>
+        <v>8.46115482400013e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>8.853869022554285e-08</v>
+        <v>8.853869022554276e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.262116281607957e-08</v>
+        <v>4.262116281607962e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.446523389828706e-08</v>
+        <v>4.44652338982871e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.385377143420712e-08</v>
+        <v>8.385377143420711e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.136295151815603e-08</v>
+        <v>8.136295151815588e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.384619763440884e-08</v>
+        <v>8.384619763440891e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.132834271317385e-08</v>
+        <v>8.132834271317377e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.132834271317385e-08</v>
+        <v>8.132834271317377e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.348304111330331e-08</v>
+        <v>8.348304111330339e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.385377143420712e-08</v>
+        <v>8.385377143420711e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.136295151815603e-08</v>
+        <v>8.136295151815588e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.385377143420712e-08</v>
+        <v>8.385377143420711e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.385377143420712e-08</v>
+        <v>8.385377143420711e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.385377143420712e-08</v>
+        <v>8.385377143420711e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.367373478013124e-07</v>
+        <v>1.367373478013125e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.052718618109942e-07</v>
+        <v>2.052718618109944e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.225014384216045e-07</v>
+        <v>2.225014384216047e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.85843193921762e-07</v>
+        <v>1.858431939217621e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.364820874203524e-07</v>
+        <v>1.364820874203522e-07</v>
       </c>
       <c r="G6" t="n">
         <v>2.074012204310451e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.077719507519376e-07</v>
+        <v>2.077719507519375e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.052811308358977e-07</v>
+        <v>2.052811308358978e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0778591108219e-07</v>
+        <v>2.077859110821898e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.354178435798747e-07</v>
+        <v>1.354178435798745e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.819735333514089e-07</v>
+        <v>2.819735333514092e-07</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.833270832990441e-07</v>
+        <v>1.833270832990444e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.246388834142853e-07</v>
+        <v>2.246388834142855e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.271297747992273e-07</v>
+        <v>2.271297747992275e-07</v>
       </c>
       <c r="E7" t="n">
         <v>2.751862565319652e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.246388944229046e-07</v>
+        <v>2.246388944229047e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.267589730094326e-07</v>
+        <v>2.267589730094327e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>2.271297033303364e-07</v>
+        <v>2.271297033303366e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.246388834142853e-07</v>
+        <v>2.246388834142855e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>2.271297033303364e-07</v>
+        <v>2.271297033303366e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.017503233175793e-07</v>
+        <v>2.017503233175794e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>2.271297033303364e-07</v>
+        <v>2.271297033303366e-07</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.636847184636537e-08</v>
+        <v>5.636847184636535e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.115960522503642e-08</v>
+        <v>4.115960522503639e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>1.744414188569634e-08</v>
+        <v>1.74441418856964e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.115960522503642e-08</v>
+        <v>4.115960522503639e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>4.115960522503642e-08</v>
+        <v>4.115960522503639e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>3.804337693440954e-08</v>
+        <v>3.80433769344096e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.338872800745621e-08</v>
+        <v>5.338872800745622e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.115960522503642e-08</v>
+        <v>4.115960522503639e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.225775348638804e-08</v>
+        <v>5.225775348638812e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.253730930285859e-08</v>
+        <v>5.253730930285857e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.659008212969133e-08</v>
+        <v>-5.159406390671005e-09</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.771396691783773e-08</v>
+        <v>5.771396691783779e-08</v>
       </c>
       <c r="C9" t="n">
         <v>4.26660177221339e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>4.186147114617028e-08</v>
+        <v>4.186147114617032e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>4.266601772213392e-08</v>
+        <v>4.26660177221339e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.266601772213392e-08</v>
+        <v>4.26660177221339e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.006178250526422e-08</v>
+        <v>5.006178250526426e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.65067398266263e-08</v>
+        <v>5.650673982662633e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.266601772213392e-08</v>
+        <v>4.26660177221339e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.604275308502211e-08</v>
+        <v>5.60427530850221e-08</v>
       </c>
       <c r="K9" t="n">
         <v>5.615396781900236e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>3.270361249865413e-08</v>
+        <v>3.270361249865411e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.738051003272916e-07</v>
+        <v>2.738051003272917e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.600714768771022e-07</v>
+        <v>2.600714768771025e-07</v>
       </c>
       <c r="D2" t="n">
         <v>3.281462800268663e-07</v>
       </c>
       <c r="E2" t="n">
-        <v>2.600714768771022e-07</v>
+        <v>2.600714768771025e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.600714768771022e-07</v>
+        <v>2.600714768771025e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>3.51048003117521e-07</v>
+        <v>3.510480031175283e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>2.132504707786718e-07</v>
+        <v>2.132504707786719e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>2.600714768771022e-07</v>
+        <v>2.600714768771025e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>5.455443963966087e-07</v>
+        <v>5.455443963966097e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>4.236142788337393e-07</v>
+        <v>4.23614278833739e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>2.937927886613286e-07</v>
+        <v>2.937927886613287e-07</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.833834699930862e-08</v>
+        <v>4.833834699930852e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.517157828980058e-08</v>
+        <v>4.517157828980064e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>4.833834699930862e-08</v>
+        <v>4.833834699930852e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.597479132205102e-08</v>
+        <v>4.597479132205112e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.597479132205106e-08</v>
+        <v>4.597479132205116e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>4.802031741401052e-08</v>
+        <v>4.802031741401061e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>4.833834699930862e-08</v>
+        <v>4.833834699930852e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.61910801069614e-08</v>
+        <v>4.619108010696144e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>4.833834699930862e-08</v>
+        <v>4.833834699930852e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>4.833834699930862e-08</v>
+        <v>4.833834699930852e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>4.833834699930862e-08</v>
+        <v>4.833834699930852e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.71676830134956e-08</v>
+        <v>7.716768301349565e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.776628916047658e-08</v>
+        <v>3.776628916047665e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.070256630779355e-08</v>
+        <v>4.070274728317763e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.734492037933362e-08</v>
+        <v>3.734492037933366e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.830963655977414e-08</v>
+        <v>3.83096365597741e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>4.018021930928171e-08</v>
+        <v>7.684965342819775e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>4.044978896662072e-08</v>
+        <v>8.072628283995949e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.835098200223246e-08</v>
+        <v>7.502041612114861e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>7.8031330559898e-08</v>
+        <v>4.135448085457857e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.049665620774818e-08</v>
+        <v>4.049665620774816e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.059758362576483e-08</v>
+        <v>4.059758362576485e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6575,13 +6575,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.575248338972235e-08</v>
+        <v>7.57524833897223e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.360521649737522e-08</v>
+        <v>7.360521649737525e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.574538270686549e-08</v>
+        <v>7.574538270686546e-08</v>
       </c>
       <c r="E5" t="n">
         <v>7.359083262330293e-08</v>
@@ -6590,22 +6590,22 @@
         <v>7.359083262330293e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.543445380442439e-08</v>
+        <v>7.543445380442433e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.575248338972235e-08</v>
+        <v>7.57524833897223e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.360521649737522e-08</v>
+        <v>7.360521649737525e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.575248338972235e-08</v>
+        <v>7.57524833897223e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.575248338972235e-08</v>
+        <v>7.57524833897223e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.575248338972235e-08</v>
+        <v>7.57524833897223e-08</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.223430046070688e-07</v>
+        <v>1.223430046070686e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>1.822206866593779e-07</v>
+        <v>1.822206866593778e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.972199690137141e-07</v>
+        <v>1.972199690137142e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.652565329210214e-07</v>
+        <v>1.652565329210213e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.221572448828965e-07</v>
+        <v>1.221572448828966e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.84042252862671e-07</v>
+        <v>1.840422528626709e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>1.843602824479592e-07</v>
+        <v>1.843602824479594e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.822130155556217e-07</v>
+        <v>1.822130155556216e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.843724706165949e-07</v>
+        <v>1.843724706165951e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.211910018291592e-07</v>
+        <v>1.211910018291594e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.491425149545219e-07</v>
+        <v>2.491425149545221e-07</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.491348919582104e-07</v>
+        <v>1.491348919582105e-07</v>
       </c>
       <c r="C7" t="n">
         <v>1.813902492954938e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.835375652141604e-07</v>
+        <v>1.835375652141607e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.21090209699144e-07</v>
+        <v>2.210902096991442e-07</v>
       </c>
       <c r="F7" t="n">
         <v>1.813902630373861e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.832194866025428e-07</v>
+        <v>1.832194866025429e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.835375161878405e-07</v>
+        <v>1.835375161878407e-07</v>
       </c>
       <c r="I7" t="n">
         <v>1.813902492954938e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.835375161878405e-07</v>
+        <v>1.835375161878407e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.627958124458901e-07</v>
+        <v>1.63604521219941e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.835375161878405e-07</v>
+        <v>1.835375161878407e-07</v>
       </c>
     </row>
     <row r="8">
@@ -6695,13 +6695,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.268097816033346e-08</v>
+        <v>5.268097816033351e-08</v>
       </c>
       <c r="C8" t="n">
         <v>3.78802958484329e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.081796064600655e-08</v>
+        <v>5.081796064600656e-08</v>
       </c>
       <c r="E8" t="n">
         <v>3.78802958484329e-08</v>
@@ -6710,22 +6710,22 @@
         <v>3.78802958484329e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.033720995863938e-08</v>
+        <v>5.033720995863933e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.459578743348112e-08</v>
+        <v>5.459578743348114e-08</v>
       </c>
       <c r="I8" t="n">
         <v>3.78802958484329e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.61497000437508e-08</v>
+        <v>4.614970004375081e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>4.841670897451185e-08</v>
+        <v>4.841670897451186e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.610154545660769e-08</v>
+        <v>5.267520125456268e-08</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.502538052657481e-08</v>
+        <v>5.502538052657488e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>4.056946185924328e-08</v>
+        <v>4.05694618592433e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.426678223586415e-08</v>
+        <v>5.426678223586419e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>4.056946185924328e-08</v>
+        <v>4.05694618592433e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.056946185924328e-08</v>
+        <v>4.05694618592433e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.395437160877895e-08</v>
+        <v>5.395437160877899e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.580865677079821e-08</v>
+        <v>5.580865677079819e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.056946185924328e-08</v>
+        <v>4.05694618592433e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.236984265090155e-08</v>
+        <v>5.236984265090154e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>5.328909026198596e-08</v>
+        <v>5.328909026198601e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>5.642016973387483e-08</v>
+        <v>5.50271763591388e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6851,13 +6851,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.899632162372701e-07</v>
+        <v>3.899632162372695e-07</v>
       </c>
       <c r="C2" t="n">
         <v>4.702013376485056e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>2.467482580094149e-07</v>
+        <v>2.467482580094146e-07</v>
       </c>
       <c r="E2" t="n">
         <v>4.702013376485056e-07</v>
@@ -6866,22 +6866,22 @@
         <v>4.702013376485056e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>3.120076437273619e-07</v>
+        <v>3.120076437273601e-07</v>
       </c>
       <c r="H2" t="n">
-        <v>2.008481128580155e-07</v>
+        <v>2.008481128580149e-07</v>
       </c>
       <c r="I2" t="n">
         <v>4.702013376485056e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>6.514204025428518e-07</v>
+        <v>6.514204025428505e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>3.50653168288378e-07</v>
+        <v>3.506531682883769e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>2.057659720823207e-07</v>
+        <v>3.227731686162914e-07</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.921767146142076e-08</v>
+        <v>4.921767146142061e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.713042368886893e-08</v>
+        <v>4.71304236888689e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>4.921767146142076e-08</v>
+        <v>4.921767146142062e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.788467649190289e-08</v>
+        <v>4.788467649190283e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.788467649190286e-08</v>
+        <v>4.788467649190285e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>4.892655464672947e-08</v>
+        <v>4.892655464672935e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>4.921767146142076e-08</v>
+        <v>4.921767146142062e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.724697550851801e-08</v>
+        <v>4.724697550851787e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>4.921767146142076e-08</v>
+        <v>4.921767146142061e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>4.921767146142076e-08</v>
+        <v>4.921767146142062e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>4.921767146142076e-08</v>
+        <v>4.921767146142062e-08</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.186308100518541e-08</v>
+        <v>4.186308100518539e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>3.982474911003985e-08</v>
+        <v>3.982474911003928e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>4.1654299735257e-08</v>
+        <v>4.165429973525666e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>3.935781367178314e-08</v>
+        <v>3.935781367178307e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>3.992534752121809e-08</v>
+        <v>3.992534752121801e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>7.787850968201744e-08</v>
+        <v>4.157196419049413e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>8.1539321026307e-08</v>
+        <v>8.153932102630687e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>3.989238505228284e-08</v>
+        <v>3.989238505228268e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>7.887705533406101e-08</v>
+        <v>4.272956103155709e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.165659449547838e-08</v>
+        <v>4.165659449547834e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>4.176225137432861e-08</v>
+        <v>4.176225137432849e-08</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.660260631286164e-08</v>
+        <v>7.660260631286156e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.463191035995882e-08</v>
+        <v>7.463191035995869e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.659546641002586e-08</v>
+        <v>7.659546641002578e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.462814655832702e-08</v>
+        <v>7.462814655832687e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.462814655832702e-08</v>
+        <v>7.462814655832687e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.631148949817032e-08</v>
+        <v>7.631148949817011e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.660260631286164e-08</v>
+        <v>7.660260631286156e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.463191035995882e-08</v>
+        <v>7.463191035995869e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.660260631286164e-08</v>
+        <v>7.660260631286156e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.660260631286164e-08</v>
+        <v>7.660260631286156e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.660260631286164e-08</v>
+        <v>7.660260631286156e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.228490731394895e-07</v>
+        <v>1.228490731394893e-07</v>
       </c>
       <c r="C6" t="n">
         <v>1.826539214926969e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>1.974126540357607e-07</v>
+        <v>1.974126540357602e-07</v>
       </c>
       <c r="E6" t="n">
         <v>1.657596641178409e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.228380154349696e-07</v>
+        <v>1.228380154349694e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>1.843156724648783e-07</v>
+        <v>1.843156724648781e-07</v>
       </c>
       <c r="H6" t="n">
         <v>1.846067892795648e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>1.826360933266668e-07</v>
+        <v>1.826360933266665e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>1.846189264368162e-07</v>
+        <v>1.846189264368159e-07</v>
       </c>
       <c r="K6" t="n">
         <v>1.217018918534156e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.49117887885392e-07</v>
+        <v>2.491178878853916e-07</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.443305657907741e-07</v>
+        <v>1.443305657907737e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>1.75180905720428e-07</v>
+        <v>1.751809057204276e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>1.771516472794796e-07</v>
+        <v>1.771516472794791e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.130557453459693e-07</v>
+        <v>2.130557453459689e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>1.751809208471888e-07</v>
+        <v>1.751809208471885e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>1.768604848586393e-07</v>
+        <v>1.768604848586391e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>1.771516016733308e-07</v>
+        <v>1.771516016733305e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>1.75180905720428e-07</v>
+        <v>1.751809057204276e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>1.771516016733308e-07</v>
+        <v>1.771516016733305e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.573634537062303e-07</v>
+        <v>1.5736345370623e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>1.771516016733308e-07</v>
+        <v>1.771516016733305e-07</v>
       </c>
     </row>
     <row r="8">
@@ -7091,37 +7091,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.95140390283535e-08</v>
+        <v>4.951403902835349e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>3.275414986463272e-08</v>
+        <v>3.275414986463269e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>5.313129456686027e-08</v>
+        <v>5.313129456686015e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>3.275414986463272e-08</v>
+        <v>3.275414986463269e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>3.275414986463272e-08</v>
+        <v>3.275414986463269e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>5.142682612464688e-08</v>
+        <v>5.142682612464678e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.484740693678979e-08</v>
+        <v>5.484740693678971e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>3.275414986463272e-08</v>
+        <v>3.275414986463269e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>4.36229765590222e-08</v>
+        <v>4.362297655902216e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.009906145049572e-08</v>
+        <v>5.00990614504956e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>5.19191096724549e-08</v>
+        <v>5.485911351416807e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7131,37 +7131,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.36450682360317e-08</v>
+        <v>5.364506823603162e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>3.867089383702058e-08</v>
+        <v>3.867089383702052e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>5.511848473937775e-08</v>
+        <v>5.511848473937762e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>3.867089383702058e-08</v>
+        <v>3.867089383702052e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>3.867089383702058e-08</v>
+        <v>3.867089383702052e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>5.433839262961527e-08</v>
+        <v>5.43383926296152e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.58203197101093e-08</v>
+        <v>5.582031971010918e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>3.867089383702058e-08</v>
+        <v>3.867089383702052e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.125118962105991e-08</v>
+        <v>5.125118962105987e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>5.388376622477439e-08</v>
+        <v>5.38837662247743e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>5.58245179483831e-08</v>
+        <v>5.582451794838306e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.043024615722352e-07</v>
+        <v>3.043024615722345e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>2.539560559860093e-07</v>
+        <v>2.539560559860084e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>6.522590371209841e-06</v>
+        <v>6.522590371209833e-06</v>
       </c>
       <c r="E2" t="n">
-        <v>2.539560559860093e-07</v>
+        <v>2.539560559860084e-07</v>
       </c>
       <c r="F2" t="n">
-        <v>2.539560559860093e-07</v>
+        <v>2.539560559860084e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>3.031772942680516e-06</v>
+        <v>3.03177294268051e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>7.243151289713652e-07</v>
+        <v>7.243151289713567e-07</v>
       </c>
       <c r="I2" t="n">
-        <v>2.539560559860093e-07</v>
+        <v>2.539560559860084e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>4.72156134950732e-07</v>
+        <v>4.721561349507309e-07</v>
       </c>
       <c r="K2" t="n">
-        <v>5.046604805376343e-07</v>
+        <v>5.046604805376328e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>9.278654220897362e-07</v>
+        <v>6.535271159018725e-07</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.558275668573661e-08</v>
+        <v>5.558275668573658e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.812004872307451e-08</v>
+        <v>4.812004872307443e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.558275668573661e-08</v>
+        <v>5.558275668573658e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.926738036668917e-08</v>
+        <v>4.926738036668907e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.926738036668915e-08</v>
+        <v>4.926738036668894e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.513907237189523e-08</v>
+        <v>5.513907237189504e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.558275668573661e-08</v>
+        <v>5.558275668573658e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.262707680346259e-08</v>
+        <v>5.262707680346246e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.558275668573661e-08</v>
+        <v>5.558275668573658e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.558275668573661e-08</v>
+        <v>5.558275668573658e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.558275668573661e-08</v>
+        <v>5.558275668573658e-08</v>
       </c>
     </row>
     <row r="4">
@@ -7327,16 +7327,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.135090005865116e-08</v>
+        <v>5.135090005865104e-08</v>
       </c>
       <c r="C4" t="n">
-        <v>4.37638166307626e-08</v>
+        <v>4.376381663076205e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>6.1440818779777e-08</v>
+        <v>6.144081877977558e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>4.323546039298977e-08</v>
+        <v>4.323546039298993e-08</v>
       </c>
       <c r="F4" t="n">
         <v>4.796093456687052e-08</v>
@@ -7345,19 +7345,19 @@
         <v>1.040610114267867e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>1.096451592357834e-07</v>
+        <v>1.096451592357831e-07</v>
       </c>
       <c r="I4" t="n">
         <v>1.015490158583541e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.069370062153883e-07</v>
+        <v>1.069370062153881e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>4.814467393527886e-08</v>
+        <v>4.814467393527898e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.160311677514545e-08</v>
+        <v>5.160311677514532e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.616280738336006e-08</v>
+        <v>9.61628073833599e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>9.320712750108605e-08</v>
+        <v>9.320712750108589e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>9.615521432944765e-08</v>
+        <v>9.615521432944745e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>9.31172643037637e-08</v>
+        <v>9.311726430376338e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>9.31172643037637e-08</v>
+        <v>9.311726430376338e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>9.571912306951853e-08</v>
+        <v>9.571912306951828e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>9.616280738336006e-08</v>
+        <v>9.61628073833599e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>9.320712750108605e-08</v>
+        <v>9.320712750108589e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>9.616280738336006e-08</v>
+        <v>9.61628073833599e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>9.616280738336006e-08</v>
+        <v>9.61628073833599e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>9.616280738336006e-08</v>
+        <v>9.61628073833599e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.561083322489444e-07</v>
+        <v>1.56108332248944e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.353692796227592e-07</v>
+        <v>2.353692796206917e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.554454185704997e-07</v>
+        <v>2.554454185704985e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>2.12871432723853e-07</v>
+        <v>2.128714327238525e-07</v>
       </c>
       <c r="F6" t="n">
-        <v>1.557116127148463e-07</v>
+        <v>1.557116127148458e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.379411628972812e-07</v>
+        <v>2.379411628972808e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.383848472111031e-07</v>
+        <v>2.383848472111028e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.354291673288488e-07</v>
+        <v>2.35429167328848e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.384010168959395e-07</v>
+        <v>2.384010168959392e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.545800037406239e-07</v>
+        <v>1.545800037406236e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>3.243295469368636e-07</v>
+        <v>3.243295469368624e-07</v>
       </c>
     </row>
     <row r="7">
@@ -7447,34 +7447,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.373764988860233e-07</v>
+        <v>2.373764988860227e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>2.927069436802562e-07</v>
+        <v>2.927069436802557e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.95662768763755e-07</v>
+        <v>2.956627687637543e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>3.599680472494959e-07</v>
+        <v>3.599680472494952e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.927069599196074e-07</v>
+        <v>2.927069599196067e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.95218939248689e-07</v>
+        <v>2.95218939248688e-07</v>
       </c>
       <c r="H7" t="n">
         <v>2.956626235625303e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>2.927069436802562e-07</v>
+        <v>2.927069436802557e-07</v>
       </c>
       <c r="J7" t="n">
         <v>2.956626235625303e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.618914750887554e-07</v>
+        <v>2.618914750887548e-07</v>
       </c>
       <c r="L7" t="n">
         <v>2.956626235625303e-07</v>
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.094455765244681e-08</v>
+        <v>6.09445576524467e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.427923158467116e-08</v>
+        <v>4.427923158467102e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>-9.033000861124587e-08</v>
+        <v>-9.033000861124622e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.427923158467116e-08</v>
+        <v>4.427923158467102e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>4.427923158467116e-08</v>
+        <v>4.427923158467102e-08</v>
       </c>
       <c r="G8" t="n">
         <v>-3.231366287156972e-09</v>
       </c>
       <c r="H8" t="n">
-        <v>5.236509968593772e-08</v>
+        <v>5.236509968593783e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.427923158467116e-08</v>
+        <v>4.427923158467102e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.766709270179518e-08</v>
+        <v>5.766709270179501e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.62117020355372e-08</v>
+        <v>5.621170203553713e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>4.960104991894102e-08</v>
+        <v>4.960104991894095e-08</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6.326890906933924e-08</v>
+        <v>6.326890906933911e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>4.631206457011908e-08</v>
+        <v>4.631206457011891e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.659903678575084e-09</v>
+        <v>1.659903678574918e-09</v>
       </c>
       <c r="E9" t="n">
-        <v>4.631206457011908e-08</v>
+        <v>4.631206457011891e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.631206457011908e-08</v>
+        <v>4.631206457011891e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.674911117442961e-08</v>
+        <v>3.674911117442956e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.978779408147323e-08</v>
+        <v>5.978779408147311e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.631206457011908e-08</v>
+        <v>4.631206457011891e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>6.193742275848714e-08</v>
+        <v>6.193742275848696e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>6.134179627423316e-08</v>
+        <v>6.134179627423304e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>5.866163863518912e-08</v>
+        <v>6.061270624817429e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7643,13 +7643,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.948050669451564e-07</v>
+        <v>1.948050669451562e-07</v>
       </c>
       <c r="C2" t="n">
         <v>2.495200800165707e-07</v>
       </c>
       <c r="D2" t="n">
-        <v>4.480366187130282e-06</v>
+        <v>4.480366187130273e-06</v>
       </c>
       <c r="E2" t="n">
         <v>2.495200800165707e-07</v>
@@ -7658,22 +7658,22 @@
         <v>2.495200800165707e-07</v>
       </c>
       <c r="G2" t="n">
-        <v>1.456864673547177e-06</v>
+        <v>1.456864673547174e-06</v>
       </c>
       <c r="H2" t="n">
-        <v>3.06442615588497e-07</v>
+        <v>3.064426155884973e-07</v>
       </c>
       <c r="I2" t="n">
         <v>2.495200800165707e-07</v>
       </c>
       <c r="J2" t="n">
-        <v>5.314001165844473e-07</v>
+        <v>5.314001165844475e-07</v>
       </c>
       <c r="K2" t="n">
         <v>2.462160174775328e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>2.855361572788791e-07</v>
+        <v>1.796440860699804e-05</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.128332230086853e-08</v>
+        <v>5.128332230086864e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.688599147451801e-08</v>
+        <v>4.688599147451802e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.128332230086853e-08</v>
+        <v>5.128332230086864e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.777960402368336e-08</v>
+        <v>4.777960402368339e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.777960402368335e-08</v>
+        <v>4.777960402368338e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.091771410119038e-08</v>
+        <v>5.091771410119047e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.128332230086853e-08</v>
+        <v>5.128332230086864e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.883238965683053e-08</v>
+        <v>4.883238965683055e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.128332230086853e-08</v>
+        <v>5.128332230086864e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.128332230086853e-08</v>
+        <v>5.128332230086864e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.128332230086853e-08</v>
+        <v>5.128332230086864e-08</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.365468093836154e-08</v>
+        <v>9.365468093836151e-08</v>
       </c>
       <c r="C4" t="n">
         <v>4.053756920039496e-08</v>
       </c>
       <c r="D4" t="n">
-        <v>5.328982492040211e-08</v>
+        <v>5.3290053639898e-08</v>
       </c>
       <c r="E4" t="n">
-        <v>4.007078544090276e-08</v>
+        <v>4.007078544090268e-08</v>
       </c>
       <c r="F4" t="n">
-        <v>4.25627470714134e-08</v>
+        <v>4.256274707141346e-08</v>
       </c>
       <c r="G4" t="n">
-        <v>4.485498340359202e-08</v>
+        <v>9.328907273868352e-08</v>
       </c>
       <c r="H4" t="n">
-        <v>9.732691341766279e-08</v>
+        <v>9.732691341766255e-08</v>
       </c>
       <c r="I4" t="n">
-        <v>9.120374829432351e-08</v>
+        <v>9.120374829432354e-08</v>
       </c>
       <c r="J4" t="n">
-        <v>4.625729923917579e-08</v>
+        <v>4.625729923917595e-08</v>
       </c>
       <c r="K4" t="n">
-        <v>4.342814848038427e-08</v>
+        <v>4.342814848038388e-08</v>
       </c>
       <c r="L4" t="n">
-        <v>5.081647907960258e-08</v>
+        <v>5.081647907960241e-08</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.337434994921482e-08</v>
+        <v>8.337434994921474e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.092341730517686e-08</v>
+        <v>8.092341730517671e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.336725389779202e-08</v>
+        <v>8.336725389779207e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.087286720327693e-08</v>
+        <v>8.087286720327672e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.087286720327693e-08</v>
+        <v>8.087286720327672e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.300874174953675e-08</v>
+        <v>8.300874174953658e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.337434994921482e-08</v>
+        <v>8.337434994921474e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.092341730517686e-08</v>
+        <v>8.092341730517671e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.337434994921482e-08</v>
+        <v>8.337434994921474e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.337434994921482e-08</v>
+        <v>8.337434994921474e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.337434994921482e-08</v>
+        <v>8.337434994921474e-08</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.349843906937533e-07</v>
+        <v>1.349843906937532e-07</v>
       </c>
       <c r="C6" t="n">
-        <v>2.01677013619204e-07</v>
+        <v>2.016770136192037e-07</v>
       </c>
       <c r="D6" t="n">
-        <v>2.184961227956454e-07</v>
+        <v>2.184961227956458e-07</v>
       </c>
       <c r="E6" t="n">
-        <v>1.827604377403773e-07</v>
+        <v>1.82760437740377e-07</v>
       </c>
       <c r="F6" t="n">
         <v>1.347000884413932e-07</v>
       </c>
       <c r="G6" t="n">
-        <v>2.037878565048207e-07</v>
+        <v>2.037878565048204e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.041534647044773e-07</v>
+        <v>2.041534647044771e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.017025320604606e-07</v>
+        <v>2.017025320604605e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.041670584039032e-07</v>
+        <v>2.041670584039028e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.336995396304623e-07</v>
+        <v>1.33699539630462e-07</v>
       </c>
       <c r="L6" t="n">
-        <v>2.764063463322579e-07</v>
+        <v>2.764063463322573e-07</v>
       </c>
     </row>
     <row r="7">
@@ -7849,16 +7849,16 @@
         <v>2.178525264554485e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>2.203035278343197e-07</v>
+        <v>2.203035278343196e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>2.66397546300448e-07</v>
+        <v>2.663975463004478e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>2.17852520865467e-07</v>
+        <v>2.178525208654668e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>2.199378508998085e-07</v>
+        <v>2.199378508998082e-07</v>
       </c>
       <c r="H7" t="n">
         <v>2.203034590994866e-07</v>
@@ -7870,7 +7870,7 @@
         <v>2.203034590994866e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>1.673329915839979e-07</v>
+        <v>1.959294325411013e-07</v>
       </c>
       <c r="L7" t="n">
         <v>2.203034590994866e-07</v>
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.874448081747577e-08</v>
+        <v>5.874448081747572e-08</v>
       </c>
       <c r="C8" t="n">
-        <v>4.112041293156131e-08</v>
+        <v>4.112041293156126e-08</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.833367247433216e-08</v>
+        <v>-5.833367247433219e-08</v>
       </c>
       <c r="E8" t="n">
-        <v>4.112041293156131e-08</v>
+        <v>4.112041293156126e-08</v>
       </c>
       <c r="F8" t="n">
-        <v>4.112041293156131e-08</v>
+        <v>4.112041293156126e-08</v>
       </c>
       <c r="G8" t="n">
-        <v>2.577265939421824e-08</v>
+        <v>2.57726593942181e-08</v>
       </c>
       <c r="H8" t="n">
-        <v>5.659642937537093e-08</v>
+        <v>5.65964293753709e-08</v>
       </c>
       <c r="I8" t="n">
-        <v>4.112041293156131e-08</v>
+        <v>4.112041293156126e-08</v>
       </c>
       <c r="J8" t="n">
-        <v>5.110706383928958e-08</v>
+        <v>5.110706383928955e-08</v>
       </c>
       <c r="K8" t="n">
-        <v>5.735858308808083e-08</v>
+        <v>5.735858308808073e-08</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.262023142031458e-07</v>
+        <v>-3.26202314203146e-07</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.979263358442657e-08</v>
+        <v>5.979263358442648e-08</v>
       </c>
       <c r="C9" t="n">
-        <v>4.345629007776926e-08</v>
+        <v>4.345629007776916e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.211064339995024e-08</v>
+        <v>1.211064339995028e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>4.345629007776926e-08</v>
+        <v>4.345629007776916e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>4.345629007776926e-08</v>
+        <v>4.345629007776916e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>4.612609660839313e-08</v>
+        <v>4.612609660839304e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>5.892293010469568e-08</v>
+        <v>5.892293010469566e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>4.345629007776926e-08</v>
+        <v>4.345629007776916e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>5.668618095882722e-08</v>
+        <v>5.668618095882721e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>5.9228420640771e-08</v>
+        <v>5.922842064077098e-08</v>
       </c>
       <c r="L9" t="n">
-        <v>-9.669956295315784e-08</v>
+        <v>-9.669956295315789e-08</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Hydrogen/hydrogen particulate matter results.xlsx
+++ b/Results/Hydrogen/hydrogen particulate matter results.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,321 +511,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>4.366392414759077e-07</v>
+        <v>6.91148094999695e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>3.936670559190901e-07</v>
+        <v>5.158697154662115e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>8.051541435880207e-06</v>
+        <v>7.690653699654472e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>3.936670559190901e-07</v>
+        <v>5.158697154662115e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>3.936670559190901e-07</v>
+        <v>5.158697154662115e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>4.036299184806343e-06</v>
+        <v>7.196861997011361e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.45549978936852e-06</v>
+        <v>7.001105510673062e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>3.936670559190901e-07</v>
+        <v>5.158697154662115e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>7.900681948354725e-07</v>
+        <v>6.943738765115047e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>6.980655527460443e-07</v>
+        <v>6.937714230600757e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.349530518736892e-06</v>
+        <v>6.976810690931747e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.025740673436631e-08</v>
+        <v>6.976165923742574e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.301730932589345e-08</v>
+        <v>5.202360389340298e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>6.025740673436631e-08</v>
+        <v>6.976165923742574e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.42334077879551e-08</v>
+        <v>5.202360389340298e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.42334077879551e-08</v>
+        <v>5.202360389340298e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.981712675539091e-08</v>
+        <v>6.90120203070367e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>6.025740673436631e-08</v>
+        <v>6.976165923742574e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.732999974403962e-08</v>
+        <v>5.202360389340298e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>6.025740673436631e-08</v>
+        <v>6.976165923742574e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>6.025740673436631e-08</v>
+        <v>6.976165923742574e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>6.025740673436631e-08</v>
+        <v>6.976165923742574e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.705250091532245e-08</v>
+        <v>4.366392414759083e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>4.850617043672319e-08</v>
+        <v>3.936670559190919e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>6.813238218081976e-08</v>
+        <v>8.051541435880208e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.786910075493029e-08</v>
+        <v>3.936670559190919e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>5.361911658513965e-08</v>
+        <v>3.936670559190919e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>1.175196236549867e-07</v>
+        <v>4.036299184806337e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.236006816988418e-07</v>
+        <v>1.455499789368522e-06</v>
       </c>
       <c r="I4" t="n">
-        <v>1.150324966436354e-07</v>
+        <v>3.936670559190919e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.204898880987073e-07</v>
+        <v>7.900681948354723e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>5.336612535878888e-08</v>
+        <v>6.980655527460448e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>5.736812362766005e-08</v>
+        <v>1.349530518736895e-06</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.078869942230716e-07</v>
+        <v>6.025740673436631e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>1.049595872327449e-07</v>
+        <v>5.30173093258935e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.078787258132965e-07</v>
+        <v>6.025740673436631e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>1.04863716860797e-07</v>
+        <v>5.423340778795508e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.04863716860797e-07</v>
+        <v>5.423340778795506e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.074467142440961e-07</v>
+        <v>5.981712675539091e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.078869942230716e-07</v>
+        <v>6.025740673436631e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>1.049595872327449e-07</v>
+        <v>5.732999974403961e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.078869942230716e-07</v>
+        <v>6.025740673436631e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>1.078869942230716e-07</v>
+        <v>6.025740673436631e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.078869942230716e-07</v>
+        <v>6.025740673436631e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.756872942155769e-07</v>
+        <v>5.705250091532251e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.665242177432859e-07</v>
+        <v>4.850617043672348e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.889697352551192e-07</v>
+        <v>6.813238218081987e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.408675538367467e-07</v>
+        <v>4.786910075493021e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.756817942100689e-07</v>
+        <v>5.361911658513973e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.690738497145974e-07</v>
+        <v>1.175196236549866e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.695141296935627e-07</v>
+        <v>1.236006816988418e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.665867227032463e-07</v>
+        <v>1.150324966436353e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.69532569347107e-07</v>
+        <v>1.204898880987075e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.739444125735331e-07</v>
+        <v>5.336612535878902e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.675241050203671e-07</v>
+        <v>5.736812362766003e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.95710206085332e-07</v>
+        <v>1.078869942230716e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>3.668140388495846e-07</v>
+        <v>1.049595872327449e-07</v>
       </c>
       <c r="D7" t="n">
-        <v>3.697416155964926e-07</v>
+        <v>1.078787258132965e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>4.522446861720684e-07</v>
+        <v>1.048637168607971e-07</v>
       </c>
       <c r="F7" t="n">
-        <v>3.668140491737304e-07</v>
+        <v>1.048637168607971e-07</v>
       </c>
       <c r="G7" t="n">
-        <v>3.693011658609361e-07</v>
+        <v>1.074467142440961e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>3.697414458399116e-07</v>
+        <v>1.078869942230716e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>3.668140388495846e-07</v>
+        <v>1.049595872327449e-07</v>
       </c>
       <c r="J7" t="n">
-        <v>3.697414458399116e-07</v>
+        <v>1.078869942230716e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.765228564620834e-07</v>
+        <v>1.078869942230716e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>3.697414458399116e-07</v>
+        <v>1.078869942230716e-07</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.175206072869755e-08</v>
+        <v>1.75687294215577e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>4.465298833201357e-08</v>
+        <v>2.665242177432861e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.014685898710431e-07</v>
+        <v>2.889697352551197e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>4.465298833201357e-08</v>
+        <v>2.408675538367469e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>4.465298833201357e-08</v>
+        <v>1.756817942100689e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.411858998049846e-08</v>
+        <v>2.690738497145976e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>4.348035064442428e-08</v>
+        <v>2.695141296935628e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>4.465298833201357e-08</v>
+        <v>2.665867227032464e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>5.510831403015922e-08</v>
+        <v>2.695325693471072e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>5.626853763347773e-08</v>
+        <v>1.73944412573533e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>4.839385479320784e-08</v>
+        <v>3.675241050203674e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.957102060853321e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.668140388495849e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.697416155964927e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>4.522446861720683e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.668140491737305e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.693011658609362e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.697414458399119e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.668140388495849e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.697414458399119e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.765228564620836e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.697414458399119e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>6.175206072869758e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4.465298833201359e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-1.014685898710431e-07</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4.465298833201359e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.465298833201359e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-1.411858998049854e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.348035064442425e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.465298833201359e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5.510831403015926e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.626853763347774e-08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4.839385479320795e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>6.547041665342225e-08</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>6.547041665342226e-08</v>
+      </c>
+      <c r="C11" t="n">
         <v>4.823331797743089e-08</v>
       </c>
-      <c r="D9" t="n">
-        <v>-1.00377202623524e-09</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>-1.003772026235319e-09</v>
+      </c>
+      <c r="E11" t="n">
         <v>4.823331797743089e-08</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>4.823331797743089e-08</v>
       </c>
-      <c r="G9" t="n">
-        <v>3.414392736774885e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>5.805297594335384e-08</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>3.414392736774895e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5.805297594335389e-08</v>
+      </c>
+      <c r="I11" t="n">
         <v>4.823331797743089e-08</v>
       </c>
-      <c r="J9" t="n">
-        <v>6.277006888440382e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>6.323772897618394e-08</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5.919748026318883e-08</v>
+      <c r="J11" t="n">
+        <v>6.277006888440386e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.323772897618396e-08</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.919748026318884e-08</v>
       </c>
     </row>
   </sheetData>
@@ -839,7 +919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,321 +987,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.690265430143054e-07</v>
+        <v>5.739128627210096e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>4.270441188257596e-07</v>
+        <v>4.390383949341686e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>4.189471375831564e-07</v>
+        <v>5.770999546595732e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>4.270441188257596e-07</v>
+        <v>4.390383949341686e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>4.270441188257596e-07</v>
+        <v>4.390383949341686e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>3.515945831359966e-07</v>
+        <v>5.744932464299508e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.448267370275241e-07</v>
+        <v>5.745925356072217e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>4.270441188257596e-07</v>
+        <v>4.390383949341686e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>7.684316695982611e-07</v>
+        <v>5.805893376880561e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.32716785734099e-07</v>
+        <v>5.747871489259758e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.840095303275719e-07</v>
+        <v>5.742795648968889e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.922318950248407e-08</v>
+        <v>5.817745443299811e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.706597002734644e-08</v>
+        <v>4.413410960326895e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>4.922318950248407e-08</v>
+        <v>5.817745443299811e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.782391848251858e-08</v>
+        <v>4.413410960326895e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.782391848251856e-08</v>
+        <v>4.413410960326895e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>4.892917175940224e-08</v>
+        <v>5.8015330803186e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>4.922318950248407e-08</v>
+        <v>5.817745443299811e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.723404544650428e-08</v>
+        <v>4.413410960326895e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>4.922318950248407e-08</v>
+        <v>5.817745443299811e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>4.922318950248407e-08</v>
+        <v>5.817745443299811e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>4.922318950248407e-08</v>
+        <v>5.817745443299811e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.171314297844069e-08</v>
+        <v>1.690265430143049e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>3.963571107334136e-08</v>
+        <v>4.270441188257606e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>7.909685696516611e-08</v>
+        <v>4.189471375831564e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>3.916914819201256e-08</v>
+        <v>4.270441188257606e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>3.982600125888682e-08</v>
+        <v>4.270441188257606e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>7.776599375778939e-08</v>
+        <v>3.515945831359981e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>8.161986200231294e-08</v>
+        <v>2.448267370275241e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>3.972399892246078e-08</v>
+        <v>4.270441188257606e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>4.271169151584162e-08</v>
+        <v>7.68431669598259e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>4.132234860991958e-08</v>
+        <v>2.32716785734099e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>4.170182959024688e-08</v>
+        <v>1.840095303275723e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.706528460487932e-08</v>
+        <v>4.922318950248409e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.507614054889929e-08</v>
+        <v>4.706597002734647e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.705814227114054e-08</v>
+        <v>4.922318950248409e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.507399189531014e-08</v>
+        <v>4.782391848251855e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.507399189531014e-08</v>
+        <v>4.782391848251856e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.677126686179748e-08</v>
+        <v>4.892917175940223e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.706528460487932e-08</v>
+        <v>4.922318950248409e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.507614054889929e-08</v>
+        <v>4.723404544650421e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.706528460487932e-08</v>
+        <v>4.922318950248409e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.706528460487932e-08</v>
+        <v>4.922318950248409e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.706528460487932e-08</v>
+        <v>4.922318950248409e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.237516907413763e-07</v>
+        <v>4.17131429784406e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.841875864978448e-07</v>
+        <v>3.963571107334112e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.990974214309898e-07</v>
+        <v>7.90968569651662e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.671159773671226e-07</v>
+        <v>3.91691481920128e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.237436847942726e-07</v>
+        <v>3.98260012588868e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.85863209218028e-07</v>
+        <v>7.776599375778916e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.861572269611019e-07</v>
+        <v>8.161986200231272e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.8416808290513e-07</v>
+        <v>3.972399892246077e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.861694914337246e-07</v>
+        <v>4.271169151584157e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.225924758647243e-07</v>
+        <v>4.132234860991954e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.513450278101053e-07</v>
+        <v>4.170182959024677e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.451716976492686e-07</v>
+        <v>7.706528460487927e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.762685497979525e-07</v>
+        <v>7.507614054889938e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.78257740937647e-07</v>
+        <v>7.705814227114043e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.144491482718516e-07</v>
+        <v>7.507399189531017e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.762685640599321e-07</v>
+        <v>7.507399189531017e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.779636761108506e-07</v>
+        <v>7.677126686179754e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.782576938539325e-07</v>
+        <v>7.706528460487927e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.762685497979525e-07</v>
+        <v>7.507614054889938e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.782576938539325e-07</v>
+        <v>7.706528460487927e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.590875575174431e-07</v>
+        <v>7.706528460487927e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.782576938539325e-07</v>
+        <v>7.706528460487927e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.533035465317524e-08</v>
+        <v>1.237516907413766e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>3.406250437552523e-08</v>
+        <v>1.841875864978448e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>4.865547604308445e-08</v>
+        <v>1.990974214309893e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>3.406250437552523e-08</v>
+        <v>1.671159773671228e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>3.406250437552523e-08</v>
+        <v>1.237436847942727e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>5.05862489347918e-08</v>
+        <v>1.858632092180278e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>5.398822836453866e-08</v>
+        <v>1.861572269611019e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>3.406250437552523e-08</v>
+        <v>1.841680829051299e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>4.147025552601567e-08</v>
+        <v>1.861694914337246e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>5.350306336229037e-08</v>
+        <v>1.225924758647241e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.550078975124497e-08</v>
+        <v>2.513450278101054e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.451716976492685e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.762685497979526e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.782577409376471e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.144491482718516e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.762685640599326e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.779636761108506e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.782576938539326e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.762685497979526e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.782576938539325e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.590875575174431e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.782576938539325e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5.53303546531753e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.406250437552523e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.865547604308448e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.406250437552523e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3.406250437552523e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5.05862489347919e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.398822836453877e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.406250437552523e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.147025552601566e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.350306336229048e-08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.550078975124517e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>5.609584679911294e-08</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.932122701849201e-08</v>
-      </c>
-      <c r="D9" t="n">
-        <v>5.337746495380191e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3.932122701849201e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3.932122701849201e-08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5.406906871779652e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>5.555314234930175e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.932122701849201e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.045710502344472e-08</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="B11" t="n">
+        <v>5.6095846799113e-08</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.9321227018492e-08</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.337746495380199e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.9321227018492e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3.9321227018492e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5.406906871779659e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5.555314234930185e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.9321227018492e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.04571050234448e-08</v>
+      </c>
+      <c r="K11" t="n">
         <v>5.535185205902514e-08</v>
       </c>
-      <c r="L9" t="n">
-        <v>5.616731891011427e-08</v>
+      <c r="L11" t="n">
+        <v>5.616731891011438e-08</v>
       </c>
     </row>
   </sheetData>
@@ -1235,7 +1395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1303,320 +1463,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.53088414031617e-07</v>
+        <v>9.625734633770182e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>3.072606018528199e-07</v>
+        <v>2.780397484307302e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>3.972313489377312e-06</v>
+        <v>7.344720048106194e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.461616584797014e-07</v>
+        <v>4.43353290048685e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>2.461616584797014e-07</v>
+        <v>4.43353290048685e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.85647841976811e-06</v>
+        <v>5.705975787216033e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>5.199749669447885e-07</v>
+        <v>6.958505393114966e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.461616584797014e-07</v>
+        <v>4.43353290048685e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.312022349256621e-06</v>
+        <v>6.348665580854779e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>3.541354347706611e-07</v>
+        <v>1.062741125128207e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>3.947599806144932e-07</v>
+        <v>6.076095573553515e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.488871828781379e-08</v>
+        <v>9.764157350495961e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.995004315065272e-08</v>
+        <v>2.79332591168858e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.488871828781377e-08</v>
+        <v>7.020420994141516e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.806519814687295e-08</v>
+        <v>4.48277547668233e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.806519814687295e-08</v>
+        <v>4.48277547668233e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.45225147314808e-08</v>
+        <v>5.598491313019608e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.488871828781379e-08</v>
+        <v>7.020420994141516e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.244037742980614e-08</v>
+        <v>4.48277547668233e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.488871828781379e-08</v>
+        <v>6.312817385564609e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.488871828781377e-08</v>
+        <v>1.076092565825972e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>5.488871828781377e-08</v>
+        <v>6.13739585277491e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.51063484757013e-08</v>
+        <v>1.530884140316171e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>4.50789253777505e-08</v>
+        <v>3.072606018528299e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>5.364884893721439e-08</v>
+        <v>3.972313489377314e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.199467722369271e-08</v>
+        <v>2.461616584797012e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>4.528316774375229e-08</v>
+        <v>2.461616584797012e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>4.759414376990441e-08</v>
+        <v>1.856478419768115e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.044113236725796e-07</v>
+        <v>5.199749669447928e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>4.551200646822991e-08</v>
+        <v>2.461616584797012e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>9.772125904075009e-08</v>
+        <v>1.312022349256621e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>4.606215616103756e-08</v>
+        <v>3.541354347706613e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>4.801894937294705e-08</v>
+        <v>3.947599806144934e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.303916902300963e-08</v>
+        <v>5.488871828781375e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>9.299140403773319e-08</v>
+        <v>4.995004315065283e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>9.303225878397343e-08</v>
+        <v>5.488871828781375e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>9.05635417696991e-08</v>
+        <v>4.806519814687292e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>9.05635417696991e-08</v>
+        <v>4.806519814687295e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>9.267296546667645e-08</v>
+        <v>5.45225147314806e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>9.303916902300963e-08</v>
+        <v>5.488871828781375e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>9.0590828165002e-08</v>
+        <v>5.244037742980609e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>9.303916902300963e-08</v>
+        <v>5.488871828781375e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>9.303916902300963e-08</v>
+        <v>5.488871828781375e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>9.303916902300963e-08</v>
+        <v>5.488871828781375e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.521169163162513e-07</v>
+        <v>9.510634847570148e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.321573597386614e-07</v>
+        <v>4.507892537775035e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.488134505255817e-07</v>
+        <v>5.364884893721448e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.078509631714454e-07</v>
+        <v>4.199467722369192e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.521951323840816e-07</v>
+        <v>4.52831677437524e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.318401751972714e-07</v>
+        <v>4.759414376990454e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.32206378753918e-07</v>
+        <v>1.044113236725797e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.297580378955967e-07</v>
+        <v>4.551200646823007e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.322221186217251e-07</v>
+        <v>9.772125904075005e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.506292134308406e-07</v>
+        <v>4.606215616103749e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.158665192423846e-07</v>
+        <v>4.801894937294713e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.045086770133318e-07</v>
+        <v>9.303916902300976e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.538092376894103e-07</v>
+        <v>9.299140403773323e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.538571078399273e-07</v>
+        <v>9.303225878397353e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>3.083556991885841e-07</v>
+        <v>9.056354176969916e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.514086784927368e-07</v>
+        <v>9.056354176969916e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.534907991183537e-07</v>
+        <v>9.267296546667646e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.53857002674687e-07</v>
+        <v>9.303916902300976e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.514086618166791e-07</v>
+        <v>9.059082816500204e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.53857002674687e-07</v>
+        <v>9.303916902300976e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.252644332127579e-07</v>
+        <v>9.303916902300976e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.53857002674687e-07</v>
+        <v>9.303916902300976e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.506683340491321e-08</v>
+        <v>1.521169163162511e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>2.200628114844446e-08</v>
+        <v>2.321573597386616e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.023165177883683e-08</v>
+        <v>2.488134505255815e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>4.049692709954898e-08</v>
+        <v>2.078509631714453e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>4.049692709954898e-08</v>
+        <v>1.521951323840813e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>1.565828715144605e-08</v>
+        <v>2.318401751972715e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>6.085770804277507e-08</v>
+        <v>2.322063787539177e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>4.049692709954898e-08</v>
+        <v>2.297580378955971e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>3.565885712382998e-08</v>
+        <v>2.322221186217248e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>1.008214397719929e-07</v>
+        <v>1.506292134308407e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.472422319519187e-08</v>
+        <v>3.158665192423841e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.045086770133322e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.538092376894103e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.538571078399272e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.083556991885845e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.514086784927372e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.534907991183539e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.538570026746871e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.514086618166793e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.538570026746871e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.25264433212758e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.538570026746871e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9.506683340491326e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.200628114844448e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-2.023165177883678e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4.049692709954902e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.049692709954902e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1.565828715144593e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6.085770804277502e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.049692709954902e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.56588571238301e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.008214397719929e-07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.472422319519192e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>9.508583138697087e-08</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.510718097927413e-08</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3.229859519635616e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.236478861472983e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.236478861472983e-08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3.871101453849722e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6.533236578173419e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.236478861472982e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.098802915605303e-08</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="B11" t="n">
+        <v>9.508583138697082e-08</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.510718097927412e-08</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3.229859519635622e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.236478861472987e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.236478861472987e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.871101453849721e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6.53323657817342e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.236478861472987e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.098802915605309e-08</v>
+      </c>
+      <c r="K11" t="n">
         <v>1.03185634232507e-07</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L11" t="n">
         <v>5.773530496777261e-08</v>
       </c>
     </row>
@@ -1631,7 +1871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1699,321 +1939,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.241550746804986e-07</v>
+        <v>9.503939426345181e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>2.651528341159905e-07</v>
+        <v>2.65133369549779e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>2.675936937967789e-06</v>
+        <v>7.059430256392085e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.005635988237706e-07</v>
+        <v>4.316702246160089e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>2.005635988237706e-07</v>
+        <v>4.316702246160089e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.074415021229929e-06</v>
+        <v>5.419431724236747e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>3.476622679897456e-07</v>
+        <v>6.784611104947454e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.005635988237706e-07</v>
+        <v>4.316702246160089e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.05962486463863e-06</v>
+        <v>6.119991988546178e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.040571411160863e-07</v>
+        <v>1.041944438402712e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>2.176973340858179e-07</v>
+        <v>5.864185574584623e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.237788405299081e-08</v>
+        <v>9.644288274559693e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.926237117237769e-08</v>
+        <v>2.666604637890282e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.237788405299081e-08</v>
+        <v>6.860578367158989e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.862674048732737e-08</v>
+        <v>4.368730540359019e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.862674048732738e-08</v>
+        <v>4.368730540359019e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.193755406297226e-08</v>
+        <v>5.387530014278776e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.237788405299081e-08</v>
+        <v>6.860578367158989e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.942794433711447e-08</v>
+        <v>4.368730540359019e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.237788405299081e-08</v>
+        <v>6.102656827366859e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.237788405299081e-08</v>
+        <v>1.05665649738122e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>5.237788405299081e-08</v>
+        <v>5.939765407665171e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.623553736582241e-08</v>
+        <v>1.241550746804986e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>4.314359141454922e-08</v>
+        <v>2.6515283411599e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>8.89970339877642e-08</v>
+        <v>2.675936937967795e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>3.973455208376208e-08</v>
+        <v>2.005635988237703e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>4.182035809847546e-08</v>
+        <v>2.005635988237703e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>8.579520737580384e-08</v>
+        <v>1.074415021229926e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>9.529111864688733e-08</v>
+        <v>3.476622679897445e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>4.192678720012733e-08</v>
+        <v>2.005635988237703e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>4.613868545592488e-08</v>
+        <v>1.059624864638627e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>4.361944122660295e-08</v>
+        <v>2.040571411160863e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>4.488320522410399e-08</v>
+        <v>2.176973340858179e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.584078607331042e-08</v>
+        <v>5.237788405299055e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.582415668582062e-08</v>
+        <v>4.926237117237767e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.583429950187965e-08</v>
+        <v>5.237788405299055e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.29324801454624e-08</v>
+        <v>4.862674048732731e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.29324801454624e-08</v>
+        <v>4.862674048732727e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.540045608329182e-08</v>
+        <v>5.193755406297215e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.584078607331042e-08</v>
+        <v>5.237788405299055e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.289084635743405e-08</v>
+        <v>4.942794433711447e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.584078607331042e-08</v>
+        <v>5.237788405299055e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.584078607331042e-08</v>
+        <v>5.237788405299055e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.584078607331042e-08</v>
+        <v>5.237788405299055e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.39858399498169e-07</v>
+        <v>8.623553736582245e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.123517982445633e-07</v>
+        <v>4.314359141454983e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.273283065376555e-07</v>
+        <v>8.89970339877641e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.895960652195689e-07</v>
+        <v>3.973455208376219e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.392336383774029e-07</v>
+        <v>4.182035809847554e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.118655247508525e-07</v>
+        <v>8.579520737580372e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.12305854741519e-07</v>
+        <v>9.529111864688696e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.093559150249948e-07</v>
+        <v>4.192678720012733e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.123200927339714e-07</v>
+        <v>4.613868545592503e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.385126508199346e-07</v>
+        <v>4.361944122660304e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.879832796996333e-07</v>
+        <v>4.48832052241041e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.684793882786209e-07</v>
+        <v>8.584078607331037e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.079109738122671e-07</v>
+        <v>8.582415668582066e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.07927680637731e-07</v>
+        <v>8.583429950187962e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.505001564403504e-07</v>
+        <v>8.29324801454624e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.049776789818446e-07</v>
+        <v>8.29324801454624e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.074872732097383e-07</v>
+        <v>8.540045608329171e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.079276031997574e-07</v>
+        <v>8.584078607331037e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.049776634838809e-07</v>
+        <v>8.2890846357434e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.079276031997574e-07</v>
+        <v>8.584078607331037e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.85071185119466e-07</v>
+        <v>8.584078607331037e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.079276031997574e-07</v>
+        <v>8.584078607331037e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.4379792991303e-08</v>
+        <v>1.398583994981687e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>2.136241753878252e-08</v>
+        <v>2.123517982445627e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>4.6889451010394e-09</v>
+        <v>2.273283065376554e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>4.013631468499808e-08</v>
+        <v>1.895960652195688e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>4.013631468499808e-08</v>
+        <v>1.392336383774027e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>2.97525597044229e-08</v>
+        <v>2.118655247508523e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>6.238186862733656e-08</v>
+        <v>2.123058547415188e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>4.013631468499808e-08</v>
+        <v>2.093559150249948e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>3.780546191050799e-08</v>
+        <v>2.123200927339715e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>1.020777178979146e-07</v>
+        <v>1.385126508199345e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.604812043111669e-08</v>
+        <v>2.87983279699633e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.684793882786206e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.07910973812267e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.079276806377306e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.5050015644035e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.049776789818444e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.07487273209738e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.079276031997569e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.049776634838808e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.079276031997569e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.850711851194657e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.079276031997569e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9.437979299130295e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.136241753878253e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>4.688945101039241e-09</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4.013631468499804e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.013631468499804e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.975255970442305e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6.238186862733656e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.013631468499804e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.780546191050793e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.020777178979142e-07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.604812043111663e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>9.410068185057104e-08</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>9.410068185057098e-08</v>
+      </c>
+      <c r="C11" t="n">
         <v>2.410016893106089e-08</v>
       </c>
-      <c r="D9" t="n">
-        <v>4.151193732344165e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.155131036830552e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.155131036830552e-08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4.321839346829909e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6.501420986989895e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.155131036830552e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.063424248894866e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.025619234189166e-07</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5.71178072627975e-08</v>
+      <c r="D11" t="n">
+        <v>4.151193732344159e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.155131036830545e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.155131036830545e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.321839346829907e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6.501420986989893e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.155131036830545e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.063424248894849e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.025619234189163e-07</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.711780726279752e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2027,7 +2347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2095,321 +2415,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.041731537190035e-07</v>
+        <v>9.431911862152795e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>2.037519987820467e-07</v>
+        <v>2.555857391161949e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.836857284092334e-06</v>
+        <v>6.866139577792351e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.520894132202871e-07</v>
+        <v>4.208291008918805e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.520894132202871e-07</v>
+        <v>4.208291008918805e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>6.276954754195297e-07</v>
+        <v>5.224530996580979e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.729169579525103e-07</v>
+        <v>6.681222248132446e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.520894132202871e-07</v>
+        <v>4.208291008918805e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>7.757460788661339e-07</v>
+        <v>5.849014495711858e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.424974630921816e-07</v>
+        <v>1.030082301646331e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.724643866126646e-07</v>
+        <v>5.764149807557747e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.229930626123263e-08</v>
+        <v>9.574393748769904e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>5.000810807230971e-08</v>
+        <v>2.577650968269912e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.229930626123261e-08</v>
+        <v>6.764450636447802e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.824490359781211e-08</v>
+        <v>4.264943851309437e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.824490359781211e-08</v>
+        <v>4.264943851309437e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.191614867310623e-08</v>
+        <v>5.241913607343531e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.229930626123261e-08</v>
+        <v>6.764450636447802e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.972646631705128e-08</v>
+        <v>4.264943851309437e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.229930626123261e-08</v>
+        <v>5.86046610941729e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.229930626123261e-08</v>
+        <v>1.045427311362033e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>5.229930626123261e-08</v>
+        <v>5.84379770152728e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.402744808220838e-08</v>
+        <v>1.041731537190037e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>4.287701115780258e-08</v>
+        <v>2.037519987820469e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>4.686648619128194e-08</v>
+        <v>1.836857284092333e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>3.972675371469693e-08</v>
+        <v>1.520894132202872e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>4.139939473791443e-08</v>
+        <v>1.520894132202872e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>8.341800705167387e-08</v>
+        <v>6.276954754195272e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>9.371026110411061e-08</v>
+        <v>2.729169579525109e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>8.12283246956188e-08</v>
+        <v>1.520894132202872e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>8.592719103973482e-08</v>
+        <v>7.757460788661341e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>4.321662366125641e-08</v>
+        <v>1.424974630921818e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>4.402046030334954e-08</v>
+        <v>1.724643866126647e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.455759966678947e-08</v>
+        <v>5.22993062612326e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.455952944081333e-08</v>
+        <v>5.000810807230979e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.455111587097352e-08</v>
+        <v>5.22993062612326e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.204965344856139e-08</v>
+        <v>4.824490359781218e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.204965344856139e-08</v>
+        <v>4.824490359781221e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.417444207866306e-08</v>
+        <v>5.191614867310619e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.455759966678947e-08</v>
+        <v>5.22993062612326e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.198475972260816e-08</v>
+        <v>4.97264663170513e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.455759966678947e-08</v>
+        <v>5.22993062612326e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.455759966678947e-08</v>
+        <v>5.22993062612326e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.455759966678947e-08</v>
+        <v>5.22993062612326e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.376215384198434e-07</v>
+        <v>4.402744808220858e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.085825944521582e-07</v>
+        <v>4.287701115780267e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.231924553888093e-07</v>
+        <v>4.686648619127751e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.866132175542814e-07</v>
+        <v>3.972675371469705e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.373378941976006e-07</v>
+        <v>4.139939473791461e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.08112986590988e-07</v>
+        <v>8.341800705167381e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.084961441802433e-07</v>
+        <v>9.371026110411084e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.05923304234933e-07</v>
+        <v>8.122832469561893e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.085100730598503e-07</v>
+        <v>8.592719103973499e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.363050062279301e-07</v>
+        <v>4.321662366125664e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.825305963325874e-07</v>
+        <v>4.402046030334967e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.521402658802744e-07</v>
+        <v>8.455759966678957e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.870057846507428e-07</v>
+        <v>8.455952944081348e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.870039179454378e-07</v>
+        <v>8.455111587097365e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.246629327998853e-07</v>
+        <v>8.204965344856159e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.844310296366633e-07</v>
+        <v>8.204965344856159e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.866206972885924e-07</v>
+        <v>8.417444207866322e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.870038548767191e-07</v>
+        <v>8.455759966678957e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.844310149325375e-07</v>
+        <v>8.198475972260828e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.870038548767191e-07</v>
+        <v>8.455759966678957e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.659842359470475e-07</v>
+        <v>8.455759966678957e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.870038548767191e-07</v>
+        <v>8.455759966678957e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.41530530549478e-08</v>
+        <v>1.376215384198438e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>2.192446920912125e-08</v>
+        <v>2.085825944521582e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>2.419453611154883e-08</v>
+        <v>2.23192455388809e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>4.02721555375309e-08</v>
+        <v>1.866132175542815e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>4.02721555375309e-08</v>
+        <v>1.373378941976005e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>3.887089574301428e-08</v>
+        <v>2.081129865909879e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>6.302279968638249e-08</v>
+        <v>2.084961441802431e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>4.02721555375309e-08</v>
+        <v>2.059233042349331e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>4.195314126077713e-08</v>
+        <v>2.085100730598504e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>1.02444406259735e-07</v>
+        <v>1.363050062279302e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.603630490757832e-08</v>
+        <v>2.825305963325876e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.521402658802743e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.87005784650743e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.87003917945438e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.246629327998856e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.844310296366634e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.866206972885927e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.870038548767191e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.844310149325377e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.870038548767191e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.659842359470478e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.870038548767191e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9.415305305494789e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.192446920912126e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.419453611154892e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4.02721555375309e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.02721555375309e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.887089574301434e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6.30227996863825e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.02721555375309e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.195314126077726e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.024444062597354e-07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.603630490757831e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>9.359526113477823e-08</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>9.359526113477834e-08</v>
+      </c>
+      <c r="C11" t="n">
         <v>2.380588322041693e-08</v>
       </c>
-      <c r="D9" t="n">
-        <v>4.889152084600131e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.100123875935532e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.100123875935532e-08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4.608081743978807e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6.470933121428577e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.100123875935532e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.09136503676783e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.020534856588754e-07</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5.654872961290165e-08</v>
+      <c r="D11" t="n">
+        <v>4.889152084600138e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.100123875935533e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.100123875935533e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.608081743978809e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6.470933121428579e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.100123875935533e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.091365036767839e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.020534856588756e-07</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.654872961290161e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2423,7 +2823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2491,321 +2891,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.311982352188964e-07</v>
+        <v>9.717301696940688e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.230865380150212e-07</v>
+        <v>2.582499248234716e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>2.235559612580156e-06</v>
+        <v>6.971096465998843e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.311828981725897e-07</v>
+        <v>4.28806355015432e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>2.311828981725897e-07</v>
+        <v>4.28806355015432e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.157216196650619e-06</v>
+        <v>5.433654806286202e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>4.394780240715981e-07</v>
+        <v>6.768476896626529e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.311828981725897e-07</v>
+        <v>4.28806355015432e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.056842521608991e-06</v>
+        <v>6.056892975746159e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.66773183398707e-07</v>
+        <v>1.044135943469682e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>4.338716358076104e-07</v>
+        <v>5.904723162176564e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.305883975270714e-08</v>
+        <v>9.860937057116875e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.853866136308164e-08</v>
+        <v>2.61374364674271e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.305883975270714e-08</v>
+        <v>6.836810735567329e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.722898400648722e-08</v>
+        <v>4.337435997730458e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.722898400648722e-08</v>
+        <v>4.337435997730458e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.271714823305021e-08</v>
+        <v>5.399383948035486e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.305883975270714e-08</v>
+        <v>6.836810735567329e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.076628194939309e-08</v>
+        <v>4.337435997730458e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.305883975270714e-08</v>
+        <v>6.045093436981455e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.305883975270714e-08</v>
+        <v>1.058299109775689e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>5.305883975270714e-08</v>
+        <v>5.960783685026349e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.472431709766736e-08</v>
+        <v>1.311982352188968e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>4.249299598364385e-08</v>
+        <v>1.230865380150215e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>4.780923465562937e-08</v>
+        <v>2.235559612580156e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>3.998555277193534e-08</v>
+        <v>2.311828981725946e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>4.233034998124393e-08</v>
+        <v>2.311828981725946e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>4.438262557801046e-08</v>
+        <v>1.157216196650619e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>9.743921735139269e-08</v>
+        <v>4.394780240716124e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>8.609771902734273e-08</v>
+        <v>2.311828981725946e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>4.598718604161584e-08</v>
+        <v>1.056842521608993e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>4.35006271482806e-08</v>
+        <v>2.667731833987075e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>4.480123692364427e-08</v>
+        <v>4.338716358076114e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.831144195827666e-08</v>
+        <v>5.305883975270728e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.829081594302537e-08</v>
+        <v>4.853866136308162e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.830454230097967e-08</v>
+        <v>5.305883975270728e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.611419457427141e-08</v>
+        <v>4.722898400648735e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.611419457427141e-08</v>
+        <v>4.722898400648736e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.796975043861969e-08</v>
+        <v>5.271714823305034e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.831144195827666e-08</v>
+        <v>5.305883975270728e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.601888415496257e-08</v>
+        <v>5.076628194939322e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.831144195827666e-08</v>
+        <v>5.305883975270728e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.831144195827666e-08</v>
+        <v>5.305883975270728e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.831144195827666e-08</v>
+        <v>5.305883975270728e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.44987734382844e-07</v>
+        <v>4.472431709766753e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.211629995714622e-07</v>
+        <v>4.249299598364722e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.368443595965869e-07</v>
+        <v>4.780923465562942e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.980692988020615e-07</v>
+        <v>3.998555277193556e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.451677930957156e-07</v>
+        <v>4.233034998124407e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.207268227466146e-07</v>
+        <v>4.438262557801058e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.210685142665716e-07</v>
+        <v>9.743921735139279e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.187759564629575e-07</v>
+        <v>8.609771902734303e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.210834663145083e-07</v>
+        <v>4.598718604161591e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.435744948338365e-07</v>
+        <v>4.350062714828061e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.005412506279109e-07</v>
+        <v>4.480123692364425e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.861893425490552e-07</v>
+        <v>8.831144195827701e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.306775780122037e-07</v>
+        <v>8.829081594302582e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.306982865424791e-07</v>
+        <v>8.830454230097998e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.797680236825564e-07</v>
+        <v>8.611419457427201e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.28405662592792e-07</v>
+        <v>8.611419457427201e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.303565125077983e-07</v>
+        <v>8.796975043862008e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.306982040274551e-07</v>
+        <v>8.831144195827701e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.284056462241411e-07</v>
+        <v>8.601888415496286e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.30698204027455e-07</v>
+        <v>8.831144195827701e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.049096295925802e-07</v>
+        <v>8.831144195827701e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.30698204027455e-07</v>
+        <v>8.831144195827701e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.649893865028339e-08</v>
+        <v>1.449877343828445e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>2.431244566324228e-08</v>
+        <v>2.211629995714633e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>1.802998199430649e-08</v>
+        <v>2.368443595965882e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>3.935060622987188e-08</v>
+        <v>1.980692988020623e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>3.935060622987188e-08</v>
+        <v>1.451677930957161e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>2.931449686863259e-08</v>
+        <v>2.207268227466153e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>6.062614012199741e-08</v>
+        <v>2.210685142665724e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>3.935060622987188e-08</v>
+        <v>2.187759564629584e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>3.8542314275552e-08</v>
+        <v>2.210834663145091e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>1.01013277252604e-07</v>
+        <v>1.435744948338369e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.214109054349939e-08</v>
+        <v>3.005412506279118e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.861893425490561e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.306775780122046e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.3069828654248e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.797680236825579e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.284056625927928e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.303565125077991e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.306982040274561e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.284056462241421e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.306982040274561e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.04909629592581e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.306982040274561e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9.649893865028343e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.431244566324234e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.802998199430662e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.935060622987206e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3.935060622987206e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.931449686863269e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6.062614012199734e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.935060622987206e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.854231427555245e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.010132772526045e-07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.214109054349957e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>9.621276371985654e-08</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.499461585054237e-08</v>
-      </c>
-      <c r="D9" t="n">
-        <v>4.680695720247914e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.104981472351884e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.104981472351884e-08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4.310736852612991e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6.416214920275694e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.104981472351884e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.06004377959423e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.022220106524079e-07</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5.564983825707918e-08</v>
+      <c r="B11" t="n">
+        <v>9.621276371985663e-08</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.499461585054249e-08</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.680695720247931e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.104981472351902e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.104981472351902e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.310736852613008e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6.41621492027571e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.104981472351902e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.06004377959427e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.022220106524086e-07</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.564983825707934e-08</v>
       </c>
     </row>
   </sheetData>
@@ -2819,7 +3299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2887,321 +3367,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.023248337249542e-07</v>
+        <v>9.597884155119562e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.100358726570036e-07</v>
+        <v>2.396417920014614e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.539709852106313e-07</v>
+        <v>6.493775095258084e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.901093754983884e-07</v>
+        <v>4.089098836171753e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.901093754983884e-07</v>
+        <v>4.089098836171753e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.791405198082798e-07</v>
+        <v>5.030296190549187e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.776064410510904e-07</v>
+        <v>6.494862958973944e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.901093754983884e-07</v>
+        <v>4.089098836171753e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>6.665907946515706e-07</v>
+        <v>5.655786536763857e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.298319342049669e-07</v>
+        <v>1.014900973167014e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.968166064252032e-07</v>
+        <v>5.59545901549562e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.987711788079796e-08</v>
+        <v>9.744231356970674e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.747576497531786e-08</v>
+        <v>2.427459494543501e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>4.987711788079796e-08</v>
+        <v>6.586245332429109e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.721357849295159e-08</v>
+        <v>4.139920360798335e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.721357849295159e-08</v>
+        <v>4.139920360798335e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>4.94704286610448e-08</v>
+        <v>5.097161127005558e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>4.987711788079796e-08</v>
+        <v>6.586245332429109e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.714111838987816e-08</v>
+        <v>4.139920360798335e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>4.987711788079796e-08</v>
+        <v>5.677495585358206e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>4.987711788079796e-08</v>
+        <v>1.030250433603627e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>4.987711788079796e-08</v>
+        <v>5.670880365757232e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.062790162026407e-08</v>
+        <v>1.023248337249541e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>3.990187300539363e-08</v>
+        <v>1.100358726570034e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>7.935180757439641e-08</v>
+        <v>1.539709852106311e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>3.70626074398574e-08</v>
+        <v>1.901093754983885e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>3.793832937205919e-08</v>
+        <v>1.901093754983885e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>4.022121240051097e-08</v>
+        <v>1.791405198082818e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>8.606383554601551e-08</v>
+        <v>1.776064410510903e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>7.474400095579171e-08</v>
+        <v>1.901093754983885e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>7.917638298077978e-08</v>
+        <v>6.665907946515702e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>4.030518430816234e-08</v>
+        <v>1.29831934204967e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>4.063958370606556e-08</v>
+        <v>1.968166064252028e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.944158339081244e-08</v>
+        <v>4.987711788079785e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.946409599471044e-08</v>
+        <v>4.747576497531782e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.94350782090638e-08</v>
+        <v>4.987711788079783e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.684605723895671e-08</v>
+        <v>4.721357849295166e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.684605723895671e-08</v>
+        <v>4.721357849295166e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.903489417105937e-08</v>
+        <v>4.947042866104478e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.944158339081244e-08</v>
+        <v>4.987711788079785e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.67055838998928e-08</v>
+        <v>4.714111838987824e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.944158339081244e-08</v>
+        <v>4.987711788079785e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.944158339081244e-08</v>
+        <v>4.987711788079785e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.944158339081244e-08</v>
+        <v>4.987711788079785e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.299678979123565e-07</v>
+        <v>4.062790162026411e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.969659778975277e-07</v>
+        <v>3.990187300539382e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.10642968985424e-07</v>
+        <v>7.93518075743963e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.759143228404528e-07</v>
+        <v>3.706260743985752e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.294376561679356e-07</v>
+        <v>3.793832937205934e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.963808018369662e-07</v>
+        <v>4.02212124005111e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.96787491057353e-07</v>
+        <v>8.606383554601573e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.940514915657997e-07</v>
+        <v>7.474400095579182e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.96800623016759e-07</v>
+        <v>7.917638298077997e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.287266896616744e-07</v>
+        <v>4.030518430816299e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.665861434625293e-07</v>
+        <v>4.063958370606568e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.465741113156581e-07</v>
+        <v>7.944158339081241e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.802725736276547e-07</v>
+        <v>7.946409599471034e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.802501095507091e-07</v>
+        <v>7.943507820906383e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.163754566132561e-07</v>
+        <v>7.684605723895674e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.77514076969165e-07</v>
+        <v>7.684605723895674e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.798433718040037e-07</v>
+        <v>7.903489417105926e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.802500610237566e-07</v>
+        <v>7.944158339081241e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.775140615328372e-07</v>
+        <v>7.670558389989275e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.802500610237566e-07</v>
+        <v>7.944158339081241e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.607381039174713e-07</v>
+        <v>7.944158339081241e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.802500610237566e-07</v>
+        <v>7.944158339081241e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.585942084726616e-08</v>
+        <v>1.299678979123565e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>2.259932102590835e-08</v>
+        <v>1.969659778975281e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>6.342495566467972e-08</v>
+        <v>2.106429689854237e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>3.805139830342909e-08</v>
+        <v>1.759143228404531e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>3.805139830342909e-08</v>
+        <v>1.294376561679357e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>4.799803515845464e-08</v>
+        <v>1.963808018369662e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>6.324746752957876e-08</v>
+        <v>1.96787491057353e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>3.805139830342909e-08</v>
+        <v>1.940514915657997e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>4.260509289239975e-08</v>
+        <v>1.968006230167592e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>1.011858343440749e-07</v>
+        <v>1.287266896616742e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.374998403902574e-08</v>
+        <v>2.66586143462529e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.46574111315658e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.802725736276549e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.802501095507091e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.163754566132562e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.775140769691649e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.798433718040039e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.802500610237566e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.775140615328374e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.802500610237566e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.607381039174714e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.802500610237566e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9.585942084726617e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.259932102590839e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.342495566467975e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.805139830342906e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3.805139830342906e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.799803515845466e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6.324746752957872e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.805139830342906e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.260509289239963e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.011858343440752e-07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.374998403902574e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>9.525862031810546e-08</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.320192422798033e-08</v>
-      </c>
-      <c r="D9" t="n">
-        <v>6.382868174961359e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3.936772627932294e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3.936772627932294e-08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4.894997529848855e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6.375880271968007e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.936772627932294e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.01105325636267e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.00653251353079e-07</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5.460831779931893e-08</v>
+      <c r="B11" t="n">
+        <v>9.52586203181054e-08</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.320192422798028e-08</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.382868174961357e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.936772627932287e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3.936772627932287e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.894997529848863e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6.375880271968001e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.936772627932287e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.011053256362668e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.006532513530792e-07</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.460831779931896e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3215,7 +3775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3283,321 +3843,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.00183040040855e-07</v>
+        <v>9.725578948691843e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.12155595128191e-07</v>
+        <v>2.383536724086641e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.513079827743596e-07</v>
+        <v>6.476560741518202e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.59851240541686e-07</v>
+        <v>4.036248296697718e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.59851240541686e-07</v>
+        <v>4.036248296697718e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.419087778284487e-07</v>
+        <v>5.002859403930414e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.639482821063557e-07</v>
+        <v>6.476537452152911e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.59851240541686e-07</v>
+        <v>4.036248296697718e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>4.93284478771414e-07</v>
+        <v>5.515341638461913e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.196361164240528e-07</v>
+        <v>1.011502669542902e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.655726388933614e-07</v>
+        <v>5.57266949927037e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.067503295666443e-08</v>
+        <v>9.87441038370713e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.8893388585154e-08</v>
+        <v>2.414342580821875e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.067503295666443e-08</v>
+        <v>6.569286077794329e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.721677555659023e-08</v>
+        <v>4.090018998214198e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.721677555659023e-08</v>
+        <v>4.090018998214198e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.031086350306292e-08</v>
+        <v>5.073797440038939e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.067503295666443e-08</v>
+        <v>6.569286077794329e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.822288371028779e-08</v>
+        <v>4.090018998214198e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.067503295666443e-08</v>
+        <v>5.554647410803526e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.067503295666443e-08</v>
+        <v>1.026939636375852e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>5.067503295666443e-08</v>
+        <v>5.651179532660464e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.870311915163364e-08</v>
+        <v>1.001830400408554e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>4.094214461190412e-08</v>
+        <v>1.12155595128191e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>4.154955693188209e-08</v>
+        <v>1.513079827743599e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>3.813343318683268e-08</v>
+        <v>1.598512405416863e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>3.912320009626188e-08</v>
+        <v>1.598512405416863e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>7.833894969803315e-08</v>
+        <v>1.419087778284516e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>4.155619903954523e-08</v>
+        <v>1.639482821063559e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>7.625096990525686e-08</v>
+        <v>1.598512405416863e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>4.248708513391592e-08</v>
+        <v>4.932844787714141e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>4.126873362224431e-08</v>
+        <v>1.196361164240535e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>4.154498536227719e-08</v>
+        <v>1.655726388933617e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.017906860262552e-08</v>
+        <v>5.067503295666494e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.020252729241389e-08</v>
+        <v>4.889338858515345e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.017254895498012e-08</v>
+        <v>5.067503295666494e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.784075377309767e-08</v>
+        <v>4.721677555659028e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.784075377309767e-08</v>
+        <v>4.721677555659029e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.981489914902454e-08</v>
+        <v>5.031086350306419e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.017906860262552e-08</v>
+        <v>5.067503295666494e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.772691935624864e-08</v>
+        <v>4.822288371028793e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.017906860262552e-08</v>
+        <v>5.067503295666494e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.017906860262552e-08</v>
+        <v>5.067503295666494e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.017906860262552e-08</v>
+        <v>5.067503295666494e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.309251456377319e-07</v>
+        <v>7.870311915163394e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.980535309067919e-07</v>
+        <v>4.094214461190403e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.117870461750657e-07</v>
+        <v>4.154955693188221e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.772451119838022e-07</v>
+        <v>3.813343318683282e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.306677764594148e-07</v>
+        <v>3.912320009626168e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.975353119108923e-07</v>
+        <v>7.833894969803332e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.97899481365617e-07</v>
+        <v>4.155619903954519e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.954473321181158e-07</v>
+        <v>7.625096990525701e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.979126437326e-07</v>
+        <v>4.248708513391596e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.296810629638865e-07</v>
+        <v>4.126873362224432e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.678597753358449e-07</v>
+        <v>4.154498536227771e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.40269631550895e-07</v>
+        <v>8.017906860262558e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.720281256707793e-07</v>
+        <v>8.020252729241377e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.720047144422182e-07</v>
+        <v>8.017254895498028e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.061741374759298e-07</v>
+        <v>7.784075377309767e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.69552532808601e-07</v>
+        <v>7.784075377309767e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.716404975273901e-07</v>
+        <v>7.981489914902481e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.720046669809905e-07</v>
+        <v>8.017906860262558e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.695525177346139e-07</v>
+        <v>7.772691935624845e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.720046669809905e-07</v>
+        <v>8.017906860262558e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.536172827816996e-07</v>
+        <v>8.017906860262558e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.720046669809905e-07</v>
+        <v>8.017906860262558e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.722668310341742e-08</v>
+        <v>1.30925145637732e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>2.243419166462542e-08</v>
+        <v>1.980535309067919e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>6.333650715823837e-08</v>
+        <v>2.117870461750659e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>3.83059936422989e-08</v>
+        <v>1.772451119838021e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>3.83059936422989e-08</v>
+        <v>1.306677764594147e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>4.866277883544905e-08</v>
+        <v>1.97535311910892e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>6.338594527490598e-08</v>
+        <v>1.97899481365617e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>3.83059936422989e-08</v>
+        <v>1.954473321181158e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>4.540634966080819e-08</v>
+        <v>1.979126437326005e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>1.011185774782375e-07</v>
+        <v>1.296810629638867e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.422584840317511e-08</v>
+        <v>2.678597753358447e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.402696315508949e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.720281256707792e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.720047144422179e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.061741374759298e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.695525328086012e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.716404975273901e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.720046669809911e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.695525177346139e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.720046669809911e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.536172827816991e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.720046669809911e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9.722668310341758e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.243419166462534e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.33365071582384e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.830599364229888e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3.830599364229888e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.866277883544918e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6.33859452749061e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.830599364229888e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.54063496608082e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.011185774782376e-07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.422584840317501e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>9.656535821737301e-08</v>
       </c>
-      <c r="C9" t="n">
-        <v>2.305766025852528e-08</v>
-      </c>
-      <c r="D9" t="n">
-        <v>6.369345900896296e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3.918211536513538e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3.918211536513538e-08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4.908437344400027e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6.371572061594352e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.918211536513538e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.053962744647162e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.00433461231329e-07</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5.468658185766244e-08</v>
+      <c r="C11" t="n">
+        <v>2.305766025852526e-08</v>
+      </c>
+      <c r="D11" t="n">
+        <v>6.369345900896284e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.91821153651354e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3.91821153651354e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.908437344400046e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6.371572061594366e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.91821153651354e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.053962744647154e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.004334612313291e-07</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.468658185766266e-08</v>
       </c>
     </row>
   </sheetData>
@@ -3611,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3679,321 +4319,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.227362748174471e-07</v>
+        <v>9.665896672702892e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>1.189065703227136e-07</v>
+        <v>2.489104507154606e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>4.266127296845137e-07</v>
+        <v>6.616283442368789e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.192598099246536e-07</v>
+        <v>4.167998157014001e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>2.192598099246536e-07</v>
+        <v>4.167998157014e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>4.885836228001124e-07</v>
+        <v>5.17460105735692e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>3.823455434106101e-07</v>
+        <v>6.607542111785351e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.192598099246536e-07</v>
+        <v>4.167998157014e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>8.912787726321672e-07</v>
+        <v>5.804004895144237e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.727807752286674e-07</v>
+        <v>1.025829025465755e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>3.923162837531198e-07</v>
+        <v>5.742202413429773e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.162290703509224e-08</v>
+        <v>9.810995107561524e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.760142708227327e-08</v>
+        <v>2.520614987779549e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.162290703509224e-08</v>
+        <v>6.680390295670056e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.643567113708026e-08</v>
+        <v>4.21758191321228e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.643567113708026e-08</v>
+        <v>4.21758191321228e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.130460981095087e-08</v>
+        <v>5.210406346543666e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.162290703509224e-08</v>
+        <v>6.680390295670056e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.947933372122877e-08</v>
+        <v>4.21758191321228e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.162290703509224e-08</v>
+        <v>5.807251150345384e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.162290703509224e-08</v>
+        <v>1.040881643665119e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>5.162290703509224e-08</v>
+        <v>5.801091039037396e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.219656546407438e-08</v>
+        <v>1.227362748174472e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>4.091750946320765e-08</v>
+        <v>1.189065703227136e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>4.251141582522722e-08</v>
+        <v>4.266127296845134e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>3.855915080071279e-08</v>
+        <v>2.192598099246539e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>4.005196759663763e-08</v>
+        <v>2.192598099246539e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>4.187826823993305e-08</v>
+        <v>4.88583622800121e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>9.15090129070758e-08</v>
+        <v>3.823455434106095e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>4.005299215021073e-08</v>
+        <v>2.192598099246539e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>4.330793549013562e-08</v>
+        <v>8.912787726321691e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>4.160170046737533e-08</v>
+        <v>1.727807752286672e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>4.226313257379024e-08</v>
+        <v>3.923162837531195e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.416509231158724e-08</v>
+        <v>5.162290703509211e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.417457625524411e-08</v>
+        <v>4.76014270822734e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.415820369501657e-08</v>
+        <v>5.162290703509211e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.214865515403499e-08</v>
+        <v>4.643567113708018e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.214865515403499e-08</v>
+        <v>4.64356711370803e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.384679508744618e-08</v>
+        <v>5.13046098109512e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.416509231158724e-08</v>
+        <v>5.162290703509211e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.202151899772346e-08</v>
+        <v>4.947933372122883e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.416509231158724e-08</v>
+        <v>5.162290703509211e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.416509231158724e-08</v>
+        <v>5.162290703509211e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.416509231158724e-08</v>
+        <v>5.162290703509211e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.384813047414026e-07</v>
+        <v>4.219656546407409e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.10936211280496e-07</v>
+        <v>4.091750946320783e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.257739562848744e-07</v>
+        <v>4.251141582522676e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.889920791207445e-07</v>
+        <v>3.855915080071257e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.387095024312648e-07</v>
+        <v>4.005196759663755e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.104636498722218e-07</v>
+        <v>4.187826823993323e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.107819470966565e-07</v>
+        <v>9.150901290707573e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.086383737824986e-07</v>
+        <v>4.005299215021064e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.107961562397707e-07</v>
+        <v>4.330793549013524e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.37138283187658e-07</v>
+        <v>4.160170046737566e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.863060137200394e-07</v>
+        <v>4.226313257379021e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.689979481507096e-07</v>
+        <v>8.416509231158678e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.08916017128316e-07</v>
+        <v>8.417457625524418e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.089065925898281e-07</v>
+        <v>8.415820369501626e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.528166928331353e-07</v>
+        <v>8.214865515403507e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.067629745354662e-07</v>
+        <v>8.214865515403507e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.085882359605178e-07</v>
+        <v>8.38467950874459e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.089065331846592e-07</v>
+        <v>8.416509231158678e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.067629598707952e-07</v>
+        <v>8.202151899772341e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.089065331846592e-07</v>
+        <v>8.416509231158678e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.857833672684631e-07</v>
+        <v>8.416509231158678e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.089065331846592e-07</v>
+        <v>8.416509231158678e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>9.616960241481308e-08</v>
+        <v>1.384813047414024e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>2.344457726571739e-08</v>
+        <v>2.109362112804961e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>5.823857040389997e-08</v>
+        <v>2.257739562848746e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>3.839566365689299e-08</v>
+        <v>1.889920791207446e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>3.839566365689299e-08</v>
+        <v>1.387095024312647e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>4.239139521496821e-08</v>
+        <v>2.104636498722211e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>6.019617355133824e-08</v>
+        <v>2.107819470966567e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>3.839566365689299e-08</v>
+        <v>2.086383737824986e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>3.976471979067894e-08</v>
+        <v>2.107961562397704e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>1.014019123895945e-07</v>
+        <v>1.37138283187658e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.134448119477221e-08</v>
+        <v>2.863060137200392e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.689979481507095e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.089160171283159e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.089065925898276e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.528166928331355e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.067629745354662e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.085882359605177e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.089065331846587e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.067629598707953e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.089065331846587e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.85783367268463e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.089065331846587e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>9.616960241481292e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.344457726571747e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5.823857040389995e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.839566365689298e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3.839566365689298e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.239139521496802e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6.019617355133822e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.839566365689298e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3.976471979067907e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.014019123895942e-07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.134448119477211e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>9.57761019028399e-08</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.408952391925166e-08</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B11" t="n">
+        <v>9.577610190283955e-08</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.408952391925172e-08</v>
+      </c>
+      <c r="D11" t="n">
         <v>6.22655808160684e-08</v>
       </c>
-      <c r="E9" t="n">
-        <v>3.995999878226977e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3.995999878226977e-08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4.732671556716872e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6.306888318082959e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.995999878226977e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.97099453786592e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.013606493365011e-07</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5.438877760564972e-08</v>
+      <c r="E11" t="n">
+        <v>3.995999878226973e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3.995999878226973e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.73267155671688e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6.306888318082948e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.995999878226973e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.970994537865942e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.013606493365009e-07</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.438877760564958e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4007,7 +4727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4075,321 +4795,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.093762764317297e-07</v>
+        <v>1.029506070105996e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.122264383389444e-07</v>
+        <v>2.428008598064372e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.530767380113777e-07</v>
+        <v>6.46860714288438e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.850240857529553e-07</v>
+        <v>4.085163900984577e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.850240857529553e-07</v>
+        <v>4.085163900984577e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.481893750036532e-07</v>
+        <v>5.085749015499033e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.691205143770042e-07</v>
+        <v>6.468910304919163e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.850240857529553e-07</v>
+        <v>4.085163900984577e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>6.795502139351482e-07</v>
+        <v>5.632606287226696e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.440315533290705e-07</v>
+        <v>1.019939940741568e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.781654125386858e-07</v>
+        <v>5.571882737495379e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.978134825341883e-08</v>
+        <v>1.04517209551796e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.733596279418545e-08</v>
+        <v>2.459336724162283e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>4.978134825341883e-08</v>
+        <v>6.560814785837582e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.721269247639687e-08</v>
+        <v>4.136530931271643e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.721269247639687e-08</v>
+        <v>4.136530931271643e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>4.937502790006995e-08</v>
+        <v>5.157091429731954e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>4.978134825341883e-08</v>
+        <v>6.560814785837582e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.704755612992626e-08</v>
+        <v>4.136530931271643e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>4.978134825341883e-08</v>
+        <v>5.652511712597986e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>4.978134825341883e-08</v>
+        <v>1.035205318853683e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>4.978134825341883e-08</v>
+        <v>5.64890033695974e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.741517145615333e-08</v>
+        <v>1.093762764317301e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>3.997422576561337e-08</v>
+        <v>1.122264383389443e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>4.081008803952631e-08</v>
+        <v>1.53076738011378e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>3.713038165965295e-08</v>
+        <v>1.850240857529555e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>3.798718982894441e-08</v>
+        <v>1.850240857529555e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>4.026364715421237e-08</v>
+        <v>1.481893750036592e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>8.595902130258754e-08</v>
+        <v>1.691205143770048e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>7.468137933266063e-08</v>
+        <v>1.850240857529555e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>4.163775017471686e-08</v>
+        <v>6.795502139351481e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>4.042712613728842e-08</v>
+        <v>1.440315533290706e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>4.067142741301268e-08</v>
+        <v>1.781654125386868e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.888489392929793e-08</v>
+        <v>4.978134825341921e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.890870269714235e-08</v>
+        <v>4.733596279418549e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.887841346041313e-08</v>
+        <v>4.978134825341921e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.631487917604324e-08</v>
+        <v>4.721269247639693e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.631487917604324e-08</v>
+        <v>4.721269247639693e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.847857357594905e-08</v>
+        <v>4.937502790006998e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.888489392929793e-08</v>
+        <v>4.978134825341921e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.615110180580543e-08</v>
+        <v>4.704755612992627e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.888489392929793e-08</v>
+        <v>4.978134825341918e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.888489392929793e-08</v>
+        <v>4.978134825341921e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.888489392929793e-08</v>
+        <v>4.978134825341921e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.290261069888069e-07</v>
+        <v>7.741517145615336e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.954667253916927e-07</v>
+        <v>3.997422576561365e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.089998491826729e-07</v>
+        <v>4.08100880395267e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.745725213556114e-07</v>
+        <v>3.713038165965295e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.284935468666349e-07</v>
+        <v>3.798718982894468e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.948585000887304e-07</v>
+        <v>4.026364715421257e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.952648204426987e-07</v>
+        <v>8.595902130258746e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.925310283185868e-07</v>
+        <v>7.468137933266092e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.952778382413041e-07</v>
+        <v>4.163775017471688e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.277956888767236e-07</v>
+        <v>4.042712613728921e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.644566954369511e-07</v>
+        <v>4.067142741301276e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.45624942352277e-07</v>
+        <v>7.888489392929776e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.790698314578047e-07</v>
+        <v>7.890870269714235e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.790460702009379e-07</v>
+        <v>7.887841346041328e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.148795111305613e-07</v>
+        <v>7.631487917604331e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.763122462039555e-07</v>
+        <v>7.631487917604331e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.786397023366114e-07</v>
+        <v>7.84785735759491e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.7904602268996e-07</v>
+        <v>7.888489392929776e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.763122305664677e-07</v>
+        <v>7.615110180580541e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7904602268996e-07</v>
+        <v>7.888489392929776e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.369629045892557e-07</v>
+        <v>7.888489392929776e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.7904602268996e-07</v>
+        <v>7.888489392929776e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.027666620866104e-07</v>
+        <v>1.290261069888066e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>2.286513726043568e-08</v>
+        <v>1.954667253916928e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>6.319000012985801e-08</v>
+        <v>2.089998491826735e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>3.813791832997739e-08</v>
+        <v>1.745725213556112e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>3.813791832997739e-08</v>
+        <v>1.28493546866635e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>4.932796598865919e-08</v>
+        <v>1.94858500088731e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>6.317347635835296e-08</v>
+        <v>1.952648204426991e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>3.813791832997739e-08</v>
+        <v>1.92531028318587e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>4.205267644276223e-08</v>
+        <v>1.952778382413044e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>1.013338560231964e-07</v>
+        <v>1.277956888767239e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.392130999471512e-08</v>
+        <v>2.644566954369519e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.456249423522766e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.790698314578049e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.790460702009382e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.148795111305614e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.763122462039557e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.786397023366118e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.790460226899605e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.763122305664681e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.790460226899605e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.369629045892556e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.790460226899605e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.027666620866105e-07</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.286513726043569e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.319000012985797e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.813791832997739e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3.813791832997739e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>4.932796598865904e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6.317347635835301e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.813791832997739e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.205267644276232e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.013338560231964e-07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.392130999471525e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1.021541023352768e-07</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.349373583166145e-08</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B11" t="n">
+        <v>1.021541023352764e-07</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.34937358316614e-08</v>
+      </c>
+      <c r="D11" t="n">
         <v>6.358580650618859e-08</v>
       </c>
-      <c r="E9" t="n">
-        <v>3.938316582761464e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3.938316582761464e-08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4.983694152669777e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6.35813197578435e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.938316582761464e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>4.9741056240471e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.00999049588346e-07</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5.455051870662907e-08</v>
+      <c r="E11" t="n">
+        <v>3.938316582761468e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3.938316582761468e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.983694152669772e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6.358131975784341e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.938316582761468e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>4.974105624047101e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.009990495883459e-07</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.455051870662895e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4403,7 +5203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4471,321 +5271,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.045517597102551e-07</v>
+        <v>1.223500308602271e-07</v>
       </c>
       <c r="C2" t="n">
-        <v>1.120880802422139e-07</v>
+        <v>2.438422911372482e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.486424718639444e-07</v>
+        <v>6.462566993613117e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>1.60223367719429e-07</v>
+        <v>4.032494352494886e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>1.60223367719429e-07</v>
+        <v>4.032494352494886e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.42301194290159e-07</v>
+        <v>5.235088324323806e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>1.640857020488908e-07</v>
+        <v>6.462868377335965e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>1.60223367719429e-07</v>
+        <v>4.032494352494886e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>4.977464822505849e-07</v>
+        <v>5.499672863051545e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>1.361668700297881e-07</v>
+        <v>1.015320166478007e-07</v>
       </c>
       <c r="L2" t="n">
-        <v>1.660452078642489e-07</v>
+        <v>5.558956675957466e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.067575311114652e-08</v>
+        <v>1.242322116208846e-07</v>
       </c>
       <c r="C3" t="n">
-        <v>4.879059450894706e-08</v>
+        <v>2.470095042535726e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.067575311114652e-08</v>
+        <v>6.55536548669157e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.721612287098855e-08</v>
+        <v>4.086144174609956e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.721612287098856e-08</v>
+        <v>4.086144174609956e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.03097822839797e-08</v>
+        <v>5.309655516873237e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.067575311114652e-08</v>
+        <v>6.55536548669157e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.821173431145123e-08</v>
+        <v>4.086144174609956e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.067575311114652e-08</v>
+        <v>5.538204700510147e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.067575311114652e-08</v>
+        <v>1.030620989483984e-07</v>
       </c>
       <c r="L3" t="n">
-        <v>5.067575311114652e-08</v>
+        <v>5.637180021775115e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.899880417969121e-08</v>
+        <v>1.045517597102552e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>4.111479249240773e-08</v>
+        <v>1.12088080242214e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>4.175360762882951e-08</v>
+        <v>1.486424718639447e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>3.829637599148661e-08</v>
+        <v>1.60223367719429e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>3.930853556735618e-08</v>
+        <v>1.60223367719429e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>4.137624636159182e-08</v>
+        <v>1.42301194290162e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>8.851252397581256e-08</v>
+        <v>1.640857020488911e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>3.927819838906343e-08</v>
+        <v>1.60223367719429e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>8.080716278664068e-08</v>
+        <v>4.977464822505853e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>4.151791359903878e-08</v>
+        <v>1.361668700297879e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>4.174337176085609e-08</v>
+        <v>1.660452078642492e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.982652642884782e-08</v>
+        <v>5.067575311114637e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.98495000681311e-08</v>
+        <v>4.879059450894716e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.982003811098141e-08</v>
+        <v>5.067575311114637e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.748134467696702e-08</v>
+        <v>4.721612287098854e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.748134467696702e-08</v>
+        <v>4.721612287098854e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.946055560168108e-08</v>
+        <v>5.03097822839796e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.982652642884782e-08</v>
+        <v>5.067575311114637e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.736250762915256e-08</v>
+        <v>4.821173431145119e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.982652642884782e-08</v>
+        <v>5.067575311114637e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.982652642884782e-08</v>
+        <v>5.067575311114637e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.982652642884782e-08</v>
+        <v>5.067575311114637e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.303065004677609e-07</v>
+        <v>7.899880417969102e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.970440103083444e-07</v>
+        <v>4.111479249240772e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.106914369029926e-07</v>
+        <v>4.175360762882925e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.763317709836495e-07</v>
+        <v>3.829637599148657e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.300277049394182e-07</v>
+        <v>3.930853556735621e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.965198170975734e-07</v>
+        <v>4.137624636159186e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.968857879258506e-07</v>
+        <v>8.851252397581247e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.944217691250446e-07</v>
+        <v>3.927819838906359e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.968988726528563e-07</v>
+        <v>8.080716278664058e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.290697560184937e-07</v>
+        <v>4.15179135990388e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.664334209433344e-07</v>
+        <v>4.174337176085622e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.400678749335832e-07</v>
+        <v>7.982652642884778e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.717692304704784e-07</v>
+        <v>7.984950006813114e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.7174630430569e-07</v>
+        <v>7.982003811098105e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.058384812692889e-07</v>
+        <v>7.748134467696711e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.692822534732608e-07</v>
+        <v>7.748134467696711e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.713802860040282e-07</v>
+        <v>7.946055560168097e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.717462568311952e-07</v>
+        <v>7.982652642884778e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.692822380314997e-07</v>
+        <v>7.736250762915275e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.717462568311952e-07</v>
+        <v>7.982652642884778e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.526470283501596e-07</v>
+        <v>7.982652642884778e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.717462568311952e-07</v>
+        <v>7.982652642884778e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.226113046498165e-07</v>
+        <v>1.303065004677607e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>2.299365169181234e-08</v>
+        <v>1.970440103083444e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>6.326156558507476e-08</v>
+        <v>2.106914369029925e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>3.825720324387161e-08</v>
+        <v>1.763317709836497e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>3.825720324387161e-08</v>
+        <v>1.300277049394183e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>5.101129802349958e-08</v>
+        <v>1.965198170975733e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>6.324305549218837e-08</v>
+        <v>1.968857879258505e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>3.825720324387161e-08</v>
+        <v>1.944217691250448e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>4.513781322319226e-08</v>
+        <v>1.968988726528563e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>1.01084298801542e-07</v>
+        <v>1.290697560184939e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.407516294090689e-08</v>
+        <v>2.664334209433343e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.400678749335834e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.717692304704787e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.717463043056904e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.058384812692892e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.69282253473261e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.713802860040285e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.717462568311953e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.692822380315002e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.717462568311953e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.526470283501597e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.717462568311953e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>1.226113046498165e-07</v>
+      </c>
+      <c r="C10" t="n">
+        <v>2.299365169181237e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>6.326156558507477e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.825720324387164e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3.825720324387164e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5.101129802349967e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>6.324305549218823e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.825720324387164e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.513781322319215e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1.010842988015418e-07</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.407516294090698e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>1.216125130228672e-07</v>
-      </c>
-      <c r="C9" t="n">
-        <v>2.360740274912364e-08</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B11" t="n">
+        <v>1.216125130228671e-07</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2.360740274912366e-08</v>
+      </c>
+      <c r="D11" t="n">
         <v>6.358276200843842e-08</v>
       </c>
-      <c r="E9" t="n">
-        <v>3.91400067072194e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3.91400067072194e-08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5.140208459683698e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6.357735369441526e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.91400067072194e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.033556961331077e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>1.006321112781056e-07</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5.454458947966194e-08</v>
+      <c r="E11" t="n">
+        <v>3.914000670721943e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3.914000670721943e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5.140208459683696e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6.357735369441528e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.914000670721943e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.033556961331068e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1.006321112781058e-07</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.454458947966182e-08</v>
       </c>
     </row>
   </sheetData>
@@ -4799,7 +5679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4867,321 +5747,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.341837292572536e-07</v>
+        <v>6.825729254480966e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>2.743915809930676e-07</v>
+        <v>5.040525938480702e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>7.17506427319739e-06</v>
+        <v>7.581871397939445e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.743915809930676e-07</v>
+        <v>5.040525938480702e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>2.743915809930676e-07</v>
+        <v>5.040525938480702e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>3.744213244059114e-06</v>
+        <v>7.117338738716179e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>7.398971486803651e-07</v>
+        <v>6.862435323399651e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.743915809930676e-07</v>
+        <v>5.040525938480702e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>1.051700586331189e-06</v>
+        <v>6.898855290289863e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>5.415060926222116e-07</v>
+        <v>6.848301314148752e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>4.824037088658687e-07</v>
+        <v>6.837527459330566e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.708051490568686e-08</v>
+        <v>6.897875303253662e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.903636380012861e-08</v>
+        <v>5.093554826978616e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.708051490568686e-08</v>
+        <v>6.897875303253662e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.022531758062952e-08</v>
+        <v>5.093554826978616e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.022531758062952e-08</v>
+        <v>5.093554826978616e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.661627283992013e-08</v>
+        <v>6.820727439058349e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.708051490568686e-08</v>
+        <v>6.897875303253662e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.39940866071953e-08</v>
+        <v>5.093554826978616e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.708051490568686e-08</v>
+        <v>6.897875303253662e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.708051490568686e-08</v>
+        <v>6.897875303253662e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.708051490568686e-08</v>
+        <v>6.897875303253662e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.403868183201082e-08</v>
+        <v>3.341837292572522e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>4.54776458872284e-08</v>
+        <v>2.743915809930685e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>6.405657244387115e-08</v>
+        <v>7.175064273197405e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.48908415301253e-08</v>
+        <v>2.743915809930685e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>5.043407685297167e-08</v>
+        <v>2.743915809930685e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>5.357443976624415e-08</v>
+        <v>3.744213244059111e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.154838216815643e-07</v>
+        <v>7.398971486803664e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.072270444475289e-07</v>
+        <v>2.743915809930685e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>5.565741469572436e-08</v>
+        <v>1.051700586331188e-06</v>
       </c>
       <c r="K4" t="n">
-        <v>5.011784770370821e-08</v>
+        <v>5.41506092622212e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>5.433090206823987e-08</v>
+        <v>4.824037088658676e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1.007369300270198e-07</v>
+        <v>5.708051490568685e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>9.765050172852843e-08</v>
+        <v>4.903636380012857e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>1.00729319840299e-07</v>
+        <v>5.708051490568685e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>9.754465618016432e-08</v>
+        <v>5.022531758062954e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>9.754465618016432e-08</v>
+        <v>5.022531758062952e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>1.002726879612532e-07</v>
+        <v>5.661627283992013e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>1.007369300270198e-07</v>
+        <v>5.708051490568685e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>9.765050172852843e-08</v>
+        <v>5.399408660719532e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>1.007369300270198e-07</v>
+        <v>5.708051490568685e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>1.007369300270198e-07</v>
+        <v>5.708051490568685e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>1.007369300270198e-07</v>
+        <v>5.708051490568685e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.633074026762552e-07</v>
+        <v>5.403868183201068e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.466642534687652e-07</v>
+        <v>4.547764588722811e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.677649908340922e-07</v>
+        <v>6.405657244387107e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.230080407234044e-07</v>
+        <v>4.489084153012527e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.629048465507621e-07</v>
+        <v>5.043407685297161e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.493607607660383e-07</v>
+        <v>5.357443976624404e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.498250028317814e-07</v>
+        <v>1.154838216815642e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.467385745333135e-07</v>
+        <v>1.072270444475287e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.498420060106142e-07</v>
+        <v>5.565741469572424e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.617002938331745e-07</v>
+        <v>5.011784770370827e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.401998706750486e-07</v>
+        <v>5.433090206823969e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.536637237231948e-07</v>
+        <v>1.007369300270198e-07</v>
       </c>
       <c r="C7" t="n">
-        <v>3.132227195178387e-07</v>
+        <v>9.765050172852832e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>3.163093162580337e-07</v>
+        <v>1.007293198402988e-07</v>
       </c>
       <c r="E7" t="n">
-        <v>3.855143860501478e-07</v>
+        <v>9.754465618016423e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>3.132227380447555e-07</v>
+        <v>9.754465618016423e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>3.158449057505634e-07</v>
+        <v>1.002726879612531e-07</v>
       </c>
       <c r="H7" t="n">
-        <v>3.163091478163302e-07</v>
+        <v>1.007369300270198e-07</v>
       </c>
       <c r="I7" t="n">
-        <v>3.132227195178387e-07</v>
+        <v>9.765050172852832e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>3.163091478163302e-07</v>
+        <v>1.007369300270198e-07</v>
       </c>
       <c r="K7" t="n">
-        <v>2.800122139151261e-07</v>
+        <v>1.007369300270198e-07</v>
       </c>
       <c r="L7" t="n">
-        <v>3.163091478163302e-07</v>
+        <v>1.007369300270198e-07</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.27202229094495e-08</v>
+        <v>1.633074026762553e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>4.57901879915319e-08</v>
+        <v>2.466642534687646e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>-9.56768311252067e-08</v>
+        <v>2.677649908340924e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>4.57901879915319e-08</v>
+        <v>2.230080407234045e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>4.57901879915319e-08</v>
+        <v>1.629048465507619e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.493545116431378e-08</v>
+        <v>2.493607607660385e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>5.529448651223884e-08</v>
+        <v>2.498250028317814e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>4.57901879915319e-08</v>
+        <v>2.467385745333135e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>4.756449117548126e-08</v>
+        <v>2.49842006010614e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>5.800130741289512e-08</v>
+        <v>1.617002938331746e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>6.038249559099635e-08</v>
+        <v>3.401998706750481e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.536637237231947e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>3.132227195178386e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>3.163093162580334e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.855143860501475e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>3.132227380447552e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3.158449057505632e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.1630914781633e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>3.132227195178386e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>3.1630914781633e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.800122139151257e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>3.1630914781633e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>6.272022290944929e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4.579018799153191e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-9.567683112520694e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4.579018799153191e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.579018799153191e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-1.493545116431378e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.52944865122387e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.579018799153191e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.756449117548123e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.800130741289496e-08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>6.03824955909962e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>6.540964139405293e-08</v>
-      </c>
-      <c r="C9" t="n">
-        <v>4.806410406091119e-08</v>
-      </c>
-      <c r="D9" t="n">
-        <v>8.998984614087457e-10</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.806410406091119e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.806410406091119e-08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3.334318229953845e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6.239796835809115e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.806410406091119e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.924499551473516e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>6.348824040150717e-08</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6.004165672374655e-08</v>
+      <c r="B11" t="n">
+        <v>6.540964139405284e-08</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4.806410406091115e-08</v>
+      </c>
+      <c r="D11" t="n">
+        <v>8.998984614085339e-10</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.806410406091115e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.806410406091115e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.334318229953838e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6.239796835809099e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.806410406091115e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.924499551473497e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.348824040150703e-08</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6.004165672374644e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5195,7 +6155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5263,321 +6223,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.354753810628175e-07</v>
+        <v>6.748026335844414e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>2.636150955602723e-07</v>
+        <v>4.97799195633785e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>6.094988997790073e-06</v>
+        <v>7.455705302485906e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.636150955602723e-07</v>
+        <v>4.97799195633785e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>2.636150955602723e-07</v>
+        <v>4.97799195633785e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>3.360796403415851e-06</v>
+        <v>7.04145194045386e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>6.272739429722324e-07</v>
+        <v>6.78727194437074e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.636150955602723e-07</v>
+        <v>4.97799195633785e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>7.957293993714327e-07</v>
+        <v>6.809696320129619e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>4.778667664144549e-07</v>
+        <v>6.778802975859656e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>5.516244298327425e-07</v>
+        <v>6.780242731201347e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.473054962707794e-08</v>
+        <v>6.828708262159572e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.842325102806614e-08</v>
+        <v>5.029154334127554e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.473054962707789e-08</v>
+        <v>6.828708262159572e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.945814139428703e-08</v>
+        <v>5.029154334127554e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.945814139428705e-08</v>
+        <v>5.029154334127554e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.429761458391053e-08</v>
+        <v>6.753911754164188e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.473054962707789e-08</v>
+        <v>6.828708262159572e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.185154927503721e-08</v>
+        <v>5.029154334127554e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.473054962707789e-08</v>
+        <v>6.828708262159572e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.473054962707789e-08</v>
+        <v>6.828708262159572e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.473054962707789e-08</v>
+        <v>6.828708262159572e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.197927044348811e-08</v>
+        <v>2.354753810628194e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>4.4225015052932e-08</v>
+        <v>2.63615095560273e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>6.039905003636657e-08</v>
+        <v>6.094988997790074e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.365682386554454e-08</v>
+        <v>2.63615095560273e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>4.860437185249986e-08</v>
+        <v>2.63615095560273e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>5.15463354003205e-08</v>
+        <v>3.360796403415853e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.084187021655169e-07</v>
+        <v>6.272739429722336e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.011800937678873e-07</v>
+        <v>2.63615095560273e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>5.33842883670887e-08</v>
+        <v>7.957293993714312e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>4.836207657252313e-08</v>
+        <v>4.778667664144542e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>5.232871815881931e-08</v>
+        <v>5.516244298327417e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.425358606502092e-08</v>
+        <v>5.47305496270783e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>9.137458571298002e-08</v>
+        <v>4.842325102806608e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>9.424648871445416e-08</v>
+        <v>5.47305496270782e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>9.125525782474427e-08</v>
+        <v>4.9458141394287e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>9.125525782474427e-08</v>
+        <v>4.945814139428704e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>9.382065102185307e-08</v>
+        <v>5.429761458391048e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>9.425358606502091e-08</v>
+        <v>5.47305496270782e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>9.137458571298002e-08</v>
+        <v>5.185154927503753e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>9.425358606502091e-08</v>
+        <v>5.47305496270782e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>9.425358606502091e-08</v>
+        <v>5.47305496270782e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>9.425358606502091e-08</v>
+        <v>5.47305496270782e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.514803356863422e-07</v>
+        <v>5.197927044348809e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.275099288354529e-07</v>
+        <v>4.4225015052932e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.468590379723543e-07</v>
+        <v>6.039905003636656e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.059120302255493e-07</v>
+        <v>4.365682386554452e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.510384977418771e-07</v>
+        <v>4.860437185249985e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.300453611865419e-07</v>
+        <v>5.154633540032074e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.304782962296647e-07</v>
+        <v>1.08418702165517e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.275992958776689e-07</v>
+        <v>1.011800937678874e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.304938215827445e-07</v>
+        <v>5.338428836708891e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5001290800999e-07</v>
+        <v>4.836207657252317e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.129982717144951e-07</v>
+        <v>5.232871815881928e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.195913864167202e-07</v>
+        <v>9.425358606502068e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.699328323344834e-07</v>
+        <v>9.137458571298004e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.728119866215755e-07</v>
+        <v>9.424648871445403e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>3.313482604411776e-07</v>
+        <v>9.125525782474432e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.699328502649229e-07</v>
+        <v>9.125525782474433e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.723788976433563e-07</v>
+        <v>9.38206510218533e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.728118326865243e-07</v>
+        <v>9.425358606502067e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.699328323344834e-07</v>
+        <v>9.137458571298004e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.728118326865243e-07</v>
+        <v>9.425358606502067e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.419757618494618e-07</v>
+        <v>9.425358606502067e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.728118326865243e-07</v>
+        <v>9.425358606502067e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.39897636267267e-08</v>
+        <v>1.514803356863422e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>4.493597626678514e-08</v>
+        <v>2.275099288354531e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>-8.425606442271906e-08</v>
+        <v>2.468590379723544e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>4.493597626678514e-08</v>
+        <v>2.059120302255495e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>4.493597626678514e-08</v>
+        <v>1.510384977418773e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.354038242147016e-08</v>
+        <v>2.300453611865418e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>5.600437404402981e-08</v>
+        <v>2.304782962296654e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>4.493597626678514e-08</v>
+        <v>2.275992958776691e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>5.120062542061679e-08</v>
+        <v>2.304938215827447e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>5.755088608411535e-08</v>
+        <v>1.500129080099902e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.74080544655948e-08</v>
+        <v>3.129982717144955e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.195913864167202e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.699328323344836e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.72811986621576e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.31348260441178e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.699328502649228e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.723788976433561e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.728118326865244e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.699328323344836e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.728118326865244e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.419757618494616e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.728118326865244e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>6.398976362672695e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4.493597626678551e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-8.425606442271925e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4.493597626678551e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.493597626678551e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-1.354038242147009e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.600437404403032e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.493597626678551e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5.120062542061669e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.755088608411544e-08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.740805446559469e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>6.552496952103557e-08</v>
-      </c>
-      <c r="C9" t="n">
-        <v>4.734311947730597e-08</v>
-      </c>
-      <c r="D9" t="n">
-        <v>5.149434993530028e-09</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.734311947730597e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.734311947730597e-08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3.35230885362875e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6.228404789824522e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.734311947730597e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>6.032257072354248e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>6.290302611981475e-08</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5.97329054430464e-08</v>
+      <c r="B11" t="n">
+        <v>6.552496952103548e-08</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4.734311947730625e-08</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.149434993529875e-09</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.734311947730625e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.734311947730625e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.352308853628768e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6.228404789824513e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.734311947730625e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>6.032257072354267e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.290302611981471e-08</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.973290544304607e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5591,7 +6631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5659,321 +6699,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.123997817056847e-07</v>
+        <v>6.576380046317946e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>2.951342442699999e-07</v>
+        <v>4.851882938156504e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>5.011671275641508e-06</v>
+        <v>7.177944876401696e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.951342442699999e-07</v>
+        <v>4.851882938156504e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>2.951342442699999e-07</v>
+        <v>4.851882938156504e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>2.87157298630995e-06</v>
+        <v>6.831926958355802e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>5.976323854231771e-07</v>
+        <v>6.616908061833412e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.951342442699999e-07</v>
+        <v>4.851882938156504e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>5.019149751398626e-07</v>
+        <v>6.607838308512214e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>4.103965068834804e-07</v>
+        <v>6.603191462141872e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>3.196448738298212e-07</v>
+        <v>6.63744056793888e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.415721722656026e-08</v>
+        <v>6.657900158708586e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.905293511181093e-08</v>
+        <v>4.89699832975083e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.415721722656025e-08</v>
+        <v>6.657900158708586e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>5.003038269914346e-08</v>
+        <v>4.89699832975083e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>5.003038269914342e-08</v>
+        <v>4.89699832975083e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.375900618144072e-08</v>
+        <v>6.591695394948138e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.415721722656025e-08</v>
+        <v>6.657900158708586e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.150466008238184e-08</v>
+        <v>4.89699832975083e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.415721722656025e-08</v>
+        <v>6.657900158708586e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.415721722656025e-08</v>
+        <v>6.657900158708586e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.415721722656025e-08</v>
+        <v>6.657900158708586e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.075332001722527e-08</v>
+        <v>2.1239978170568e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>4.397631622250618e-08</v>
+        <v>2.951342442699994e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>5.767139834006181e-08</v>
+        <v>5.011671275641504e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.341885110673823e-08</v>
+        <v>2.951342442699994e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>4.77065514344089e-08</v>
+        <v>2.951342442699994e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>1.002745986171328e-07</v>
+        <v>2.871572986309936e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.048513251119231e-07</v>
+        <v>5.976323854231765e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>4.810076287304702e-08</v>
+        <v>2.951342442699994e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.027325433580553e-07</v>
+        <v>5.019149751398603e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>4.754328966723237e-08</v>
+        <v>4.103965068834883e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>5.091773832542276e-08</v>
+        <v>3.196448738299089e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.21641326403972e-08</v>
+        <v>5.415721722656011e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.951157549621883e-08</v>
+        <v>4.905293511181104e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>9.215703966352142e-08</v>
+        <v>5.415721722656008e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.939523896342285e-08</v>
+        <v>5.003038269914331e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.939523896342285e-08</v>
+        <v>5.003038269914331e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>9.176592159527766e-08</v>
+        <v>5.37590061814409e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>9.216413264039714e-08</v>
+        <v>5.415721722656008e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.951157549621883e-08</v>
+        <v>5.15046600823818e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>9.216413264039714e-08</v>
+        <v>5.415721722656008e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>9.216413264039714e-08</v>
+        <v>5.415721722656008e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>9.216413264039714e-08</v>
+        <v>5.415721722656008e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.476085115512159e-07</v>
+        <v>5.075332001722538e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.214630237697725e-07</v>
+        <v>4.397631622250559e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.400848302645744e-07</v>
+        <v>5.767139834006129e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.005223130278398e-07</v>
+        <v>4.34188511067382e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.473186982708329e-07</v>
+        <v>4.770655143440894e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.238043451074761e-07</v>
+        <v>1.002745986171327e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.242025561525486e-07</v>
+        <v>1.04851325111923e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.215499990084172e-07</v>
+        <v>4.810076287304646e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.242176090670754e-07</v>
+        <v>1.027325433580554e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.461857378476607e-07</v>
+        <v>4.754328966723274e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.042114404236281e-07</v>
+        <v>5.091773832542275e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.993082033744453e-07</v>
+        <v>9.216413264039743e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.44291150967719e-07</v>
+        <v>8.951157549621884e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.469438459924834e-07</v>
+        <v>9.215703966352141e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.992616588566084e-07</v>
+        <v>8.939523896342272e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.442911676209882e-07</v>
+        <v>8.939523896342272e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.465454970667779e-07</v>
+        <v>9.176592159527777e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.469437081118969e-07</v>
+        <v>9.216413264039744e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.44291150967719e-07</v>
+        <v>8.951157549621884e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.469437081118969e-07</v>
+        <v>9.216413264039744e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.193435675799919e-07</v>
+        <v>9.216413264039744e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.469437081118969e-07</v>
+        <v>9.216413264039744e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.283252782029427e-08</v>
+        <v>1.476085115512161e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>4.26831192475412e-08</v>
+        <v>2.214630237697726e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>-6.318426971460047e-08</v>
+        <v>2.400848302645742e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>4.26831192475412e-08</v>
+        <v>2.005223130278397e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>4.26831192475412e-08</v>
+        <v>1.473186982708326e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>-4.922168432349335e-09</v>
+        <v>2.238043451074761e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>5.457292522066073e-08</v>
+        <v>2.242025561525486e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>4.26831192475412e-08</v>
+        <v>2.215499990084171e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>5.632120025520552e-08</v>
+        <v>2.242176090670755e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>5.722323588051622e-08</v>
+        <v>1.461857378476608e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.029338008965608e-08</v>
+        <v>3.042114404236284e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.993082033744459e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.442911509677191e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.469438459924837e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.992616588566084e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.442911676209885e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.465454970667786e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.469437081118977e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.442911509677191e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.469437081118977e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.193435675799924e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.469437081118977e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>6.283252782029412e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4.268311924754112e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-6.318426971460053e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4.268311924754112e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.268311924754112e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-4.922168432349209e-09</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.457292522066062e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.268311924754112e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5.632120025520546e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.7223235880516e-08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.029338008965598e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
+      <c r="B11" t="n">
         <v>6.405914295998579e-08</v>
       </c>
-      <c r="C9" t="n">
-        <v>4.565828620378301e-08</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.273674679074043e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.565828620378301e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.565828620378301e-08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3.608724314893673e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>6.070627761051543e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.565828620378301e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>6.141105078944322e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>6.177501140987324e-08</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5.896439599886198e-08</v>
+      <c r="C11" t="n">
+        <v>4.565828620378302e-08</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.273674679074058e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.565828620378302e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.565828620378302e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.60872431489366e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>6.070627761051546e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.565828620378302e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>6.14110507894433e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.177501140987322e-08</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.896439599886205e-08</v>
       </c>
     </row>
   </sheetData>
@@ -5987,7 +7107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6055,321 +7175,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.236407504686309e-07</v>
+        <v>5.946994062800773e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>2.043781854830418e-07</v>
+        <v>4.437453865652723e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>1.733232771032254e-06</v>
+        <v>6.132813903292426e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.043781854830418e-07</v>
+        <v>4.437453865652723e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>2.043781854830418e-07</v>
+        <v>4.437453865652723e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>9.731014902652515e-07</v>
+        <v>6.000721837756627e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>3.780542697514776e-07</v>
+        <v>5.961850647938012e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.043781854830418e-07</v>
+        <v>4.437453865652723e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>4.255508539246241e-07</v>
+        <v>5.96691167490639e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>3.767306759699556e-07</v>
+        <v>5.965313269565864e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>3.254864332624493e-06</v>
+        <v>5.994667180225571e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.130304696422687e-08</v>
+        <v>6.02277276957089e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.585095511957495e-08</v>
+        <v>4.491456998993875e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.130304696422687e-08</v>
+        <v>6.02277276957089e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.685840397788099e-08</v>
+        <v>4.491456998993875e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.685840397788101e-08</v>
+        <v>4.491456998993875e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.093231664332297e-08</v>
+        <v>5.990132466002641e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.130304696422687e-08</v>
+        <v>6.02277276957089e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.881222704817558e-08</v>
+        <v>4.491456998993875e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.130304696422687e-08</v>
+        <v>6.02277276957089e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.130304696422687e-08</v>
+        <v>6.02277276957089e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.130304696422687e-08</v>
+        <v>6.02277276957089e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8.710236815605257e-08</v>
+        <v>2.23640750468628e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>3.923139320590187e-08</v>
+        <v>2.043781854830418e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>8.892156884114622e-08</v>
+        <v>1.733232771032253e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>3.880335000359866e-08</v>
+        <v>2.043781854830418e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>4.085054759164486e-08</v>
+        <v>2.043781854830418e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>8.673163783514883e-08</v>
+        <v>9.731014902652519e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>4.352581871580315e-08</v>
+        <v>3.780542697514778e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>8.46115482400013e-08</v>
+        <v>2.043781854830418e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>8.853869022554276e-08</v>
+        <v>4.255508539246248e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>4.262116281607962e-08</v>
+        <v>3.767306759699551e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>4.44652338982871e-08</v>
+        <v>3.254864332624485e-06</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.385377143420711e-08</v>
+        <v>5.13030469642268e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.136295151815588e-08</v>
+        <v>4.585095511957498e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.384619763440891e-08</v>
+        <v>5.13030469642268e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.132834271317377e-08</v>
+        <v>4.685840397788103e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.132834271317377e-08</v>
+        <v>4.685840397788103e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.348304111330339e-08</v>
+        <v>5.093231664332298e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.385377143420711e-08</v>
+        <v>5.130304696422683e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.136295151815588e-08</v>
+        <v>4.881222704817549e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.385377143420711e-08</v>
+        <v>5.130304696422679e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.385377143420711e-08</v>
+        <v>5.13030469642268e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.385377143420711e-08</v>
+        <v>5.13030469642268e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.367373478013125e-07</v>
+        <v>8.710236815605254e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.052718618109944e-07</v>
+        <v>3.923139320590175e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.225014384216047e-07</v>
+        <v>8.892156884114619e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.858431939217621e-07</v>
+        <v>3.880335000359855e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.364820874203522e-07</v>
+        <v>4.085054759164492e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.074012204310451e-07</v>
+        <v>8.673163783514887e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.077719507519375e-07</v>
+        <v>4.352581871580316e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.052811308358978e-07</v>
+        <v>8.461154824000139e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.077859110821898e-07</v>
+        <v>8.853869022554281e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.354178435798745e-07</v>
+        <v>4.262116281607962e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.819735333514092e-07</v>
+        <v>4.446523389828705e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.833270832990444e-07</v>
+        <v>8.38537714342072e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.246388834142855e-07</v>
+        <v>8.136295151815595e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.271297747992275e-07</v>
+        <v>8.3846197634409e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.751862565319652e-07</v>
+        <v>8.132834271317376e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.246388944229047e-07</v>
+        <v>8.132834271317375e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.267589730094327e-07</v>
+        <v>8.348304111330347e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.271297033303366e-07</v>
+        <v>8.38537714342072e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.246388834142855e-07</v>
+        <v>8.136295151815595e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.271297033303366e-07</v>
+        <v>8.38537714342072e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.017503233175794e-07</v>
+        <v>8.38537714342072e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.271297033303366e-07</v>
+        <v>8.38537714342072e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.636847184636535e-08</v>
+        <v>1.367373478013126e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>4.115960522503639e-08</v>
+        <v>2.052718618109943e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>1.74441418856964e-08</v>
+        <v>2.225014384216047e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>4.115960522503639e-08</v>
+        <v>1.858431939217622e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>4.115960522503639e-08</v>
+        <v>1.364820874203523e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>3.80433769344096e-08</v>
+        <v>2.074012204310453e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>5.338872800745622e-08</v>
+        <v>2.077719507519378e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>4.115960522503639e-08</v>
+        <v>2.052811308358979e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>5.225775348638812e-08</v>
+        <v>2.077859110821901e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>5.253730930285857e-08</v>
+        <v>1.354178435798748e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>-5.159406390671005e-09</v>
+        <v>2.81973533351409e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.833270832990442e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.246388834142852e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.271297747992274e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.751862565319652e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.246388944229045e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.267589730094326e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.271297033303364e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.246388834142852e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.271297033303364e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.017503233175792e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.271297033303364e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5.636847184636542e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4.115960522503652e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.744414188569646e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4.115960522503652e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.115960522503652e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3.804337693440966e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.338872800745623e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.115960522503652e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5.22577534863881e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.253730930285868e-08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-5.159406390670952e-09</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>5.771396691783779e-08</v>
-      </c>
-      <c r="C9" t="n">
-        <v>4.26660177221339e-08</v>
-      </c>
-      <c r="D9" t="n">
-        <v>4.186147114617032e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.26660177221339e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.26660177221339e-08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5.006178250526426e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>5.650673982662633e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.26660177221339e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.60427530850221e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>5.615396781900236e-08</v>
-      </c>
-      <c r="L9" t="n">
-        <v>3.270361249865411e-08</v>
+      <c r="B11" t="n">
+        <v>5.771396691783784e-08</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4.266601772213399e-08</v>
+      </c>
+      <c r="D11" t="n">
+        <v>4.18614711461704e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.266601772213399e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.266601772213399e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5.006178250526432e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5.650673982662637e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.266601772213399e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.604275308502215e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.615396781900243e-08</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3.270361249865421e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6383,7 +7583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6451,321 +7651,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.738051003272917e-07</v>
+        <v>5.753468265359458e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>2.600714768771025e-07</v>
+        <v>4.317637315502408e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>3.281462800268663e-07</v>
+        <v>5.76237632689872e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.600714768771025e-07</v>
+        <v>4.317637315502408e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>2.600714768771025e-07</v>
+        <v>4.317637315502408e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>3.510480031175283e-07</v>
+        <v>5.743949510470641e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.132504707786719e-07</v>
+        <v>5.744671457640056e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.600714768771025e-07</v>
+        <v>4.317637315502408e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>5.455443963966097e-07</v>
+        <v>5.785089713491473e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>4.23614278833739e-07</v>
+        <v>5.773864845797407e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>2.937927886613287e-07</v>
+        <v>5.753910699669404e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.833834699930852e-08</v>
+        <v>5.819588926371975e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.517157828980064e-08</v>
+        <v>4.360973109492525e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>4.833834699930852e-08</v>
+        <v>5.819588926371975e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.597479132205112e-08</v>
+        <v>4.360973109492525e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.597479132205116e-08</v>
+        <v>4.360973109492525e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>4.802031741401061e-08</v>
+        <v>5.799676839020681e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>4.833834699930852e-08</v>
+        <v>5.819588926371975e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.619108010696144e-08</v>
+        <v>4.360973109492525e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>4.833834699930852e-08</v>
+        <v>5.819588926371975e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>4.833834699930852e-08</v>
+        <v>5.819588926371975e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>4.833834699930852e-08</v>
+        <v>5.819588926371975e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>7.716768301349565e-08</v>
+        <v>2.738051003272916e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>3.776628916047665e-08</v>
+        <v>2.600714768771021e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>4.070274728317763e-08</v>
+        <v>3.28146280026866e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>3.734492037933366e-08</v>
+        <v>2.600714768771021e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>3.83096365597741e-08</v>
+        <v>2.600714768771021e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>7.684965342819775e-08</v>
+        <v>3.510480031175236e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>8.072628283995949e-08</v>
+        <v>2.132504707786718e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>7.502041612114861e-08</v>
+        <v>2.600714768771021e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>4.135448085457857e-08</v>
+        <v>5.45544396396608e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>4.049665620774816e-08</v>
+        <v>4.236142788337387e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>4.059758362576485e-08</v>
+        <v>2.937927886613284e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.57524833897223e-08</v>
+        <v>4.83383469993086e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.360521649737525e-08</v>
+        <v>4.517157828980058e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.574538270686546e-08</v>
+        <v>4.83383469993086e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.359083262330293e-08</v>
+        <v>4.597479132205102e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.359083262330293e-08</v>
+        <v>4.597479132205105e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.543445380442433e-08</v>
+        <v>4.802031741401063e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.57524833897223e-08</v>
+        <v>4.83383469993086e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.360521649737525e-08</v>
+        <v>4.619108010696145e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.57524833897223e-08</v>
+        <v>4.83383469993086e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.57524833897223e-08</v>
+        <v>4.83383469993086e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.57524833897223e-08</v>
+        <v>4.83383469993086e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.223430046070686e-07</v>
+        <v>7.716768301349563e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.822206866593778e-07</v>
+        <v>3.77662891604765e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.972199690137142e-07</v>
+        <v>4.070274728317763e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.652565329210213e-07</v>
+        <v>3.734492037933364e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.221572448828966e-07</v>
+        <v>3.830963655977408e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.840422528626709e-07</v>
+        <v>7.684965342819766e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.843602824479594e-07</v>
+        <v>8.072628283995941e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.822130155556216e-07</v>
+        <v>7.50204161211485e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.843724706165951e-07</v>
+        <v>4.135448085457844e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.211910018291594e-07</v>
+        <v>4.049665620774816e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.491425149545221e-07</v>
+        <v>4.059758362576479e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.491348919582105e-07</v>
+        <v>7.575248338972233e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.813902492954938e-07</v>
+        <v>7.36052164973752e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.835375652141607e-07</v>
+        <v>7.574538270686545e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.210902096991442e-07</v>
+        <v>7.359083262330291e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.813902630373861e-07</v>
+        <v>7.359083262330291e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.832194866025429e-07</v>
+        <v>7.543445380442431e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.835375161878407e-07</v>
+        <v>7.575248338972233e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.813902492954938e-07</v>
+        <v>7.36052164973752e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.835375161878407e-07</v>
+        <v>7.575248338972233e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.63604521219941e-07</v>
+        <v>7.575248338972233e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.835375161878407e-07</v>
+        <v>7.575248338972233e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.268097816033351e-08</v>
+        <v>1.223430046070687e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>3.78802958484329e-08</v>
+        <v>1.822206866593777e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>5.081796064600656e-08</v>
+        <v>1.972199690137142e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>3.78802958484329e-08</v>
+        <v>1.652565329210213e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>3.78802958484329e-08</v>
+        <v>1.221572448828964e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>5.033720995863933e-08</v>
+        <v>1.84042252862671e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>5.459578743348114e-08</v>
+        <v>1.843602824479591e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>3.78802958484329e-08</v>
+        <v>1.822130155556214e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>4.614970004375081e-08</v>
+        <v>1.843724706165949e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>4.841670897451186e-08</v>
+        <v>1.211910018291592e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.267520125456268e-08</v>
+        <v>2.491425149545221e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.491348919582103e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.813902492954933e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.835375652141603e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.210902096991438e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.813902630373858e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.832194866025425e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.835375161878406e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.813902492954933e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.835375161878406e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.636045212199406e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.835375161878406e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5.268097816033355e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.788029584843288e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5.081796064600662e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.788029584843288e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3.788029584843288e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5.033720995863942e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.45957874334812e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.788029584843288e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.614970004375086e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>4.841670897451187e-08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.267520125456272e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>5.502538052657488e-08</v>
-      </c>
-      <c r="C9" t="n">
-        <v>4.05694618592433e-08</v>
-      </c>
-      <c r="D9" t="n">
-        <v>5.426678223586419e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.05694618592433e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.05694618592433e-08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5.395437160877899e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>5.580865677079819e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.05694618592433e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.236984265090154e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>5.328909026198601e-08</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5.50271763591388e-08</v>
+      <c r="B11" t="n">
+        <v>5.502538052657489e-08</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4.056946185924327e-08</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.426678223586423e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.056946185924327e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.056946185924327e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5.395437160877896e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5.580865677079827e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.056946185924327e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.236984265090161e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.3289090261986e-08</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.502717635913882e-08</v>
       </c>
     </row>
   </sheetData>
@@ -6779,7 +8059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6847,321 +8127,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.899632162372695e-07</v>
+        <v>5.752319956498864e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>4.702013376485056e-07</v>
+        <v>4.375633752461682e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>2.467482580094146e-07</v>
+        <v>5.735075327080476e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>4.702013376485056e-07</v>
+        <v>4.375633752461682e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>4.702013376485056e-07</v>
+        <v>4.375633752461682e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>3.120076437273601e-07</v>
+        <v>5.727935952261155e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>2.008481128580149e-07</v>
+        <v>5.727175164429267e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>4.702013376485056e-07</v>
+        <v>4.375633752461682e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>6.514204025428505e-07</v>
+        <v>5.780977314726471e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>3.506531682883769e-07</v>
+        <v>5.749571048730078e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>3.227731686162914e-07</v>
+        <v>5.741304940924225e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>4.921767146142061e-08</v>
+        <v>5.803734488943689e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.71304236888689e-08</v>
+        <v>4.393087089650015e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>4.921767146142062e-08</v>
+        <v>5.803734488943689e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.788467649190283e-08</v>
+        <v>4.393087089650015e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.788467649190285e-08</v>
+        <v>4.393087089650015e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>4.892655464672935e-08</v>
+        <v>5.789044435468451e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>4.921767146142062e-08</v>
+        <v>5.803734488943689e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.724697550851787e-08</v>
+        <v>4.393087089650015e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>4.921767146142061e-08</v>
+        <v>5.803734488943689e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>4.921767146142062e-08</v>
+        <v>5.803734488943689e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>4.921767146142062e-08</v>
+        <v>5.803734488943689e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.186308100518539e-08</v>
+        <v>3.899632162372698e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>3.982474911003928e-08</v>
+        <v>4.702013376485057e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>4.165429973525666e-08</v>
+        <v>2.467482580094143e-07</v>
       </c>
       <c r="E4" t="n">
-        <v>3.935781367178307e-08</v>
+        <v>4.702013376485057e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>3.992534752121801e-08</v>
+        <v>4.702013376485057e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>4.157196419049413e-08</v>
+        <v>3.120076437273634e-07</v>
       </c>
       <c r="H4" t="n">
-        <v>8.153932102630687e-08</v>
+        <v>2.00848112858015e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>3.989238505228268e-08</v>
+        <v>4.702013376485057e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>4.272956103155709e-08</v>
+        <v>6.514204025428516e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>4.165659449547834e-08</v>
+        <v>3.506531682883774e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>4.176225137432849e-08</v>
+        <v>3.227731686162915e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7.660260631286156e-08</v>
+        <v>4.921767146142054e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>7.463191035995869e-08</v>
+        <v>4.713042368886886e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>7.659546641002578e-08</v>
+        <v>4.921767146142054e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>7.462814655832687e-08</v>
+        <v>4.788467649190282e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>7.462814655832687e-08</v>
+        <v>4.788467649190282e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>7.631148949817011e-08</v>
+        <v>4.892655464672923e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>7.660260631286156e-08</v>
+        <v>4.921767146142054e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>7.463191035995869e-08</v>
+        <v>4.724697550851789e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>7.660260631286156e-08</v>
+        <v>4.921767146142054e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>7.660260631286156e-08</v>
+        <v>4.921767146142054e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>7.660260631286156e-08</v>
+        <v>4.921767146142054e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.228490731394893e-07</v>
+        <v>4.186308100518541e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>1.826539214926969e-07</v>
+        <v>3.982474911003934e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>1.974126540357602e-07</v>
+        <v>4.16542997352567e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.657596641178409e-07</v>
+        <v>3.935781367178317e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.228380154349694e-07</v>
+        <v>3.992534752121799e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>1.843156724648781e-07</v>
+        <v>4.157196419049408e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>1.846067892795648e-07</v>
+        <v>8.153932102630678e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>1.826360933266665e-07</v>
+        <v>3.989238505228268e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>1.846189264368159e-07</v>
+        <v>4.272956103155694e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.217018918534156e-07</v>
+        <v>4.165659449547819e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.491178878853916e-07</v>
+        <v>4.176225137432849e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.443305657907737e-07</v>
+        <v>7.660260631286131e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>1.751809057204276e-07</v>
+        <v>7.46319103599587e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>1.771516472794791e-07</v>
+        <v>7.65954664100256e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.130557453459689e-07</v>
+        <v>7.462814655832686e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>1.751809208471885e-07</v>
+        <v>7.462814655832686e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>1.768604848586391e-07</v>
+        <v>7.631148949817012e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>1.771516016733305e-07</v>
+        <v>7.660260631286131e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>1.751809057204276e-07</v>
+        <v>7.46319103599587e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>1.771516016733305e-07</v>
+        <v>7.660260631286131e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.5736345370623e-07</v>
+        <v>7.660260631286131e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>1.771516016733305e-07</v>
+        <v>7.660260631286131e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.951403902835349e-08</v>
+        <v>1.228490731394893e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>3.275414986463269e-08</v>
+        <v>1.826539214926969e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>5.313129456686015e-08</v>
+        <v>1.974126540357601e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>3.275414986463269e-08</v>
+        <v>1.65759664117841e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>3.275414986463269e-08</v>
+        <v>1.228380154349695e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>5.142682612464678e-08</v>
+        <v>1.843156724648779e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>5.484740693678971e-08</v>
+        <v>1.846067892795643e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>3.275414986463269e-08</v>
+        <v>1.826360933266668e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>4.362297655902216e-08</v>
+        <v>1.846189264368159e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>5.00990614504956e-08</v>
+        <v>1.217018918534155e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>5.485911351416807e-08</v>
+        <v>2.491178878853913e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.44330565790774e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>1.751809057204279e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>1.771516472794794e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.130557453459692e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>1.751809208471887e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1.768604848586394e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1.771516016733306e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>1.751809057204279e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>1.771516016733306e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.573634537062301e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.771516016733306e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>4.951403902835345e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>3.27541498646327e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>5.313129456686015e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>3.27541498646327e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>3.27541498646327e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>5.142682612464679e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.484740693678968e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>3.27541498646327e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>4.36229765590221e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.00990614504956e-08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>5.485911351416804e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>5.364506823603162e-08</v>
-      </c>
-      <c r="C9" t="n">
-        <v>3.867089383702052e-08</v>
-      </c>
-      <c r="D9" t="n">
-        <v>5.511848473937762e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>3.867089383702052e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3.867089383702052e-08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>5.43383926296152e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>5.582031971010918e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.867089383702052e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.125118962105987e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>5.38837662247743e-08</v>
-      </c>
-      <c r="L9" t="n">
-        <v>5.582451794838306e-08</v>
+      <c r="B11" t="n">
+        <v>5.364506823603156e-08</v>
+      </c>
+      <c r="C11" t="n">
+        <v>3.867089383702053e-08</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5.51184847393776e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>3.867089383702053e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3.867089383702053e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>5.433839262961518e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5.58203197101091e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>3.867089383702053e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.125118962105977e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>5.388376622477428e-08</v>
+      </c>
+      <c r="L11" t="n">
+        <v>5.582451794838298e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7175,7 +8535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7243,321 +8603,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.043024615722345e-07</v>
+        <v>6.581776167182959e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>2.539560559860084e-07</v>
+        <v>4.84516933928062e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>6.522590371209833e-06</v>
+        <v>7.303916601448456e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.539560559860084e-07</v>
+        <v>4.84516933928062e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>2.539560559860084e-07</v>
+        <v>4.84516933928062e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>3.03177294268051e-06</v>
+        <v>6.819306600701462e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>7.243151289713567e-07</v>
+        <v>6.624032739983556e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.539560559860084e-07</v>
+        <v>4.84516933928062e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>4.721561349507309e-07</v>
+        <v>6.597753235818511e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>5.046604805376328e-07</v>
+        <v>6.604411326513336e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>6.535271159018725e-07</v>
+        <v>6.637182340603905e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.558275668573658e-08</v>
+        <v>6.654639226893643e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.812004872307443e-08</v>
+        <v>4.898167957780224e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.558275668573658e-08</v>
+        <v>6.654639226893643e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.926738036668907e-08</v>
+        <v>4.898167957780224e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.926738036668894e-08</v>
+        <v>4.898167957780224e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.513907237189504e-08</v>
+        <v>6.587574272668006e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.558275668573658e-08</v>
+        <v>6.654639226893643e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>5.262707680346246e-08</v>
+        <v>4.898167957780224e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.558275668573658e-08</v>
+        <v>6.654639226893643e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.558275668573658e-08</v>
+        <v>6.654639226893643e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.558275668573658e-08</v>
+        <v>6.654639226893643e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.135090005865104e-08</v>
+        <v>3.043024615722344e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>4.376381663076205e-08</v>
+        <v>2.539560559860044e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>6.144081877977558e-08</v>
+        <v>6.522590371209838e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.323546039298993e-08</v>
+        <v>2.539560559860044e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>4.796093456687052e-08</v>
+        <v>2.539560559860044e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>1.040610114267867e-07</v>
+        <v>3.031772942680513e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>1.096451592357831e-07</v>
+        <v>7.243151289713634e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>1.015490158583541e-07</v>
+        <v>2.539560559860044e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>1.069370062153881e-07</v>
+        <v>4.721561349507305e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>4.814467393527898e-08</v>
+        <v>5.046604805376331e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>5.160311677514532e-08</v>
+        <v>6.535271159018845e-07</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9.61628073833599e-08</v>
+        <v>5.55827566857364e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>9.320712750108589e-08</v>
+        <v>4.812004872307433e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>9.615521432944745e-08</v>
+        <v>5.55827566857364e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>9.311726430376338e-08</v>
+        <v>4.926738036668902e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>9.311726430376338e-08</v>
+        <v>4.926738036668902e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>9.571912306951828e-08</v>
+        <v>5.513907237189503e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>9.61628073833599e-08</v>
+        <v>5.55827566857364e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>9.320712750108589e-08</v>
+        <v>5.262707680346234e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>9.61628073833599e-08</v>
+        <v>5.55827566857364e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>9.61628073833599e-08</v>
+        <v>5.55827566857364e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>9.61628073833599e-08</v>
+        <v>5.55827566857364e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.56108332248944e-07</v>
+        <v>5.135090005865111e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.353692796206917e-07</v>
+        <v>4.376381663076187e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.554454185704985e-07</v>
+        <v>6.144081877977561e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>2.128714327238525e-07</v>
+        <v>4.323546039298966e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.557116127148458e-07</v>
+        <v>4.796093456687036e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.379411628972808e-07</v>
+        <v>1.040610114267865e-07</v>
       </c>
       <c r="H6" t="n">
-        <v>2.383848472111028e-07</v>
+        <v>1.096451592357832e-07</v>
       </c>
       <c r="I6" t="n">
-        <v>2.35429167328848e-07</v>
+        <v>1.015490158583539e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>2.384010168959392e-07</v>
+        <v>1.06937006215388e-07</v>
       </c>
       <c r="K6" t="n">
-        <v>1.545800037406236e-07</v>
+        <v>4.81446739352788e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>3.243295469368624e-07</v>
+        <v>5.160311677514535e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2.373764988860227e-07</v>
+        <v>9.616280738335993e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.927069436802557e-07</v>
+        <v>9.320712750108584e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.956627687637543e-07</v>
+        <v>9.615521432944756e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>3.599680472494952e-07</v>
+        <v>9.311726430376352e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.927069599196067e-07</v>
+        <v>9.311726430376352e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.95218939248688e-07</v>
+        <v>9.57191230695184e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.956626235625303e-07</v>
+        <v>9.616280738335993e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.927069436802557e-07</v>
+        <v>9.320712750108584e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.956626235625303e-07</v>
+        <v>9.616280738335993e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>2.618914750887548e-07</v>
+        <v>9.616280738335993e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.956626235625303e-07</v>
+        <v>9.616280738335993e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6.09445576524467e-08</v>
+        <v>1.561083322489441e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>4.427923158467102e-08</v>
+        <v>2.353692796206917e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>-9.033000861124622e-08</v>
+        <v>2.55445418570499e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>4.427923158467102e-08</v>
+        <v>2.128714327238525e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>4.427923158467102e-08</v>
+        <v>1.557116127148458e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>-3.231366287156972e-09</v>
+        <v>2.379411628972806e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>5.236509968593783e-08</v>
+        <v>2.383848472111027e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>4.427923158467102e-08</v>
+        <v>2.354291673288482e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>5.766709270179501e-08</v>
+        <v>2.384010168959388e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>5.621170203553713e-08</v>
+        <v>1.545800037406235e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>4.960104991894095e-08</v>
+        <v>3.243295469368626e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2.37376498886023e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.927069436802558e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.956627687637545e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>3.599680472494953e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.92706959919607e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.952189392486885e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.956626235625299e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.927069436802558e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.956626235625299e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>2.618914750887551e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.956626235625299e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>6.09445576524466e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4.427923158467095e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-9.03300086112463e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4.427923158467095e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.427923158467095e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-3.231366287157032e-09</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.236509968593761e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.427923158467095e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5.766709270179508e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.621170203553705e-08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>4.960104991894084e-08</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>6.326890906933911e-08</v>
-      </c>
-      <c r="C9" t="n">
-        <v>4.631206457011891e-08</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.659903678574918e-09</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.631206457011891e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.631206457011891e-08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3.674911117442956e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>5.978779408147311e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.631206457011891e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>6.193742275848696e-08</v>
-      </c>
-      <c r="K9" t="n">
-        <v>6.134179627423304e-08</v>
-      </c>
-      <c r="L9" t="n">
-        <v>6.061270624817429e-08</v>
+      <c r="B11" t="n">
+        <v>6.326890906933909e-08</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4.631206457011884e-08</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.659903678574899e-09</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.631206457011884e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.631206457011884e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3.674911117442943e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5.978779408147317e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.631206457011884e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>6.193742275848697e-08</v>
+      </c>
+      <c r="K11" t="n">
+        <v>6.134179627423299e-08</v>
+      </c>
+      <c r="L11" t="n">
+        <v>6.061270624817427e-08</v>
       </c>
     </row>
   </sheetData>
@@ -7571,7 +9011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7639,321 +9079,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.948050669451562e-07</v>
+        <v>6.133040517486054e-08</v>
       </c>
       <c r="C2" t="n">
-        <v>2.495200800165707e-07</v>
+        <v>4.580856487550756e-08</v>
       </c>
       <c r="D2" t="n">
-        <v>4.480366187130273e-06</v>
+        <v>6.691934784409366e-08</v>
       </c>
       <c r="E2" t="n">
-        <v>2.495200800165707e-07</v>
+        <v>4.580856487550756e-08</v>
       </c>
       <c r="F2" t="n">
-        <v>2.495200800165707e-07</v>
+        <v>4.580856487550756e-08</v>
       </c>
       <c r="G2" t="n">
-        <v>1.456864673547174e-06</v>
+        <v>6.247759185310925e-08</v>
       </c>
       <c r="H2" t="n">
-        <v>3.064426155884973e-07</v>
+        <v>6.143807194672122e-08</v>
       </c>
       <c r="I2" t="n">
-        <v>2.495200800165707e-07</v>
+        <v>4.580856487550756e-08</v>
       </c>
       <c r="J2" t="n">
-        <v>5.314001165844475e-07</v>
+        <v>6.169900161333991e-08</v>
       </c>
       <c r="K2" t="n">
-        <v>2.462160174775328e-07</v>
+        <v>6.139678011467376e-08</v>
       </c>
       <c r="L2" t="n">
-        <v>1.796440860699804e-05</v>
+        <v>6.141427844216745e-08</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.128332230086864e-08</v>
+        <v>6.212417492733947e-08</v>
       </c>
       <c r="C3" t="n">
-        <v>4.688599147451802e-08</v>
+        <v>4.629021144269969e-08</v>
       </c>
       <c r="D3" t="n">
-        <v>5.128332230086864e-08</v>
+        <v>6.212417492733947e-08</v>
       </c>
       <c r="E3" t="n">
-        <v>4.777960402368339e-08</v>
+        <v>4.629021144269969e-08</v>
       </c>
       <c r="F3" t="n">
-        <v>4.777960402368338e-08</v>
+        <v>4.629021144269969e-08</v>
       </c>
       <c r="G3" t="n">
-        <v>5.091771410119047e-08</v>
+        <v>6.170975987767346e-08</v>
       </c>
       <c r="H3" t="n">
-        <v>5.128332230086864e-08</v>
+        <v>6.212417492733947e-08</v>
       </c>
       <c r="I3" t="n">
-        <v>4.883238965683055e-08</v>
+        <v>4.629021144269969e-08</v>
       </c>
       <c r="J3" t="n">
-        <v>5.128332230086864e-08</v>
+        <v>6.212417492733947e-08</v>
       </c>
       <c r="K3" t="n">
-        <v>5.128332230086864e-08</v>
+        <v>6.212417492733947e-08</v>
       </c>
       <c r="L3" t="n">
-        <v>5.128332230086864e-08</v>
+        <v>6.212417492733947e-08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>9.365468093836151e-08</v>
+        <v>1.948050669451561e-07</v>
       </c>
       <c r="C4" t="n">
-        <v>4.053756920039496e-08</v>
+        <v>2.495200800165707e-07</v>
       </c>
       <c r="D4" t="n">
-        <v>5.3290053639898e-08</v>
+        <v>4.48036618713027e-06</v>
       </c>
       <c r="E4" t="n">
-        <v>4.007078544090268e-08</v>
+        <v>2.495200800165707e-07</v>
       </c>
       <c r="F4" t="n">
-        <v>4.256274707141346e-08</v>
+        <v>2.495200800165707e-07</v>
       </c>
       <c r="G4" t="n">
-        <v>9.328907273868352e-08</v>
+        <v>1.456864673547176e-06</v>
       </c>
       <c r="H4" t="n">
-        <v>9.732691341766255e-08</v>
+        <v>3.064426155884976e-07</v>
       </c>
       <c r="I4" t="n">
-        <v>9.120374829432354e-08</v>
+        <v>2.495200800165707e-07</v>
       </c>
       <c r="J4" t="n">
-        <v>4.625729923917595e-08</v>
+        <v>5.314001165844475e-07</v>
       </c>
       <c r="K4" t="n">
-        <v>4.342814848038388e-08</v>
+        <v>2.462160174775327e-07</v>
       </c>
       <c r="L4" t="n">
-        <v>5.081647907960241e-08</v>
+        <v>1.796440860699799e-05</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>8.337434994921474e-08</v>
+        <v>5.128332230086862e-08</v>
       </c>
       <c r="C5" t="n">
-        <v>8.092341730517671e-08</v>
+        <v>4.688599147451813e-08</v>
       </c>
       <c r="D5" t="n">
-        <v>8.336725389779207e-08</v>
+        <v>5.128332230086862e-08</v>
       </c>
       <c r="E5" t="n">
-        <v>8.087286720327672e-08</v>
+        <v>4.777960402368343e-08</v>
       </c>
       <c r="F5" t="n">
-        <v>8.087286720327672e-08</v>
+        <v>4.777960402368343e-08</v>
       </c>
       <c r="G5" t="n">
-        <v>8.300874174953658e-08</v>
+        <v>5.091771410119052e-08</v>
       </c>
       <c r="H5" t="n">
-        <v>8.337434994921474e-08</v>
+        <v>5.128332230086862e-08</v>
       </c>
       <c r="I5" t="n">
-        <v>8.092341730517671e-08</v>
+        <v>4.883238965683065e-08</v>
       </c>
       <c r="J5" t="n">
-        <v>8.337434994921474e-08</v>
+        <v>5.128332230086862e-08</v>
       </c>
       <c r="K5" t="n">
-        <v>8.337434994921474e-08</v>
+        <v>5.128332230086862e-08</v>
       </c>
       <c r="L5" t="n">
-        <v>8.337434994921474e-08</v>
+        <v>5.128332230086862e-08</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1.349843906937532e-07</v>
+        <v>9.365468093836157e-08</v>
       </c>
       <c r="C6" t="n">
-        <v>2.016770136192037e-07</v>
+        <v>4.053756920039471e-08</v>
       </c>
       <c r="D6" t="n">
-        <v>2.184961227956458e-07</v>
+        <v>5.329005363989795e-08</v>
       </c>
       <c r="E6" t="n">
-        <v>1.82760437740377e-07</v>
+        <v>4.007078544090276e-08</v>
       </c>
       <c r="F6" t="n">
-        <v>1.347000884413932e-07</v>
+        <v>4.25627470714135e-08</v>
       </c>
       <c r="G6" t="n">
-        <v>2.037878565048204e-07</v>
+        <v>9.328907273868346e-08</v>
       </c>
       <c r="H6" t="n">
-        <v>2.041534647044771e-07</v>
+        <v>9.732691341766279e-08</v>
       </c>
       <c r="I6" t="n">
-        <v>2.017025320604605e-07</v>
+        <v>9.120374829432355e-08</v>
       </c>
       <c r="J6" t="n">
-        <v>2.041670584039028e-07</v>
+        <v>4.625729923917604e-08</v>
       </c>
       <c r="K6" t="n">
-        <v>1.33699539630462e-07</v>
+        <v>4.342814848038399e-08</v>
       </c>
       <c r="L6" t="n">
-        <v>2.764063463322573e-07</v>
+        <v>5.081647907960232e-08</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1.782359923126423e-07</v>
+        <v>8.337434994921474e-08</v>
       </c>
       <c r="C7" t="n">
-        <v>2.178525264554485e-07</v>
+        <v>8.092341730517677e-08</v>
       </c>
       <c r="D7" t="n">
-        <v>2.203035278343196e-07</v>
+        <v>8.336725389779211e-08</v>
       </c>
       <c r="E7" t="n">
-        <v>2.663975463004478e-07</v>
+        <v>8.08728672032769e-08</v>
       </c>
       <c r="F7" t="n">
-        <v>2.178525208654668e-07</v>
+        <v>8.08728672032769e-08</v>
       </c>
       <c r="G7" t="n">
-        <v>2.199378508998082e-07</v>
+        <v>8.300874174953674e-08</v>
       </c>
       <c r="H7" t="n">
-        <v>2.203034590994866e-07</v>
+        <v>8.337434994921474e-08</v>
       </c>
       <c r="I7" t="n">
-        <v>2.178525264554485e-07</v>
+        <v>8.092341730517677e-08</v>
       </c>
       <c r="J7" t="n">
-        <v>2.203034590994866e-07</v>
+        <v>8.337434994921474e-08</v>
       </c>
       <c r="K7" t="n">
-        <v>1.959294325411013e-07</v>
+        <v>8.337434994921474e-08</v>
       </c>
       <c r="L7" t="n">
-        <v>2.203034590994866e-07</v>
+        <v>8.337434994921474e-08</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>5.874448081747572e-08</v>
+        <v>1.349843906937535e-07</v>
       </c>
       <c r="C8" t="n">
-        <v>4.112041293156126e-08</v>
+        <v>2.016770136192046e-07</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.833367247433219e-08</v>
+        <v>2.184961227956465e-07</v>
       </c>
       <c r="E8" t="n">
-        <v>4.112041293156126e-08</v>
+        <v>1.827604377403778e-07</v>
       </c>
       <c r="F8" t="n">
-        <v>4.112041293156126e-08</v>
+        <v>1.347000884413938e-07</v>
       </c>
       <c r="G8" t="n">
-        <v>2.57726593942181e-08</v>
+        <v>2.037878565048212e-07</v>
       </c>
       <c r="H8" t="n">
-        <v>5.65964293753709e-08</v>
+        <v>2.04153464704478e-07</v>
       </c>
       <c r="I8" t="n">
-        <v>4.112041293156126e-08</v>
+        <v>2.01702532060461e-07</v>
       </c>
       <c r="J8" t="n">
-        <v>5.110706383928955e-08</v>
+        <v>2.041670584039037e-07</v>
       </c>
       <c r="K8" t="n">
-        <v>5.735858308808073e-08</v>
+        <v>1.336995396304625e-07</v>
       </c>
       <c r="L8" t="n">
-        <v>-3.26202314203146e-07</v>
+        <v>2.764063463322585e-07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>1.78235992312642e-07</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2.178525264554481e-07</v>
+      </c>
+      <c r="D9" t="n">
+        <v>2.203035278343192e-07</v>
+      </c>
+      <c r="E9" t="n">
+        <v>2.663975463004475e-07</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2.178525208654664e-07</v>
+      </c>
+      <c r="G9" t="n">
+        <v>2.199378508998083e-07</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.203034590994863e-07</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.178525264554481e-07</v>
+      </c>
+      <c r="J9" t="n">
+        <v>2.203034590994863e-07</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1.959294325411014e-07</v>
+      </c>
+      <c r="L9" t="n">
+        <v>2.203034590994863e-07</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>5.874448081747577e-08</v>
+      </c>
+      <c r="C10" t="n">
+        <v>4.112041293156132e-08</v>
+      </c>
+      <c r="D10" t="n">
+        <v>-5.833367247433202e-08</v>
+      </c>
+      <c r="E10" t="n">
+        <v>4.112041293156132e-08</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4.112041293156132e-08</v>
+      </c>
+      <c r="G10" t="n">
+        <v>2.577265939421835e-08</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5.659642937537094e-08</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4.112041293156132e-08</v>
+      </c>
+      <c r="J10" t="n">
+        <v>5.110706383928956e-08</v>
+      </c>
+      <c r="K10" t="n">
+        <v>5.735858308808085e-08</v>
+      </c>
+      <c r="L10" t="n">
+        <v>-3.262023142031457e-07</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>5.979263358442648e-08</v>
-      </c>
-      <c r="C9" t="n">
-        <v>4.345629007776916e-08</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.211064339995028e-08</v>
-      </c>
-      <c r="E9" t="n">
-        <v>4.345629007776916e-08</v>
-      </c>
-      <c r="F9" t="n">
-        <v>4.345629007776916e-08</v>
-      </c>
-      <c r="G9" t="n">
-        <v>4.612609660839304e-08</v>
-      </c>
-      <c r="H9" t="n">
-        <v>5.892293010469566e-08</v>
-      </c>
-      <c r="I9" t="n">
-        <v>4.345629007776916e-08</v>
-      </c>
-      <c r="J9" t="n">
-        <v>5.668618095882721e-08</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="B11" t="n">
+        <v>5.97926335844266e-08</v>
+      </c>
+      <c r="C11" t="n">
+        <v>4.345629007776925e-08</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.211064339995036e-08</v>
+      </c>
+      <c r="E11" t="n">
+        <v>4.345629007776925e-08</v>
+      </c>
+      <c r="F11" t="n">
+        <v>4.345629007776925e-08</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4.612609660839308e-08</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5.892293010469569e-08</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4.345629007776925e-08</v>
+      </c>
+      <c r="J11" t="n">
+        <v>5.668618095882726e-08</v>
+      </c>
+      <c r="K11" t="n">
         <v>5.922842064077098e-08</v>
       </c>
-      <c r="L9" t="n">
-        <v>-9.669956295315789e-08</v>
+      <c r="L11" t="n">
+        <v>-9.669956295315784e-08</v>
       </c>
     </row>
   </sheetData>
